--- a/Documents/ログイン機能設計書.xlsx
+++ b/Documents/ログイン機能設計書.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724170D9-816E-4E30-A18A-91E65875C9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FCACFD-C121-4E05-9CCB-70E61F34E228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="詳細クラス図" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -963,163 +964,163 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1632,18 +1633,144 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>57149</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFA39583-2D21-919C-1E8A-A07E37F09D67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="57149" y="2209800"/>
+          <a:ext cx="3286125" cy="3009900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>942975</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7176C0E8-2493-5929-FADB-5F804514970D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3486150" y="1000125"/>
+          <a:ext cx="5172075" cy="3076575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>11699</xdr:rowOff>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>125999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>600075</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>94687</xdr:rowOff>
+      <xdr:rowOff>47062</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1672,7 +1799,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4419600" y="2869199"/>
+          <a:off x="5000625" y="2821574"/>
           <a:ext cx="3314700" cy="1216463"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1685,15 +1812,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>771525</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1707,12 +1834,14 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm rot="5400000" flipH="1" flipV="1">
-          <a:off x="2895600" y="1895475"/>
-          <a:ext cx="971550" cy="933450"/>
+        <a:xfrm flipV="1">
+          <a:off x="2190750" y="1609725"/>
+          <a:ext cx="1647825" cy="1285875"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
         </a:prstGeom>
         <a:ln>
           <a:solidFill>
@@ -1740,16 +1869,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>28578</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>876300</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>781052</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1764,8 +1893,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipV="1">
-          <a:off x="4324351" y="1943101"/>
-          <a:ext cx="1000126" cy="847722"/>
+          <a:off x="5476876" y="2028824"/>
+          <a:ext cx="857250" cy="723902"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1796,16 +1925,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>298020</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>336120</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>4295</xdr:rowOff>
+      <xdr:rowOff>80495</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1834,7 +1963,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2686050" y="1095375"/>
+          <a:off x="3838575" y="1171575"/>
           <a:ext cx="3098370" cy="794870"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1846,16 +1975,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1059370</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>73889</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>992695</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>26264</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1884,7 +2013,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1362075" y="2867025"/>
+          <a:off x="180975" y="2657475"/>
           <a:ext cx="2954845" cy="2331314"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1892,6 +2021,140 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>857250</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="テキスト ボックス 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D539B3B3-0C9F-9929-810B-4E63822172A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8029575" y="1028700"/>
+          <a:ext cx="542925" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
+            <a:t>dao</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>333374</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>981075</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト ボックス 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B229873D-BE38-4D3E-AB56-03A7AA09EF83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362074" y="2247900"/>
+          <a:ext cx="647701" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
+            <a:t>entity</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2204,214 +2467,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="J1" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="46" t="s">
+      <c r="A2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="46" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="49">
+      <c r="G2" s="56"/>
+      <c r="H2" s="59">
         <v>45806</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="35"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="38"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="39"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="63" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="27"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="22"/>
+      <c r="B6" s="20"/>
       <c r="C6" s="23"/>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="28"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="21"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="28"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="22"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="23"/>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="28"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="21"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="33" t="s">
         <v>48</v>
       </c>
       <c r="C9" s="23"/>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="28"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="21"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="68"/>
-      <c r="B10" s="66" t="s">
+      <c r="A10" s="31"/>
+      <c r="B10" s="33" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="28"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="69"/>
-      <c r="B11" s="66" t="s">
+      <c r="A11" s="32"/>
+      <c r="B11" s="33" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="23"/>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="28"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="21"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="22"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="23"/>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="28"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="21"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="30"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="29"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3402,21 +3665,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -3429,6 +3677,21 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -3451,19 +3714,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -3475,189 +3738,189 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="46" t="s">
+      <c r="A2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="46" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="49">
+      <c r="G2" s="56"/>
+      <c r="H2" s="59">
         <v>45806</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="35"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="38"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="27"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="28"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="21"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="41"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="43"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="64"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="44"/>
+      <c r="A8" s="48"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="65"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="35"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="44"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="65"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="44"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="65"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="44"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="65"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="44"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="35"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="44"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="65"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="28"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="21"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="22"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="23"/>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
       <c r="H15" s="23"/>
       <c r="I15" s="6" t="s">
         <v>6</v>
@@ -3667,10 +3930,10 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="22"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="23"/>
       <c r="D16" s="6" t="s">
         <v>4</v>
@@ -3684,17 +3947,17 @@
       <c r="G16" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="22"/>
-      <c r="J16" s="28"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="21"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="24">
+      <c r="A17" s="69">
         <v>1</v>
       </c>
-      <c r="B17" s="22"/>
+      <c r="B17" s="20"/>
       <c r="C17" s="23"/>
       <c r="D17" s="5" t="s">
         <v>32</v>
@@ -3708,17 +3971,17 @@
       <c r="G17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="31" t="s">
+      <c r="H17" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="22"/>
-      <c r="J17" s="28"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="24">
+      <c r="A18" s="69">
         <v>2</v>
       </c>
-      <c r="B18" s="22"/>
+      <c r="B18" s="20"/>
       <c r="C18" s="23"/>
       <c r="D18" s="5" t="s">
         <v>33</v>
@@ -3732,17 +3995,17 @@
       <c r="G18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="22"/>
-      <c r="J18" s="28"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="24">
+      <c r="A19" s="69">
         <v>3</v>
       </c>
-      <c r="B19" s="22"/>
+      <c r="B19" s="20"/>
       <c r="C19" s="23"/>
       <c r="D19" s="5" t="s">
         <v>34</v>
@@ -3756,15 +4019,15 @@
       <c r="G19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="31"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="28"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="24">
+      <c r="A20" s="69">
         <v>4</v>
       </c>
-      <c r="B20" s="22"/>
+      <c r="B20" s="20"/>
       <c r="C20" s="23"/>
       <c r="D20" s="5" t="s">
         <v>35</v>
@@ -3776,45 +4039,45 @@
       <c r="G20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="31"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="28"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="24"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="69"/>
+      <c r="B21" s="20"/>
       <c r="C21" s="23"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="28"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="24"/>
-      <c r="B22" s="22"/>
+      <c r="A22" s="69"/>
+      <c r="B22" s="20"/>
       <c r="C22" s="23"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="28"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="20"/>
+      <c r="A23" s="68"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="27"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="30"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="29"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4795,21 +5058,6 @@
     <row r="1000" s="1" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
@@ -4826,6 +5074,21 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -4846,19 +5109,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -4870,48 +5133,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="46" t="s">
+      <c r="A2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="46" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="49">
+      <c r="G2" s="56"/>
+      <c r="H2" s="59">
         <v>45806</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="35"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="38"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="39"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="11"/>

--- a/Documents/ログイン機能設計書.xlsx
+++ b/Documents/ログイン機能設計書.xlsx
@@ -8,17 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FCACFD-C121-4E05-9CCB-70E61F34E228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6A85DF-C388-4565-9EA7-2446D0AB92E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="3" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
     <sheet name="画面設計書" sheetId="1" r:id="rId2"/>
     <sheet name="詳細クラス図" sheetId="2" r:id="rId3"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId4"/>
+    <sheet name="JUnitテスト仕様書兼報告書" sheetId="6" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="ああ">#REF!</definedName>
+    <definedName name="範囲１" localSheetId="4">#REF!</definedName>
+    <definedName name="範囲１">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="123">
   <si>
     <t>備考</t>
   </si>
@@ -300,6 +306,376 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>テスト仕様書兼
+結果報告書</t>
+  </si>
+  <si>
+    <t>テストレベル</t>
+  </si>
+  <si>
+    <t>システムテスト</t>
+  </si>
+  <si>
+    <t>テストベース</t>
+  </si>
+  <si>
+    <t>テスト対象</t>
+  </si>
+  <si>
+    <t>ログイン画面</t>
+  </si>
+  <si>
+    <t>重要度</t>
+  </si>
+  <si>
+    <t>重要度は、次のいずれかを持つ</t>
+  </si>
+  <si>
+    <t>◎：仕様　⇒100%解決する必要がある</t>
+  </si>
+  <si>
+    <t>○：重要　⇒別途テストパス率の指針に従う</t>
+  </si>
+  <si>
+    <t>△：重要ではない　⇒別途テストパス率の指針に従う</t>
+  </si>
+  <si>
+    <t>×：無くても良い　⇒個別に検討する</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>系統</t>
+  </si>
+  <si>
+    <t>テストテーマ</t>
+  </si>
+  <si>
+    <t>条件</t>
+  </si>
+  <si>
+    <t>操作手順</t>
+  </si>
+  <si>
+    <t>予測結果</t>
+  </si>
+  <si>
+    <t>テスト日</t>
+  </si>
+  <si>
+    <t>対応者</t>
+  </si>
+  <si>
+    <t>結果</t>
+  </si>
+  <si>
+    <t>◎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正常系
+</t>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>ログイン画面へ遷移する</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>異常系</t>
+  </si>
+  <si>
+    <t>ユーザIDがDBに登録されていないときのログインボタン動作</t>
+  </si>
+  <si>
+    <t>ログインするボタンを押下する</t>
+  </si>
+  <si>
+    <t>・ユーザID：1234
+・パスワード：test</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常系</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーIDとパスワードが入力されていないときのログインボタン操作</t>
+    <rPh sb="13" eb="15">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ユーザID：
+・パスワード：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>◎</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">正常系
+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正しいユーザーIDとパスワードを入力したときのログインボタン操作</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ユーザID：yamagata
+・パスワード：0613</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニュー画面へ遷移する</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラー画面へ遷移する
+エラーの原因がユーザーIDまたはパスワードが正しくない旨通知する
+ログイン画面へ戻るリンクが表示される</t>
+    <rPh sb="48" eb="50">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/login.jsp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログインするボタンを押下する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>会社名</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>コンサイズ</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>実施者</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>期待する結果</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>備考・特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トッキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>JUnitテスト仕様書兼報告書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>テストクラス</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>検証するメソッド</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>URLアクセス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Junitテスト仕様書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン機能</t>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>logincheck(String userId)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正常系</t>
+    <rPh sb="0" eb="3">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正しいidを渡したときに、かえってくる値が
+Nullではない</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常系</t>
+    <rPh sb="0" eb="3">
+      <t>イジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UserDAOTest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UserDAOTset</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>間違ったidを渡したときに、帰ってくる値がNullである</t>
+    <rPh sb="0" eb="2">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラー画面へ遷移する
+エラーの原因がユーザーIDまたはパスワードが入力されていない旨通知する
+ログイン画面へ戻るリンクが表示される</t>
+    <rPh sb="33" eb="35">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -308,7 +684,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -336,8 +712,62 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,8 +780,14 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="47">
+  <borders count="70">
     <border>
       <left/>
       <right/>
@@ -907,11 +1343,287 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -967,51 +1679,144 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="66" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1123,9 +1928,143 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="9" fillId="0" borderId="62" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準_生産計画ED書" xfId="2" xr:uid="{8B7484DD-D763-4367-AB09-30083449E2E4}"/>
+    <cellStyle name="標準_東京理科大DBレイアウト" xfId="3" xr:uid="{BDBBD14C-2080-4392-8068-482763934B2F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2467,19 +3406,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="54" t="s">
+      <c r="E1" s="73"/>
+      <c r="F1" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="73"/>
       <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
@@ -2491,190 +3430,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="55" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="55" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="59">
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>45806</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="37"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="38"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="39"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="44"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="24" t="s">
+      <c r="B6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="21"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24" t="s">
+      <c r="B7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="21"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="54"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="24" t="s">
+      <c r="B8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="21"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="54"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="19" t="s">
+      <c r="C9" s="52"/>
+      <c r="D9" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="21"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="54"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="31"/>
-      <c r="B10" s="33" t="s">
+      <c r="A10" s="61"/>
+      <c r="B10" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="54"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="32"/>
-      <c r="B11" s="33" t="s">
+      <c r="A11" s="62"/>
+      <c r="B11" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="19" t="s">
+      <c r="C11" s="52"/>
+      <c r="D11" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="21"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="54"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="24" t="s">
+      <c r="B12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="21"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="54"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="29"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="59"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3677,6 +4616,10 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="A8:C8"/>
@@ -3688,10 +4631,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -3714,19 +4653,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="54" t="s">
+      <c r="E1" s="73"/>
+      <c r="F1" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="73"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -3738,190 +4677,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="55" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="55" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="59">
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>45806</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="37"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="38"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="38"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="69"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="70" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="44"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="21"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="62"/>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="64"/>
+      <c r="A7" s="93"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="95"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="48"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="65"/>
+      <c r="A8" s="79"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="96"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="48"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="65"/>
+      <c r="A9" s="79"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="96"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="48"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="65"/>
+      <c r="A10" s="79"/>
+      <c r="B10" s="80"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="96"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="48"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="65"/>
+      <c r="A11" s="79"/>
+      <c r="B11" s="80"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="96"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="48"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="65"/>
+      <c r="A12" s="79"/>
+      <c r="B12" s="80"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="96"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="48"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="65"/>
+      <c r="A13" s="79"/>
+      <c r="B13" s="80"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="96"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="21"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24" t="s">
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="23"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="52"/>
       <c r="I15" s="6" t="s">
         <v>6</v>
       </c>
@@ -3930,11 +4869,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="23"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="6" t="s">
         <v>4</v>
       </c>
@@ -3947,18 +4886,18 @@
       <c r="G16" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H16" s="67" t="s">
+      <c r="H16" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="69">
+      <c r="A17" s="100">
         <v>1</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="23"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="5" t="s">
         <v>32</v>
       </c>
@@ -3971,18 +4910,18 @@
       <c r="G17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="21"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="69">
+      <c r="A18" s="100">
         <v>2</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="23"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="5" t="s">
         <v>33</v>
       </c>
@@ -3995,18 +4934,18 @@
       <c r="G18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="20"/>
-      <c r="J18" s="21"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="69">
+      <c r="A19" s="100">
         <v>3</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="23"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="5" t="s">
         <v>34</v>
       </c>
@@ -4019,16 +4958,16 @@
       <c r="G19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="24"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="69">
+      <c r="A20" s="100">
         <v>4</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="23"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="5" t="s">
         <v>35</v>
       </c>
@@ -4039,45 +4978,45 @@
       <c r="G20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="24"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="21"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="69"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="23"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="21"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="69"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="23"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="54"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="68"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
+      <c r="A23" s="99"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="57"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="29"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="59"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5109,19 +6048,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="54" t="s">
+      <c r="E1" s="73"/>
+      <c r="F1" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="73"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -5133,48 +6072,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="55" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="55" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="59">
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>45806</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="37"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="38"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="39"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="11"/>
@@ -6509,4 +7448,3487 @@
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19EAADF0-8FB5-466C-B7DB-2454AA8DCCC5}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="6" width="2.5" style="1" customWidth="1"/>
+    <col min="7" max="10" width="7.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.75" style="1" customWidth="1"/>
+    <col min="12" max="20" width="7.125" style="1" customWidth="1"/>
+    <col min="21" max="26" width="7.625" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="12.625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="18" customHeight="1">
+      <c r="A1" s="76" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="85" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="85" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="73"/>
+      <c r="S1" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="75"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="116">
+        <v>45810</v>
+      </c>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="87"/>
+      <c r="S2" s="86"/>
+      <c r="T2" s="95"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="96"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="84"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="84"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="115"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="92" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="75"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="54"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="97" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="54"/>
+    </row>
+    <row r="8" spans="1:26" ht="7.5" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="13"/>
+    </row>
+    <row r="9" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="22"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+    </row>
+    <row r="10" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="20"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+    </row>
+    <row r="11" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+    </row>
+    <row r="12" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+    </row>
+    <row r="13" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+    </row>
+    <row r="14" spans="1:26" ht="8.25" customHeight="1">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="13"/>
+    </row>
+    <row r="15" spans="1:26" ht="18.75" customHeight="1">
+      <c r="A15" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="52"/>
+      <c r="C15" s="114" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="52"/>
+      <c r="E15" s="98" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="52"/>
+      <c r="G15" s="98" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="51"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" s="52"/>
+      <c r="L15" s="98" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" s="51"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="52"/>
+      <c r="R15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="T15" s="30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="54.75" customHeight="1">
+      <c r="A16" s="107">
+        <v>1</v>
+      </c>
+      <c r="B16" s="52"/>
+      <c r="C16" s="108" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="52"/>
+      <c r="E16" s="108" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="52"/>
+      <c r="G16" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="H16" s="51"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="109" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="52"/>
+      <c r="L16" s="112" t="s">
+        <v>95</v>
+      </c>
+      <c r="M16" s="113"/>
+      <c r="N16" s="113"/>
+      <c r="O16" s="106" t="s">
+        <v>79</v>
+      </c>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="52"/>
+      <c r="R16" s="146">
+        <v>45810</v>
+      </c>
+      <c r="S16" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="T16" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+    </row>
+    <row r="17" spans="1:26" ht="75" customHeight="1">
+      <c r="A17" s="107">
+        <v>2</v>
+      </c>
+      <c r="B17" s="52"/>
+      <c r="C17" s="108" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="52"/>
+      <c r="E17" s="108" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="52"/>
+      <c r="G17" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="51"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="109" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="52"/>
+      <c r="L17" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="M17" s="110"/>
+      <c r="N17" s="111"/>
+      <c r="O17" s="106" t="s">
+        <v>94</v>
+      </c>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="52"/>
+      <c r="R17" s="146">
+        <v>45810</v>
+      </c>
+      <c r="S17" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="T17" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="U17" s="33"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="33"/>
+    </row>
+    <row r="18" spans="1:26" ht="79.5" customHeight="1">
+      <c r="A18" s="107">
+        <v>3</v>
+      </c>
+      <c r="B18" s="52"/>
+      <c r="C18" s="108" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="52"/>
+      <c r="E18" s="108" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="52"/>
+      <c r="G18" s="109" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="51"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="109" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="52"/>
+      <c r="L18" s="106" t="s">
+        <v>83</v>
+      </c>
+      <c r="M18" s="51"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="106" t="s">
+        <v>122</v>
+      </c>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="52"/>
+      <c r="R18" s="146">
+        <v>45810</v>
+      </c>
+      <c r="S18" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="T18" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="33"/>
+    </row>
+    <row r="19" spans="1:26" ht="42.75" customHeight="1">
+      <c r="A19" s="107">
+        <v>4</v>
+      </c>
+      <c r="B19" s="52"/>
+      <c r="C19" s="108" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="52"/>
+      <c r="E19" s="108" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="52"/>
+      <c r="G19" s="109" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="51"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="109" t="s">
+        <v>92</v>
+      </c>
+      <c r="K19" s="52"/>
+      <c r="L19" s="106" t="s">
+        <v>83</v>
+      </c>
+      <c r="M19" s="51"/>
+      <c r="N19" s="52"/>
+      <c r="O19" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="P19" s="51"/>
+      <c r="Q19" s="52"/>
+      <c r="R19" s="146">
+        <v>45810</v>
+      </c>
+      <c r="S19" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="T19" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="U19" s="33"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
+    </row>
+    <row r="20" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A20" s="107"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="109"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="106"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="52"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="33"/>
+      <c r="V20" s="33"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="33"/>
+      <c r="Y20" s="33"/>
+      <c r="Z20" s="33"/>
+    </row>
+    <row r="21" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A21" s="107"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="106"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="52"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+    </row>
+    <row r="22" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A22" s="107"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="109"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="106"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="33"/>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="33"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="33"/>
+    </row>
+    <row r="23" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A23" s="107"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="109"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="109"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="52"/>
+      <c r="O23" s="106"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="52"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="33"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="33"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="33"/>
+    </row>
+    <row r="24" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A24" s="107"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="109"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="109"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="52"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="52"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="33"/>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="33"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
+    </row>
+    <row r="25" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A25" s="107"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="109"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="51"/>
+      <c r="N25" s="52"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="52"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="33"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+    </row>
+    <row r="26" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A26" s="107"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="109"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="52"/>
+      <c r="O26" s="106"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="52"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
+    </row>
+    <row r="27" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A27" s="107"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="109"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="106"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="106"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="52"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+    </row>
+    <row r="28" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A28" s="107"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="109"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="51"/>
+      <c r="N28" s="52"/>
+      <c r="O28" s="106"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="52"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+    </row>
+    <row r="29" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A29" s="107"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="109"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="109"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="106"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="52"/>
+      <c r="O29" s="106"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="52"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="33"/>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="33"/>
+      <c r="Y29" s="33"/>
+      <c r="Z29" s="33"/>
+    </row>
+    <row r="30" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A30" s="107"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="109"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="109"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="106"/>
+      <c r="M30" s="51"/>
+      <c r="N30" s="52"/>
+      <c r="O30" s="106"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="52"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="33"/>
+      <c r="Y30" s="33"/>
+      <c r="Z30" s="33"/>
+    </row>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A31" s="103"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="105"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="102"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="33"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="33"/>
+      <c r="Y31" s="33"/>
+      <c r="Z31" s="33"/>
+    </row>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1">
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+    </row>
+    <row r="33" spans="4:10" ht="12.75" customHeight="1">
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36"/>
+    </row>
+    <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="36" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="37" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="38" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="39" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="40" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="41" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="42" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="43" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="44" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="45" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="46" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="47" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="48" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="136">
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L29:N29"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="L16" r:id="rId1" xr:uid="{60FEEA2B-DE7F-47A6-A1DC-CD43456CE68F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1434AE2-ECA4-4D9B-945B-3109E1075373}">
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr defaultColWidth="7" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="11.875" style="38" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="48" customWidth="1"/>
+    <col min="3" max="6" width="7.125" style="38" customWidth="1"/>
+    <col min="7" max="7" width="7.125" style="48" customWidth="1"/>
+    <col min="8" max="13" width="7.125" style="38" customWidth="1"/>
+    <col min="14" max="19" width="10.625" style="38" customWidth="1"/>
+    <col min="20" max="16384" width="7" style="38"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="135" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="136"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="138" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="O1" s="138" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" s="138" t="s">
+        <v>100</v>
+      </c>
+      <c r="S1" s="140"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="136"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="138" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="139"/>
+      <c r="L2" s="139"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="O2" s="141">
+        <v>45807</v>
+      </c>
+      <c r="P2" s="142"/>
+      <c r="Q2" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="R2" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" s="144"/>
+    </row>
+    <row r="3" spans="1:19" ht="11.25" customHeight="1">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="129" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="129" t="s">
+        <v>106</v>
+      </c>
+      <c r="O4" s="130"/>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="R4" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="S4" s="131"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1">
+      <c r="A5" s="44">
+        <v>1</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="125" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="126" t="s">
+        <v>117</v>
+      </c>
+      <c r="O5" s="127"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="145">
+        <v>45810</v>
+      </c>
+      <c r="R5" s="132"/>
+      <c r="S5" s="133"/>
+    </row>
+    <row r="6" spans="1:19" ht="30" customHeight="1">
+      <c r="A6" s="46">
+        <v>2</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="125" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" s="125"/>
+      <c r="E6" s="125"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" s="125"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="125"/>
+      <c r="M6" s="125"/>
+      <c r="N6" s="126" t="s">
+        <v>121</v>
+      </c>
+      <c r="O6" s="127"/>
+      <c r="P6" s="128"/>
+      <c r="Q6" s="47">
+        <v>45810</v>
+      </c>
+      <c r="R6" s="124"/>
+      <c r="S6" s="124"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1">
+      <c r="A7" s="46">
+        <v>3</v>
+      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="125"/>
+      <c r="N7" s="126"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="128"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="124"/>
+      <c r="S7" s="124"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" customHeight="1">
+      <c r="A8" s="46">
+        <v>4</v>
+      </c>
+      <c r="B8" s="46"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="125"/>
+      <c r="K8" s="125"/>
+      <c r="L8" s="125"/>
+      <c r="M8" s="125"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="124"/>
+      <c r="S8" s="124"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" customHeight="1">
+      <c r="A9" s="46"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="122"/>
+      <c r="P9" s="123"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="124"/>
+      <c r="S9" s="124"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1">
+      <c r="A10" s="46"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="117"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="122"/>
+      <c r="P10" s="123"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="124"/>
+      <c r="S10" s="124"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1">
+      <c r="A11" s="46"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="118"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="119"/>
+      <c r="L11" s="119"/>
+      <c r="M11" s="120"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="122"/>
+      <c r="P11" s="123"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="124"/>
+      <c r="S11" s="124"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1">
+      <c r="A12" s="46"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="119"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="122"/>
+      <c r="P12" s="123"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="124"/>
+      <c r="S12" s="124"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1">
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="119"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="119"/>
+      <c r="L13" s="119"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="122"/>
+      <c r="P13" s="123"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="124"/>
+      <c r="S13" s="124"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1">
+      <c r="A14" s="46"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="120"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="122"/>
+      <c r="P14" s="123"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="124"/>
+      <c r="S14" s="124"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1">
+      <c r="A15" s="46"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="119"/>
+      <c r="L15" s="119"/>
+      <c r="M15" s="120"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="122"/>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="124"/>
+      <c r="S15" s="124"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1">
+      <c r="A16" s="46"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="122"/>
+      <c r="P16" s="123"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="124"/>
+      <c r="S16" s="124"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" customHeight="1">
+      <c r="A17" s="46"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="119"/>
+      <c r="L17" s="119"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="122"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1">
+      <c r="A18" s="46"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="119"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="124"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" customHeight="1">
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="120"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="122"/>
+      <c r="P19" s="123"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="124"/>
+      <c r="S19" s="124"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" customHeight="1">
+      <c r="A20" s="46"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="120"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="122"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="124"/>
+      <c r="S20" s="124"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" customHeight="1">
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="120"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="122"/>
+      <c r="P21" s="123"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="124"/>
+      <c r="S21" s="124"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1">
+      <c r="A22" s="46"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="118"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="120"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="122"/>
+      <c r="P22" s="123"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="124"/>
+      <c r="S22" s="124"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" customHeight="1">
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="120"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="122"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="46"/>
+      <c r="R23" s="124"/>
+      <c r="S23" s="124"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" customHeight="1">
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
+      <c r="M24" s="120"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="122"/>
+      <c r="P24" s="123"/>
+      <c r="Q24" s="46"/>
+      <c r="R24" s="124"/>
+      <c r="S24" s="124"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" customHeight="1">
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="118"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="120"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="122"/>
+      <c r="P25" s="123"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="124"/>
+      <c r="S25" s="124"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" customHeight="1">
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="118"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="120"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="122"/>
+      <c r="P26" s="123"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="124"/>
+      <c r="S26" s="124"/>
+    </row>
+    <row r="27" spans="1:19" ht="30" customHeight="1">
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="118"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="120"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="122"/>
+      <c r="P27" s="123"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="124"/>
+      <c r="S27" s="124"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" customHeight="1">
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="122"/>
+      <c r="P28" s="123"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="124"/>
+      <c r="S28" s="124"/>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="119"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="120"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="122"/>
+      <c r="P29" s="123"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="124"/>
+      <c r="S29" s="124"/>
+    </row>
+    <row r="30" spans="1:19" ht="30" customHeight="1">
+      <c r="A30" s="46"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="119"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="120"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="122"/>
+      <c r="P30" s="123"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="124"/>
+      <c r="S30" s="124"/>
+    </row>
+    <row r="31" spans="1:19" ht="30" customHeight="1">
+      <c r="A31" s="46"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="119"/>
+      <c r="J31" s="119"/>
+      <c r="K31" s="119"/>
+      <c r="L31" s="119"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="122"/>
+      <c r="P31" s="123"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="124"/>
+      <c r="S31" s="124"/>
+    </row>
+    <row r="32" spans="1:19" ht="30" customHeight="1">
+      <c r="A32" s="46"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="118"/>
+      <c r="I32" s="119"/>
+      <c r="J32" s="119"/>
+      <c r="K32" s="119"/>
+      <c r="L32" s="119"/>
+      <c r="M32" s="120"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="122"/>
+      <c r="P32" s="123"/>
+      <c r="Q32" s="46"/>
+      <c r="R32" s="124"/>
+      <c r="S32" s="124"/>
+    </row>
+    <row r="33" spans="1:19" ht="30" customHeight="1">
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="117"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="118"/>
+      <c r="I33" s="119"/>
+      <c r="J33" s="119"/>
+      <c r="K33" s="119"/>
+      <c r="L33" s="119"/>
+      <c r="M33" s="120"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="122"/>
+      <c r="P33" s="123"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="124"/>
+      <c r="S33" s="124"/>
+    </row>
+    <row r="34" spans="1:19" ht="30" customHeight="1">
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="117"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="117"/>
+      <c r="G34" s="117"/>
+      <c r="H34" s="118"/>
+      <c r="I34" s="119"/>
+      <c r="J34" s="119"/>
+      <c r="K34" s="119"/>
+      <c r="L34" s="119"/>
+      <c r="M34" s="120"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="122"/>
+      <c r="P34" s="123"/>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="124"/>
+      <c r="S34" s="124"/>
+    </row>
+    <row r="35" spans="1:19" ht="30" customHeight="1">
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="117"/>
+      <c r="D35" s="117"/>
+      <c r="E35" s="117"/>
+      <c r="F35" s="117"/>
+      <c r="G35" s="117"/>
+      <c r="H35" s="118"/>
+      <c r="I35" s="119"/>
+      <c r="J35" s="119"/>
+      <c r="K35" s="119"/>
+      <c r="L35" s="119"/>
+      <c r="M35" s="120"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="122"/>
+      <c r="P35" s="123"/>
+      <c r="Q35" s="46"/>
+      <c r="R35" s="124"/>
+      <c r="S35" s="124"/>
+    </row>
+    <row r="36" spans="1:19" ht="30" customHeight="1">
+      <c r="A36" s="46"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="118"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="119"/>
+      <c r="K36" s="119"/>
+      <c r="L36" s="119"/>
+      <c r="M36" s="120"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="122"/>
+      <c r="P36" s="123"/>
+      <c r="Q36" s="46"/>
+      <c r="R36" s="124"/>
+      <c r="S36" s="124"/>
+    </row>
+    <row r="37" spans="1:19" ht="30" customHeight="1">
+      <c r="A37" s="46"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="119"/>
+      <c r="J37" s="119"/>
+      <c r="K37" s="119"/>
+      <c r="L37" s="119"/>
+      <c r="M37" s="120"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="122"/>
+      <c r="P37" s="123"/>
+      <c r="Q37" s="46"/>
+      <c r="R37" s="124"/>
+      <c r="S37" s="124"/>
+    </row>
+    <row r="38" spans="1:19" ht="30" customHeight="1">
+      <c r="A38" s="46"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="117"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="117"/>
+      <c r="G38" s="117"/>
+      <c r="H38" s="118"/>
+      <c r="I38" s="119"/>
+      <c r="J38" s="119"/>
+      <c r="K38" s="119"/>
+      <c r="L38" s="119"/>
+      <c r="M38" s="120"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="122"/>
+      <c r="P38" s="123"/>
+      <c r="Q38" s="46"/>
+      <c r="R38" s="124"/>
+      <c r="S38" s="124"/>
+    </row>
+    <row r="39" spans="1:19" ht="30" customHeight="1">
+      <c r="A39" s="46"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="117"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="117"/>
+      <c r="G39" s="117"/>
+      <c r="H39" s="118"/>
+      <c r="I39" s="119"/>
+      <c r="J39" s="119"/>
+      <c r="K39" s="119"/>
+      <c r="L39" s="119"/>
+      <c r="M39" s="120"/>
+      <c r="N39" s="121"/>
+      <c r="O39" s="122"/>
+      <c r="P39" s="123"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="124"/>
+      <c r="S39" s="124"/>
+    </row>
+    <row r="40" spans="1:19" ht="30" customHeight="1">
+      <c r="A40" s="46"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="117"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="119"/>
+      <c r="J40" s="119"/>
+      <c r="K40" s="119"/>
+      <c r="L40" s="119"/>
+      <c r="M40" s="120"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="122"/>
+      <c r="P40" s="123"/>
+      <c r="Q40" s="46"/>
+      <c r="R40" s="124"/>
+      <c r="S40" s="124"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" customHeight="1">
+      <c r="A41" s="46"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="117"/>
+      <c r="D41" s="117"/>
+      <c r="E41" s="117"/>
+      <c r="F41" s="117"/>
+      <c r="G41" s="117"/>
+      <c r="H41" s="118"/>
+      <c r="I41" s="119"/>
+      <c r="J41" s="119"/>
+      <c r="K41" s="119"/>
+      <c r="L41" s="119"/>
+      <c r="M41" s="120"/>
+      <c r="N41" s="121"/>
+      <c r="O41" s="122"/>
+      <c r="P41" s="123"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="124"/>
+      <c r="S41" s="124"/>
+    </row>
+    <row r="42" spans="1:19" ht="30" customHeight="1">
+      <c r="A42" s="46"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="117"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="118"/>
+      <c r="I42" s="119"/>
+      <c r="J42" s="119"/>
+      <c r="K42" s="119"/>
+      <c r="L42" s="119"/>
+      <c r="M42" s="120"/>
+      <c r="N42" s="121"/>
+      <c r="O42" s="122"/>
+      <c r="P42" s="123"/>
+      <c r="Q42" s="46"/>
+      <c r="R42" s="124"/>
+      <c r="S42" s="124"/>
+    </row>
+    <row r="43" spans="1:19" ht="30" customHeight="1">
+      <c r="A43" s="46"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="117"/>
+      <c r="G43" s="117"/>
+      <c r="H43" s="118"/>
+      <c r="I43" s="119"/>
+      <c r="J43" s="119"/>
+      <c r="K43" s="119"/>
+      <c r="L43" s="119"/>
+      <c r="M43" s="120"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="122"/>
+      <c r="P43" s="123"/>
+      <c r="Q43" s="46"/>
+      <c r="R43" s="124"/>
+      <c r="S43" s="124"/>
+    </row>
+    <row r="44" spans="1:19" ht="30" customHeight="1">
+      <c r="A44" s="46"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="117"/>
+      <c r="F44" s="117"/>
+      <c r="G44" s="117"/>
+      <c r="H44" s="118"/>
+      <c r="I44" s="119"/>
+      <c r="J44" s="119"/>
+      <c r="K44" s="119"/>
+      <c r="L44" s="119"/>
+      <c r="M44" s="120"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="122"/>
+      <c r="P44" s="123"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="124"/>
+      <c r="S44" s="124"/>
+    </row>
+    <row r="45" spans="1:19" ht="30" customHeight="1">
+      <c r="A45" s="46"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="117"/>
+      <c r="D45" s="117"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="117"/>
+      <c r="G45" s="117"/>
+      <c r="H45" s="118"/>
+      <c r="I45" s="119"/>
+      <c r="J45" s="119"/>
+      <c r="K45" s="119"/>
+      <c r="L45" s="119"/>
+      <c r="M45" s="120"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="122"/>
+      <c r="P45" s="123"/>
+      <c r="Q45" s="46"/>
+      <c r="R45" s="124"/>
+      <c r="S45" s="124"/>
+    </row>
+    <row r="46" spans="1:19" ht="30" customHeight="1">
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="117"/>
+      <c r="D46" s="117"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="117"/>
+      <c r="H46" s="118"/>
+      <c r="I46" s="119"/>
+      <c r="J46" s="119"/>
+      <c r="K46" s="119"/>
+      <c r="L46" s="119"/>
+      <c r="M46" s="120"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="122"/>
+      <c r="P46" s="123"/>
+      <c r="Q46" s="46"/>
+      <c r="R46" s="124"/>
+      <c r="S46" s="124"/>
+    </row>
+    <row r="47" spans="1:19" ht="30" customHeight="1">
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="118"/>
+      <c r="I47" s="119"/>
+      <c r="J47" s="119"/>
+      <c r="K47" s="119"/>
+      <c r="L47" s="119"/>
+      <c r="M47" s="120"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="122"/>
+      <c r="P47" s="123"/>
+      <c r="Q47" s="46"/>
+      <c r="R47" s="124"/>
+      <c r="S47" s="124"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="A48" s="46"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="117"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="117"/>
+      <c r="F48" s="117"/>
+      <c r="G48" s="117"/>
+      <c r="H48" s="118"/>
+      <c r="I48" s="119"/>
+      <c r="J48" s="119"/>
+      <c r="K48" s="119"/>
+      <c r="L48" s="119"/>
+      <c r="M48" s="120"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="123"/>
+      <c r="Q48" s="46"/>
+      <c r="R48" s="124"/>
+      <c r="S48" s="124"/>
+    </row>
+    <row r="49" spans="1:19" ht="30" customHeight="1">
+      <c r="A49" s="46"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="117"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="118"/>
+      <c r="I49" s="119"/>
+      <c r="J49" s="119"/>
+      <c r="K49" s="119"/>
+      <c r="L49" s="119"/>
+      <c r="M49" s="120"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="122"/>
+      <c r="P49" s="123"/>
+      <c r="Q49" s="46"/>
+      <c r="R49" s="124"/>
+      <c r="S49" s="124"/>
+    </row>
+    <row r="50" spans="1:19" ht="30" customHeight="1">
+      <c r="A50" s="46"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="117"/>
+      <c r="D50" s="117"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="117"/>
+      <c r="G50" s="117"/>
+      <c r="H50" s="118"/>
+      <c r="I50" s="119"/>
+      <c r="J50" s="119"/>
+      <c r="K50" s="119"/>
+      <c r="L50" s="119"/>
+      <c r="M50" s="120"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="122"/>
+      <c r="P50" s="123"/>
+      <c r="Q50" s="46"/>
+      <c r="R50" s="124"/>
+      <c r="S50" s="124"/>
+    </row>
+    <row r="51" spans="1:19" ht="30" customHeight="1">
+      <c r="A51" s="46"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="117"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="117"/>
+      <c r="H51" s="118"/>
+      <c r="I51" s="119"/>
+      <c r="J51" s="119"/>
+      <c r="K51" s="119"/>
+      <c r="L51" s="119"/>
+      <c r="M51" s="120"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="122"/>
+      <c r="P51" s="123"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="124"/>
+      <c r="S51" s="124"/>
+    </row>
+    <row r="52" spans="1:19" ht="30" customHeight="1">
+      <c r="A52" s="46"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="117"/>
+      <c r="D52" s="117"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="117"/>
+      <c r="G52" s="117"/>
+      <c r="H52" s="118"/>
+      <c r="I52" s="119"/>
+      <c r="J52" s="119"/>
+      <c r="K52" s="119"/>
+      <c r="L52" s="119"/>
+      <c r="M52" s="120"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="122"/>
+      <c r="P52" s="123"/>
+      <c r="Q52" s="46"/>
+      <c r="R52" s="124"/>
+      <c r="S52" s="124"/>
+    </row>
+  </sheetData>
+  <mergeCells count="204">
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
 </file>
--- a/Documents/ログイン機能設計書.xlsx
+++ b/Documents/ログイン機能設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6A85DF-C388-4565-9EA7-2446D0AB92E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6CEBB7-D967-41E4-B62B-11643CFBE345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="3" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
@@ -1772,6 +1772,45 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="9" fillId="0" borderId="62" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1787,6 +1826,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1817,83 +1901,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1913,20 +1931,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1940,39 +1975,82 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1980,84 +2058,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="9" fillId="0" borderId="62" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2572,151 +2572,25 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>85724</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="正方形/長方形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFA39583-2D21-919C-1E8A-A07E37F09D67}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="57149" y="2209800"/>
-          <a:ext cx="3286125" cy="3009900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>942975</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7176C0E8-2493-5929-FADB-5F804514970D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3486150" y="1000125"/>
-          <a:ext cx="5172075" cy="3076575"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>125999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>47062</xdr:rowOff>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>36173</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B772A5BB-4E77-4C0D-1A63-9BD136AD0460}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8A6C65D-3B13-87FC-B9C9-F18F4CC871E0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2725,7 +2599,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2738,362 +2612,14 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5000625" y="2821574"/>
-          <a:ext cx="3314700" cy="1216463"/>
+          <a:off x="295275" y="1466850"/>
+          <a:ext cx="7772400" cy="3207998"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="コネクタ: カギ線 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FB6F42D-A920-6C89-3CAE-D1E692422A1C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2190750" y="1609725"/>
-          <a:ext cx="1647825" cy="1285875"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>781052</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="18" name="コネクタ: カギ線 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF0AFD51-B806-7AD3-8E07-CF6F0593BDA8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000" flipV="1">
-          <a:off x="5476876" y="2028824"/>
-          <a:ext cx="857250" cy="723902"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>336120</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>80495</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7694D2A7-66F2-9078-B2C3-90C2D0CC28BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3838575" y="1171575"/>
-          <a:ext cx="3098370" cy="794870"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>992695</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>26264</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="図 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D891357-21EF-7BB1-8D25-0531282C01B9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="180975" y="2657475"/>
-          <a:ext cx="2954845" cy="2331314"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>857250</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="テキスト ボックス 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D539B3B3-0C9F-9929-810B-4E63822172A6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8029575" y="1028700"/>
-          <a:ext cx="542925" cy="295275"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
-            <a:t>dao</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>333374</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="テキスト ボックス 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B229873D-BE38-4D3E-AB56-03A7AA09EF83}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1362074" y="2247900"/>
-          <a:ext cx="647701" cy="295275"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
-            <a:t>entity</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3406,19 +2932,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="85" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="85" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="73"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
@@ -3430,190 +2956,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
+      <c r="G2" s="79"/>
+      <c r="H2" s="82">
         <v>45806</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="74" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="75"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="62"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="53" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="54"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53" t="s">
+      <c r="B8" s="64"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="54"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="64" t="s">
+      <c r="C9" s="65"/>
+      <c r="D9" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="54"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="67"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="61"/>
-      <c r="B10" s="63" t="s">
+      <c r="A10" s="89"/>
+      <c r="B10" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="54"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63" t="s">
+      <c r="A11" s="90"/>
+      <c r="B11" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="64" t="s">
+      <c r="C11" s="65"/>
+      <c r="D11" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="54"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="53" t="s">
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="54"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="59"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="87"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4604,18 +4130,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -4631,6 +4145,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4653,19 +4179,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="85" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="85" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="73"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -4677,190 +4203,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
+      <c r="G2" s="79"/>
+      <c r="H2" s="82">
         <v>45806</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="69"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="101" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="75"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="62"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="93"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="95"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="79"/>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="96"/>
+      <c r="A8" s="71"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="102"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="79"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="96"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="102"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="79"/>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="96"/>
+      <c r="A10" s="71"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="102"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="96"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="102"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="79"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="96"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="102"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="79"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="96"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="102"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="97" t="s">
+      <c r="A14" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="54"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="97" t="s">
+      <c r="A15" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53" t="s">
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="6" t="s">
         <v>6</v>
       </c>
@@ -4869,11 +4395,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="97" t="s">
+      <c r="A16" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="6" t="s">
         <v>4</v>
       </c>
@@ -4886,18 +4412,18 @@
       <c r="G16" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H16" s="98" t="s">
+      <c r="H16" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="54"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="100">
+      <c r="A17" s="95">
         <v>1</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="5" t="s">
         <v>32</v>
       </c>
@@ -4910,18 +4436,18 @@
       <c r="G17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="54"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="67"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="100">
+      <c r="A18" s="95">
         <v>2</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="65"/>
       <c r="D18" s="5" t="s">
         <v>33</v>
       </c>
@@ -4934,18 +4460,18 @@
       <c r="G18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="53" t="s">
+      <c r="H18" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="54"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="100">
+      <c r="A19" s="95">
         <v>3</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
       <c r="D19" s="5" t="s">
         <v>34</v>
       </c>
@@ -4958,16 +4484,16 @@
       <c r="G19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="53"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="54"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="67"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="100">
+      <c r="A20" s="95">
         <v>4</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="52"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65"/>
       <c r="D20" s="5" t="s">
         <v>35</v>
       </c>
@@ -4978,45 +4504,45 @@
       <c r="G20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="54"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="52"/>
+      <c r="A21" s="95"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="54"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="100"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="52"/>
+      <c r="A22" s="95"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="65"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="54"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="99"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="57"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="59"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="87"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5997,6 +5523,21 @@
     <row r="1000" s="1" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
@@ -6013,21 +5554,6 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -6048,19 +5574,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="85" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="85" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="73"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -6072,48 +5598,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
-        <v>45806</v>
-      </c>
-      <c r="I2" s="65" t="s">
+      <c r="G2" s="79"/>
+      <c r="H2" s="82">
+        <v>45810</v>
+      </c>
+      <c r="I2" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="11"/>
@@ -7464,190 +6990,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="85" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="85" t="s">
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="85" t="s">
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="85" t="s">
+      <c r="P1" s="60"/>
+      <c r="Q1" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="73"/>
-      <c r="S1" s="85" t="s">
+      <c r="R1" s="60"/>
+      <c r="S1" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="75"/>
+      <c r="T1" s="62"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="86" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="86" t="s">
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="116">
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="105">
         <v>45810</v>
       </c>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="86" t="s">
+      <c r="P2" s="79"/>
+      <c r="Q2" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="87"/>
-      <c r="S2" s="86"/>
-      <c r="T2" s="95"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="101"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="96"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="102"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="84"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="89"/>
-      <c r="R4" s="84"/>
-      <c r="S4" s="89"/>
-      <c r="T4" s="115"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="104"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="74" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="72"/>
-      <c r="T5" s="75"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="62"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="53" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="54"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="67"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="97" t="s">
+      <c r="A7" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="53" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="54"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="67"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="11"/>
@@ -7846,37 +7372,37 @@
       <c r="T14" s="13"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="97" t="s">
+      <c r="A15" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="114" t="s">
+      <c r="B15" s="65"/>
+      <c r="C15" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="52"/>
-      <c r="E15" s="98" t="s">
+      <c r="D15" s="65"/>
+      <c r="E15" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="52"/>
-      <c r="G15" s="98" t="s">
+      <c r="F15" s="65"/>
+      <c r="G15" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="H15" s="51"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="98" t="s">
+      <c r="H15" s="64"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="K15" s="52"/>
-      <c r="L15" s="98" t="s">
+      <c r="K15" s="65"/>
+      <c r="L15" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="M15" s="51"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="98" t="s">
+      <c r="M15" s="64"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="52"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="65"/>
       <c r="R15" s="6" t="s">
         <v>73</v>
       </c>
@@ -7888,38 +7414,38 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="107">
+      <c r="A16" s="106">
         <v>1</v>
       </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="108" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="107" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="52"/>
-      <c r="E16" s="108" t="s">
+      <c r="D16" s="65"/>
+      <c r="E16" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="109" t="s">
+      <c r="F16" s="65"/>
+      <c r="G16" s="108" t="s">
         <v>112</v>
       </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="109" t="s">
+      <c r="H16" s="64"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="108" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="52"/>
-      <c r="L16" s="112" t="s">
+      <c r="K16" s="65"/>
+      <c r="L16" s="109" t="s">
         <v>95</v>
       </c>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="106" t="s">
+      <c r="M16" s="110"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="111" t="s">
         <v>79</v>
       </c>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="52"/>
-      <c r="R16" s="146">
+      <c r="P16" s="64"/>
+      <c r="Q16" s="65"/>
+      <c r="R16" s="51">
         <v>45810</v>
       </c>
       <c r="S16" s="31" t="s">
@@ -7936,38 +7462,38 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="75" customHeight="1">
-      <c r="A17" s="107">
+      <c r="A17" s="106">
         <v>2</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="108" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="107" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="52"/>
-      <c r="E17" s="108" t="s">
+      <c r="D17" s="65"/>
+      <c r="E17" s="107" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="52"/>
-      <c r="G17" s="109" t="s">
+      <c r="F17" s="65"/>
+      <c r="G17" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="H17" s="51"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="109" t="s">
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="K17" s="52"/>
-      <c r="L17" s="106" t="s">
+      <c r="K17" s="65"/>
+      <c r="L17" s="111" t="s">
         <v>96</v>
       </c>
-      <c r="M17" s="110"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="106" t="s">
+      <c r="M17" s="113"/>
+      <c r="N17" s="114"/>
+      <c r="O17" s="111" t="s">
         <v>94</v>
       </c>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="146">
+      <c r="P17" s="64"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="51">
         <v>45810</v>
       </c>
       <c r="S17" s="31" t="s">
@@ -7984,38 +7510,38 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="79.5" customHeight="1">
-      <c r="A18" s="107">
+      <c r="A18" s="106">
         <v>3</v>
       </c>
-      <c r="B18" s="52"/>
-      <c r="C18" s="108" t="s">
+      <c r="B18" s="65"/>
+      <c r="C18" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="52"/>
-      <c r="E18" s="108" t="s">
+      <c r="D18" s="65"/>
+      <c r="E18" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="52"/>
-      <c r="G18" s="109" t="s">
+      <c r="F18" s="65"/>
+      <c r="G18" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="51"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="109" t="s">
+      <c r="H18" s="64"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="K18" s="52"/>
-      <c r="L18" s="106" t="s">
+      <c r="K18" s="65"/>
+      <c r="L18" s="111" t="s">
         <v>83</v>
       </c>
-      <c r="M18" s="51"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="106" t="s">
+      <c r="M18" s="64"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="111" t="s">
         <v>122</v>
       </c>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="52"/>
-      <c r="R18" s="146">
+      <c r="P18" s="64"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="51">
         <v>45810</v>
       </c>
       <c r="S18" s="31" t="s">
@@ -8032,38 +7558,38 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="42.75" customHeight="1">
-      <c r="A19" s="107">
+      <c r="A19" s="106">
         <v>4</v>
       </c>
-      <c r="B19" s="52"/>
-      <c r="C19" s="108" t="s">
+      <c r="B19" s="65"/>
+      <c r="C19" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="52"/>
-      <c r="E19" s="108" t="s">
+      <c r="D19" s="65"/>
+      <c r="E19" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="52"/>
-      <c r="G19" s="109" t="s">
+      <c r="F19" s="65"/>
+      <c r="G19" s="108" t="s">
         <v>91</v>
       </c>
-      <c r="H19" s="51"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="109" t="s">
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="108" t="s">
         <v>92</v>
       </c>
-      <c r="K19" s="52"/>
-      <c r="L19" s="106" t="s">
+      <c r="K19" s="65"/>
+      <c r="L19" s="111" t="s">
         <v>83</v>
       </c>
-      <c r="M19" s="51"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="106" t="s">
+      <c r="M19" s="64"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="111" t="s">
         <v>93</v>
       </c>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="52"/>
-      <c r="R19" s="146">
+      <c r="P19" s="64"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="51">
         <v>45810</v>
       </c>
       <c r="S19" s="31" t="s">
@@ -8080,23 +7606,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="107"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="109"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="52"/>
+      <c r="A20" s="106"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="65"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -8108,23 +7634,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="107"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="52"/>
+      <c r="A21" s="106"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="65"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -8136,23 +7662,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="107"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="52"/>
-      <c r="O22" s="106"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="52"/>
+      <c r="A22" s="106"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="111"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="65"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -8164,23 +7690,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="107"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="109"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="109"/>
-      <c r="K23" s="52"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="52"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="52"/>
+      <c r="A23" s="106"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="108"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="111"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="65"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -8192,23 +7718,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="107"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="108"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="109"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="52"/>
-      <c r="O24" s="106"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="52"/>
+      <c r="A24" s="106"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="108"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="65"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -8220,23 +7746,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="107"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="52"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="52"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="52"/>
+      <c r="A25" s="106"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="108"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="64"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -8248,23 +7774,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="107"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="108"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="109"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="109"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="52"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="52"/>
+      <c r="A26" s="106"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="108"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="111"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="65"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -8276,23 +7802,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="107"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="109"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="52"/>
-      <c r="O27" s="106"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="52"/>
+      <c r="A27" s="106"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="108"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="111"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -8304,23 +7830,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="107"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="109"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="109"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="52"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="52"/>
+      <c r="A28" s="106"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="108"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="111"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="65"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -8332,23 +7858,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="107"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="109"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="109"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="106"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="52"/>
+      <c r="A29" s="106"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="107"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="111"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="65"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -8360,23 +7886,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="107"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="109"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="109"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="52"/>
-      <c r="O30" s="106"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="52"/>
+      <c r="A30" s="106"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="107"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="111"/>
+      <c r="P30" s="64"/>
+      <c r="Q30" s="65"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -8388,23 +7914,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="103"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="104"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="105"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="102"/>
-      <c r="M31" s="56"/>
-      <c r="N31" s="57"/>
-      <c r="O31" s="102"/>
-      <c r="P31" s="56"/>
-      <c r="Q31" s="57"/>
+      <c r="A31" s="116"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="118"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="115"/>
+      <c r="P31" s="84"/>
+      <c r="Q31" s="85"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -9402,121 +8928,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -9538,6 +8949,121 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -9563,72 +9089,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="128" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="135" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="138" t="s">
+      <c r="D1" s="130"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="132" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="140"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="134"/>
       <c r="N1" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="138" t="s">
+      <c r="O1" s="132" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="140"/>
+      <c r="P1" s="134"/>
       <c r="Q1" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="R1" s="138" t="s">
+      <c r="R1" s="132" t="s">
         <v>100</v>
       </c>
-      <c r="S1" s="140"/>
+      <c r="S1" s="134"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="134"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135" t="s">
+      <c r="A2" s="128"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="129" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="136"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="138" t="s">
+      <c r="D2" s="130"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="132" t="s">
         <v>114</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="139"/>
-      <c r="L2" s="139"/>
-      <c r="M2" s="140"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="134"/>
       <c r="N2" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="141">
+      <c r="O2" s="135">
         <v>45807</v>
       </c>
-      <c r="P2" s="142"/>
+      <c r="P2" s="136"/>
       <c r="Q2" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="R2" s="143" t="s">
+      <c r="R2" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="144"/>
+      <c r="S2" s="138"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="40"/>
@@ -9658,33 +9184,33 @@
       <c r="B4" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="129" t="s">
+      <c r="C4" s="119" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="129" t="s">
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="119" t="s">
         <v>111</v>
       </c>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="129" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="O4" s="130"/>
-      <c r="P4" s="131"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="121"/>
       <c r="Q4" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="R4" s="129" t="s">
+      <c r="R4" s="119" t="s">
         <v>108</v>
       </c>
-      <c r="S4" s="131"/>
+      <c r="S4" s="121"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="44">
@@ -9693,31 +9219,31 @@
       <c r="B5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="125" t="s">
+      <c r="C5" s="122" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="125" t="s">
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="125"/>
-      <c r="M5" s="125"/>
-      <c r="N5" s="126" t="s">
+      <c r="I5" s="122"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
+      <c r="M5" s="122"/>
+      <c r="N5" s="123" t="s">
         <v>117</v>
       </c>
-      <c r="O5" s="127"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="145">
+      <c r="O5" s="124"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="50">
         <v>45810</v>
       </c>
-      <c r="R5" s="132"/>
-      <c r="S5" s="133"/>
+      <c r="R5" s="126"/>
+      <c r="S5" s="127"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="46">
@@ -9726,1001 +9252,1188 @@
       <c r="B6" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="125" t="s">
+      <c r="C6" s="122" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="125"/>
-      <c r="E6" s="125"/>
-      <c r="F6" s="125"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="125" t="s">
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122" t="s">
         <v>115</v>
       </c>
-      <c r="I6" s="125"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="125"/>
-      <c r="L6" s="125"/>
-      <c r="M6" s="125"/>
-      <c r="N6" s="126" t="s">
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="123" t="s">
         <v>121</v>
       </c>
-      <c r="O6" s="127"/>
-      <c r="P6" s="128"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="125"/>
       <c r="Q6" s="47">
         <v>45810</v>
       </c>
-      <c r="R6" s="124"/>
-      <c r="S6" s="124"/>
+      <c r="R6" s="139"/>
+      <c r="S6" s="139"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="46">
         <v>3</v>
       </c>
       <c r="B7" s="45"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="125"/>
-      <c r="L7" s="125"/>
-      <c r="M7" s="125"/>
-      <c r="N7" s="126"/>
-      <c r="O7" s="127"/>
-      <c r="P7" s="128"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
+      <c r="N7" s="123"/>
+      <c r="O7" s="124"/>
+      <c r="P7" s="125"/>
       <c r="Q7" s="47"/>
-      <c r="R7" s="124"/>
-      <c r="S7" s="124"/>
+      <c r="R7" s="139"/>
+      <c r="S7" s="139"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="46">
         <v>4</v>
       </c>
       <c r="B8" s="46"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="125"/>
-      <c r="L8" s="125"/>
-      <c r="M8" s="125"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="122"/>
+      <c r="H8" s="122"/>
+      <c r="I8" s="122"/>
+      <c r="J8" s="122"/>
+      <c r="K8" s="122"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
       <c r="Q8" s="47"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="124"/>
+      <c r="R8" s="139"/>
+      <c r="S8" s="139"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="46"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="117"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="122"/>
-      <c r="P9" s="123"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="140"/>
+      <c r="L9" s="140"/>
+      <c r="M9" s="140"/>
+      <c r="N9" s="141"/>
+      <c r="O9" s="142"/>
+      <c r="P9" s="143"/>
       <c r="Q9" s="46"/>
-      <c r="R9" s="124"/>
-      <c r="S9" s="124"/>
+      <c r="R9" s="139"/>
+      <c r="S9" s="139"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="117"/>
-      <c r="F10" s="117"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="118"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="121"/>
-      <c r="O10" s="122"/>
-      <c r="P10" s="123"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="145"/>
+      <c r="K10" s="145"/>
+      <c r="L10" s="145"/>
+      <c r="M10" s="146"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="142"/>
+      <c r="P10" s="143"/>
       <c r="Q10" s="47"/>
-      <c r="R10" s="124"/>
-      <c r="S10" s="124"/>
+      <c r="R10" s="139"/>
+      <c r="S10" s="139"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="46"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="117"/>
-      <c r="G11" s="117"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="119"/>
-      <c r="L11" s="119"/>
-      <c r="M11" s="120"/>
-      <c r="N11" s="121"/>
-      <c r="O11" s="122"/>
-      <c r="P11" s="123"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="141"/>
+      <c r="O11" s="142"/>
+      <c r="P11" s="143"/>
       <c r="Q11" s="46"/>
-      <c r="R11" s="124"/>
-      <c r="S11" s="124"/>
+      <c r="R11" s="139"/>
+      <c r="S11" s="139"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="46"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="119"/>
-      <c r="L12" s="119"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="122"/>
-      <c r="P12" s="123"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="145"/>
+      <c r="K12" s="145"/>
+      <c r="L12" s="145"/>
+      <c r="M12" s="146"/>
+      <c r="N12" s="141"/>
+      <c r="O12" s="142"/>
+      <c r="P12" s="143"/>
       <c r="Q12" s="46"/>
-      <c r="R12" s="124"/>
-      <c r="S12" s="124"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="139"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="46"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="119"/>
-      <c r="J13" s="119"/>
-      <c r="K13" s="119"/>
-      <c r="L13" s="119"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="122"/>
-      <c r="P13" s="123"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="145"/>
+      <c r="L13" s="145"/>
+      <c r="M13" s="146"/>
+      <c r="N13" s="141"/>
+      <c r="O13" s="142"/>
+      <c r="P13" s="143"/>
       <c r="Q13" s="46"/>
-      <c r="R13" s="124"/>
-      <c r="S13" s="124"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="119"/>
-      <c r="K14" s="119"/>
-      <c r="L14" s="119"/>
-      <c r="M14" s="120"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="122"/>
-      <c r="P14" s="123"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="145"/>
+      <c r="J14" s="145"/>
+      <c r="K14" s="145"/>
+      <c r="L14" s="145"/>
+      <c r="M14" s="146"/>
+      <c r="N14" s="141"/>
+      <c r="O14" s="142"/>
+      <c r="P14" s="143"/>
       <c r="Q14" s="46"/>
-      <c r="R14" s="124"/>
-      <c r="S14" s="124"/>
+      <c r="R14" s="139"/>
+      <c r="S14" s="139"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="46"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="119"/>
-      <c r="K15" s="119"/>
-      <c r="L15" s="119"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="122"/>
-      <c r="P15" s="123"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="145"/>
+      <c r="J15" s="145"/>
+      <c r="K15" s="145"/>
+      <c r="L15" s="145"/>
+      <c r="M15" s="146"/>
+      <c r="N15" s="141"/>
+      <c r="O15" s="142"/>
+      <c r="P15" s="143"/>
       <c r="Q15" s="46"/>
-      <c r="R15" s="124"/>
-      <c r="S15" s="124"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="46"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="119"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="121"/>
-      <c r="O16" s="122"/>
-      <c r="P16" s="123"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="145"/>
+      <c r="K16" s="145"/>
+      <c r="L16" s="145"/>
+      <c r="M16" s="146"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="142"/>
+      <c r="P16" s="143"/>
       <c r="Q16" s="46"/>
-      <c r="R16" s="124"/>
-      <c r="S16" s="124"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="139"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="46"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="119"/>
-      <c r="K17" s="119"/>
-      <c r="L17" s="119"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="122"/>
-      <c r="P17" s="123"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="140"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="145"/>
+      <c r="K17" s="145"/>
+      <c r="L17" s="145"/>
+      <c r="M17" s="146"/>
+      <c r="N17" s="141"/>
+      <c r="O17" s="142"/>
+      <c r="P17" s="143"/>
       <c r="Q17" s="46"/>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
+      <c r="R17" s="139"/>
+      <c r="S17" s="139"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="46"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="119"/>
-      <c r="J18" s="119"/>
-      <c r="K18" s="119"/>
-      <c r="L18" s="119"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="122"/>
-      <c r="P18" s="123"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="140"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="140"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="144"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="146"/>
+      <c r="N18" s="141"/>
+      <c r="O18" s="142"/>
+      <c r="P18" s="143"/>
       <c r="Q18" s="46"/>
-      <c r="R18" s="124"/>
-      <c r="S18" s="124"/>
+      <c r="R18" s="139"/>
+      <c r="S18" s="139"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="46"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="119"/>
-      <c r="M19" s="120"/>
-      <c r="N19" s="121"/>
-      <c r="O19" s="122"/>
-      <c r="P19" s="123"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="140"/>
+      <c r="F19" s="140"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="144"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="146"/>
+      <c r="N19" s="141"/>
+      <c r="O19" s="142"/>
+      <c r="P19" s="143"/>
       <c r="Q19" s="46"/>
-      <c r="R19" s="124"/>
-      <c r="S19" s="124"/>
+      <c r="R19" s="139"/>
+      <c r="S19" s="139"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="46"/>
       <c r="B20" s="46"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="117"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="119"/>
-      <c r="J20" s="119"/>
-      <c r="K20" s="119"/>
-      <c r="L20" s="119"/>
-      <c r="M20" s="120"/>
-      <c r="N20" s="121"/>
-      <c r="O20" s="122"/>
-      <c r="P20" s="123"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="144"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="146"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="142"/>
+      <c r="P20" s="143"/>
       <c r="Q20" s="46"/>
-      <c r="R20" s="124"/>
-      <c r="S20" s="124"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="139"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="46"/>
       <c r="B21" s="46"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="117"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="118"/>
-      <c r="I21" s="119"/>
-      <c r="J21" s="119"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="119"/>
-      <c r="M21" s="120"/>
-      <c r="N21" s="121"/>
-      <c r="O21" s="122"/>
-      <c r="P21" s="123"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="145"/>
+      <c r="L21" s="145"/>
+      <c r="M21" s="146"/>
+      <c r="N21" s="141"/>
+      <c r="O21" s="142"/>
+      <c r="P21" s="143"/>
       <c r="Q21" s="46"/>
-      <c r="R21" s="124"/>
-      <c r="S21" s="124"/>
+      <c r="R21" s="139"/>
+      <c r="S21" s="139"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="46"/>
       <c r="B22" s="46"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="117"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="119"/>
-      <c r="J22" s="119"/>
-      <c r="K22" s="119"/>
-      <c r="L22" s="119"/>
-      <c r="M22" s="120"/>
-      <c r="N22" s="121"/>
-      <c r="O22" s="122"/>
-      <c r="P22" s="123"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="140"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="145"/>
+      <c r="J22" s="145"/>
+      <c r="K22" s="145"/>
+      <c r="L22" s="145"/>
+      <c r="M22" s="146"/>
+      <c r="N22" s="141"/>
+      <c r="O22" s="142"/>
+      <c r="P22" s="143"/>
       <c r="Q22" s="46"/>
-      <c r="R22" s="124"/>
-      <c r="S22" s="124"/>
+      <c r="R22" s="139"/>
+      <c r="S22" s="139"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="46"/>
       <c r="B23" s="46"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="119"/>
-      <c r="M23" s="120"/>
-      <c r="N23" s="121"/>
-      <c r="O23" s="122"/>
-      <c r="P23" s="123"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="140"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="145"/>
+      <c r="J23" s="145"/>
+      <c r="K23" s="145"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="141"/>
+      <c r="O23" s="142"/>
+      <c r="P23" s="143"/>
       <c r="Q23" s="46"/>
-      <c r="R23" s="124"/>
-      <c r="S23" s="124"/>
+      <c r="R23" s="139"/>
+      <c r="S23" s="139"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="46"/>
       <c r="B24" s="46"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="118"/>
-      <c r="I24" s="119"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="119"/>
-      <c r="L24" s="119"/>
-      <c r="M24" s="120"/>
-      <c r="N24" s="121"/>
-      <c r="O24" s="122"/>
-      <c r="P24" s="123"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="145"/>
+      <c r="J24" s="145"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="145"/>
+      <c r="M24" s="146"/>
+      <c r="N24" s="141"/>
+      <c r="O24" s="142"/>
+      <c r="P24" s="143"/>
       <c r="Q24" s="46"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="46"/>
       <c r="B25" s="46"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="119"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="119"/>
-      <c r="L25" s="119"/>
-      <c r="M25" s="120"/>
-      <c r="N25" s="121"/>
-      <c r="O25" s="122"/>
-      <c r="P25" s="123"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="144"/>
+      <c r="I25" s="145"/>
+      <c r="J25" s="145"/>
+      <c r="K25" s="145"/>
+      <c r="L25" s="145"/>
+      <c r="M25" s="146"/>
+      <c r="N25" s="141"/>
+      <c r="O25" s="142"/>
+      <c r="P25" s="143"/>
       <c r="Q25" s="46"/>
-      <c r="R25" s="124"/>
-      <c r="S25" s="124"/>
+      <c r="R25" s="139"/>
+      <c r="S25" s="139"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="46"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="119"/>
-      <c r="J26" s="119"/>
-      <c r="K26" s="119"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="120"/>
-      <c r="N26" s="121"/>
-      <c r="O26" s="122"/>
-      <c r="P26" s="123"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="144"/>
+      <c r="I26" s="145"/>
+      <c r="J26" s="145"/>
+      <c r="K26" s="145"/>
+      <c r="L26" s="145"/>
+      <c r="M26" s="146"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="142"/>
+      <c r="P26" s="143"/>
       <c r="Q26" s="46"/>
-      <c r="R26" s="124"/>
-      <c r="S26" s="124"/>
+      <c r="R26" s="139"/>
+      <c r="S26" s="139"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="46"/>
       <c r="B27" s="46"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="118"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="119"/>
-      <c r="L27" s="119"/>
-      <c r="M27" s="120"/>
-      <c r="N27" s="121"/>
-      <c r="O27" s="122"/>
-      <c r="P27" s="123"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="144"/>
+      <c r="I27" s="145"/>
+      <c r="J27" s="145"/>
+      <c r="K27" s="145"/>
+      <c r="L27" s="145"/>
+      <c r="M27" s="146"/>
+      <c r="N27" s="141"/>
+      <c r="O27" s="142"/>
+      <c r="P27" s="143"/>
       <c r="Q27" s="46"/>
-      <c r="R27" s="124"/>
-      <c r="S27" s="124"/>
+      <c r="R27" s="139"/>
+      <c r="S27" s="139"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="46"/>
       <c r="B28" s="46"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="119"/>
-      <c r="J28" s="119"/>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="120"/>
-      <c r="N28" s="121"/>
-      <c r="O28" s="122"/>
-      <c r="P28" s="123"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="144"/>
+      <c r="I28" s="145"/>
+      <c r="J28" s="145"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="146"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="142"/>
+      <c r="P28" s="143"/>
       <c r="Q28" s="46"/>
-      <c r="R28" s="124"/>
-      <c r="S28" s="124"/>
+      <c r="R28" s="139"/>
+      <c r="S28" s="139"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="46"/>
       <c r="B29" s="46"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="117"/>
-      <c r="G29" s="117"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="119"/>
-      <c r="K29" s="119"/>
-      <c r="L29" s="119"/>
-      <c r="M29" s="120"/>
-      <c r="N29" s="121"/>
-      <c r="O29" s="122"/>
-      <c r="P29" s="123"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="144"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="145"/>
+      <c r="K29" s="145"/>
+      <c r="L29" s="145"/>
+      <c r="M29" s="146"/>
+      <c r="N29" s="141"/>
+      <c r="O29" s="142"/>
+      <c r="P29" s="143"/>
       <c r="Q29" s="46"/>
-      <c r="R29" s="124"/>
-      <c r="S29" s="124"/>
+      <c r="R29" s="139"/>
+      <c r="S29" s="139"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="46"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="119"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="119"/>
-      <c r="L30" s="119"/>
-      <c r="M30" s="120"/>
-      <c r="N30" s="121"/>
-      <c r="O30" s="122"/>
-      <c r="P30" s="123"/>
+      <c r="C30" s="140"/>
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="144"/>
+      <c r="I30" s="145"/>
+      <c r="J30" s="145"/>
+      <c r="K30" s="145"/>
+      <c r="L30" s="145"/>
+      <c r="M30" s="146"/>
+      <c r="N30" s="141"/>
+      <c r="O30" s="142"/>
+      <c r="P30" s="143"/>
       <c r="Q30" s="46"/>
-      <c r="R30" s="124"/>
-      <c r="S30" s="124"/>
+      <c r="R30" s="139"/>
+      <c r="S30" s="139"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="119"/>
-      <c r="J31" s="119"/>
-      <c r="K31" s="119"/>
-      <c r="L31" s="119"/>
-      <c r="M31" s="120"/>
-      <c r="N31" s="121"/>
-      <c r="O31" s="122"/>
-      <c r="P31" s="123"/>
+      <c r="C31" s="140"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="144"/>
+      <c r="I31" s="145"/>
+      <c r="J31" s="145"/>
+      <c r="K31" s="145"/>
+      <c r="L31" s="145"/>
+      <c r="M31" s="146"/>
+      <c r="N31" s="141"/>
+      <c r="O31" s="142"/>
+      <c r="P31" s="143"/>
       <c r="Q31" s="46"/>
-      <c r="R31" s="124"/>
-      <c r="S31" s="124"/>
+      <c r="R31" s="139"/>
+      <c r="S31" s="139"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="119"/>
-      <c r="J32" s="119"/>
-      <c r="K32" s="119"/>
-      <c r="L32" s="119"/>
-      <c r="M32" s="120"/>
-      <c r="N32" s="121"/>
-      <c r="O32" s="122"/>
-      <c r="P32" s="123"/>
+      <c r="C32" s="140"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="140"/>
+      <c r="G32" s="140"/>
+      <c r="H32" s="144"/>
+      <c r="I32" s="145"/>
+      <c r="J32" s="145"/>
+      <c r="K32" s="145"/>
+      <c r="L32" s="145"/>
+      <c r="M32" s="146"/>
+      <c r="N32" s="141"/>
+      <c r="O32" s="142"/>
+      <c r="P32" s="143"/>
       <c r="Q32" s="46"/>
-      <c r="R32" s="124"/>
-      <c r="S32" s="124"/>
+      <c r="R32" s="139"/>
+      <c r="S32" s="139"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="46"/>
       <c r="B33" s="46"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="117"/>
-      <c r="F33" s="117"/>
-      <c r="G33" s="117"/>
-      <c r="H33" s="118"/>
-      <c r="I33" s="119"/>
-      <c r="J33" s="119"/>
-      <c r="K33" s="119"/>
-      <c r="L33" s="119"/>
-      <c r="M33" s="120"/>
-      <c r="N33" s="121"/>
-      <c r="O33" s="122"/>
-      <c r="P33" s="123"/>
+      <c r="C33" s="140"/>
+      <c r="D33" s="140"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="140"/>
+      <c r="G33" s="140"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="145"/>
+      <c r="J33" s="145"/>
+      <c r="K33" s="145"/>
+      <c r="L33" s="145"/>
+      <c r="M33" s="146"/>
+      <c r="N33" s="141"/>
+      <c r="O33" s="142"/>
+      <c r="P33" s="143"/>
       <c r="Q33" s="46"/>
-      <c r="R33" s="124"/>
-      <c r="S33" s="124"/>
+      <c r="R33" s="139"/>
+      <c r="S33" s="139"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="46"/>
       <c r="B34" s="46"/>
-      <c r="C34" s="117"/>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="117"/>
-      <c r="H34" s="118"/>
-      <c r="I34" s="119"/>
-      <c r="J34" s="119"/>
-      <c r="K34" s="119"/>
-      <c r="L34" s="119"/>
-      <c r="M34" s="120"/>
-      <c r="N34" s="121"/>
-      <c r="O34" s="122"/>
-      <c r="P34" s="123"/>
+      <c r="C34" s="140"/>
+      <c r="D34" s="140"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="140"/>
+      <c r="H34" s="144"/>
+      <c r="I34" s="145"/>
+      <c r="J34" s="145"/>
+      <c r="K34" s="145"/>
+      <c r="L34" s="145"/>
+      <c r="M34" s="146"/>
+      <c r="N34" s="141"/>
+      <c r="O34" s="142"/>
+      <c r="P34" s="143"/>
       <c r="Q34" s="46"/>
-      <c r="R34" s="124"/>
-      <c r="S34" s="124"/>
+      <c r="R34" s="139"/>
+      <c r="S34" s="139"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
-      <c r="C35" s="117"/>
-      <c r="D35" s="117"/>
-      <c r="E35" s="117"/>
-      <c r="F35" s="117"/>
-      <c r="G35" s="117"/>
-      <c r="H35" s="118"/>
-      <c r="I35" s="119"/>
-      <c r="J35" s="119"/>
-      <c r="K35" s="119"/>
-      <c r="L35" s="119"/>
-      <c r="M35" s="120"/>
-      <c r="N35" s="121"/>
-      <c r="O35" s="122"/>
-      <c r="P35" s="123"/>
+      <c r="C35" s="140"/>
+      <c r="D35" s="140"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="140"/>
+      <c r="G35" s="140"/>
+      <c r="H35" s="144"/>
+      <c r="I35" s="145"/>
+      <c r="J35" s="145"/>
+      <c r="K35" s="145"/>
+      <c r="L35" s="145"/>
+      <c r="M35" s="146"/>
+      <c r="N35" s="141"/>
+      <c r="O35" s="142"/>
+      <c r="P35" s="143"/>
       <c r="Q35" s="46"/>
-      <c r="R35" s="124"/>
-      <c r="S35" s="124"/>
+      <c r="R35" s="139"/>
+      <c r="S35" s="139"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="46"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="117"/>
-      <c r="F36" s="117"/>
-      <c r="G36" s="117"/>
-      <c r="H36" s="118"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="119"/>
-      <c r="K36" s="119"/>
-      <c r="L36" s="119"/>
-      <c r="M36" s="120"/>
-      <c r="N36" s="121"/>
-      <c r="O36" s="122"/>
-      <c r="P36" s="123"/>
+      <c r="C36" s="140"/>
+      <c r="D36" s="140"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="140"/>
+      <c r="G36" s="140"/>
+      <c r="H36" s="144"/>
+      <c r="I36" s="145"/>
+      <c r="J36" s="145"/>
+      <c r="K36" s="145"/>
+      <c r="L36" s="145"/>
+      <c r="M36" s="146"/>
+      <c r="N36" s="141"/>
+      <c r="O36" s="142"/>
+      <c r="P36" s="143"/>
       <c r="Q36" s="46"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
+      <c r="R36" s="139"/>
+      <c r="S36" s="139"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="46"/>
       <c r="B37" s="46"/>
-      <c r="C37" s="117"/>
-      <c r="D37" s="117"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="118"/>
-      <c r="I37" s="119"/>
-      <c r="J37" s="119"/>
-      <c r="K37" s="119"/>
-      <c r="L37" s="119"/>
-      <c r="M37" s="120"/>
-      <c r="N37" s="121"/>
-      <c r="O37" s="122"/>
-      <c r="P37" s="123"/>
+      <c r="C37" s="140"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="144"/>
+      <c r="I37" s="145"/>
+      <c r="J37" s="145"/>
+      <c r="K37" s="145"/>
+      <c r="L37" s="145"/>
+      <c r="M37" s="146"/>
+      <c r="N37" s="141"/>
+      <c r="O37" s="142"/>
+      <c r="P37" s="143"/>
       <c r="Q37" s="46"/>
-      <c r="R37" s="124"/>
-      <c r="S37" s="124"/>
+      <c r="R37" s="139"/>
+      <c r="S37" s="139"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="46"/>
       <c r="B38" s="46"/>
-      <c r="C38" s="117"/>
-      <c r="D38" s="117"/>
-      <c r="E38" s="117"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="117"/>
-      <c r="H38" s="118"/>
-      <c r="I38" s="119"/>
-      <c r="J38" s="119"/>
-      <c r="K38" s="119"/>
-      <c r="L38" s="119"/>
-      <c r="M38" s="120"/>
-      <c r="N38" s="121"/>
-      <c r="O38" s="122"/>
-      <c r="P38" s="123"/>
+      <c r="C38" s="140"/>
+      <c r="D38" s="140"/>
+      <c r="E38" s="140"/>
+      <c r="F38" s="140"/>
+      <c r="G38" s="140"/>
+      <c r="H38" s="144"/>
+      <c r="I38" s="145"/>
+      <c r="J38" s="145"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="145"/>
+      <c r="M38" s="146"/>
+      <c r="N38" s="141"/>
+      <c r="O38" s="142"/>
+      <c r="P38" s="143"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="124"/>
-      <c r="S38" s="124"/>
+      <c r="R38" s="139"/>
+      <c r="S38" s="139"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="46"/>
       <c r="B39" s="46"/>
-      <c r="C39" s="117"/>
-      <c r="D39" s="117"/>
-      <c r="E39" s="117"/>
-      <c r="F39" s="117"/>
-      <c r="G39" s="117"/>
-      <c r="H39" s="118"/>
-      <c r="I39" s="119"/>
-      <c r="J39" s="119"/>
-      <c r="K39" s="119"/>
-      <c r="L39" s="119"/>
-      <c r="M39" s="120"/>
-      <c r="N39" s="121"/>
-      <c r="O39" s="122"/>
-      <c r="P39" s="123"/>
+      <c r="C39" s="140"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="144"/>
+      <c r="I39" s="145"/>
+      <c r="J39" s="145"/>
+      <c r="K39" s="145"/>
+      <c r="L39" s="145"/>
+      <c r="M39" s="146"/>
+      <c r="N39" s="141"/>
+      <c r="O39" s="142"/>
+      <c r="P39" s="143"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="124"/>
-      <c r="S39" s="124"/>
+      <c r="R39" s="139"/>
+      <c r="S39" s="139"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="117"/>
-      <c r="D40" s="117"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="117"/>
-      <c r="G40" s="117"/>
-      <c r="H40" s="118"/>
-      <c r="I40" s="119"/>
-      <c r="J40" s="119"/>
-      <c r="K40" s="119"/>
-      <c r="L40" s="119"/>
-      <c r="M40" s="120"/>
-      <c r="N40" s="121"/>
-      <c r="O40" s="122"/>
-      <c r="P40" s="123"/>
+      <c r="C40" s="140"/>
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="144"/>
+      <c r="I40" s="145"/>
+      <c r="J40" s="145"/>
+      <c r="K40" s="145"/>
+      <c r="L40" s="145"/>
+      <c r="M40" s="146"/>
+      <c r="N40" s="141"/>
+      <c r="O40" s="142"/>
+      <c r="P40" s="143"/>
       <c r="Q40" s="46"/>
-      <c r="R40" s="124"/>
-      <c r="S40" s="124"/>
+      <c r="R40" s="139"/>
+      <c r="S40" s="139"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="46"/>
       <c r="B41" s="46"/>
-      <c r="C41" s="117"/>
-      <c r="D41" s="117"/>
-      <c r="E41" s="117"/>
-      <c r="F41" s="117"/>
-      <c r="G41" s="117"/>
-      <c r="H41" s="118"/>
-      <c r="I41" s="119"/>
-      <c r="J41" s="119"/>
-      <c r="K41" s="119"/>
-      <c r="L41" s="119"/>
-      <c r="M41" s="120"/>
-      <c r="N41" s="121"/>
-      <c r="O41" s="122"/>
-      <c r="P41" s="123"/>
+      <c r="C41" s="140"/>
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="144"/>
+      <c r="I41" s="145"/>
+      <c r="J41" s="145"/>
+      <c r="K41" s="145"/>
+      <c r="L41" s="145"/>
+      <c r="M41" s="146"/>
+      <c r="N41" s="141"/>
+      <c r="O41" s="142"/>
+      <c r="P41" s="143"/>
       <c r="Q41" s="46"/>
-      <c r="R41" s="124"/>
-      <c r="S41" s="124"/>
+      <c r="R41" s="139"/>
+      <c r="S41" s="139"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="46"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="117"/>
-      <c r="D42" s="117"/>
-      <c r="E42" s="117"/>
-      <c r="F42" s="117"/>
-      <c r="G42" s="117"/>
-      <c r="H42" s="118"/>
-      <c r="I42" s="119"/>
-      <c r="J42" s="119"/>
-      <c r="K42" s="119"/>
-      <c r="L42" s="119"/>
-      <c r="M42" s="120"/>
-      <c r="N42" s="121"/>
-      <c r="O42" s="122"/>
-      <c r="P42" s="123"/>
+      <c r="C42" s="140"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="144"/>
+      <c r="I42" s="145"/>
+      <c r="J42" s="145"/>
+      <c r="K42" s="145"/>
+      <c r="L42" s="145"/>
+      <c r="M42" s="146"/>
+      <c r="N42" s="141"/>
+      <c r="O42" s="142"/>
+      <c r="P42" s="143"/>
       <c r="Q42" s="46"/>
-      <c r="R42" s="124"/>
-      <c r="S42" s="124"/>
+      <c r="R42" s="139"/>
+      <c r="S42" s="139"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="46"/>
       <c r="B43" s="46"/>
-      <c r="C43" s="117"/>
-      <c r="D43" s="117"/>
-      <c r="E43" s="117"/>
-      <c r="F43" s="117"/>
-      <c r="G43" s="117"/>
-      <c r="H43" s="118"/>
-      <c r="I43" s="119"/>
-      <c r="J43" s="119"/>
-      <c r="K43" s="119"/>
-      <c r="L43" s="119"/>
-      <c r="M43" s="120"/>
-      <c r="N43" s="121"/>
-      <c r="O43" s="122"/>
-      <c r="P43" s="123"/>
+      <c r="C43" s="140"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="144"/>
+      <c r="I43" s="145"/>
+      <c r="J43" s="145"/>
+      <c r="K43" s="145"/>
+      <c r="L43" s="145"/>
+      <c r="M43" s="146"/>
+      <c r="N43" s="141"/>
+      <c r="O43" s="142"/>
+      <c r="P43" s="143"/>
       <c r="Q43" s="46"/>
-      <c r="R43" s="124"/>
-      <c r="S43" s="124"/>
+      <c r="R43" s="139"/>
+      <c r="S43" s="139"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="46"/>
       <c r="B44" s="46"/>
-      <c r="C44" s="117"/>
-      <c r="D44" s="117"/>
-      <c r="E44" s="117"/>
-      <c r="F44" s="117"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="118"/>
-      <c r="I44" s="119"/>
-      <c r="J44" s="119"/>
-      <c r="K44" s="119"/>
-      <c r="L44" s="119"/>
-      <c r="M44" s="120"/>
-      <c r="N44" s="121"/>
-      <c r="O44" s="122"/>
-      <c r="P44" s="123"/>
+      <c r="C44" s="140"/>
+      <c r="D44" s="140"/>
+      <c r="E44" s="140"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="140"/>
+      <c r="H44" s="144"/>
+      <c r="I44" s="145"/>
+      <c r="J44" s="145"/>
+      <c r="K44" s="145"/>
+      <c r="L44" s="145"/>
+      <c r="M44" s="146"/>
+      <c r="N44" s="141"/>
+      <c r="O44" s="142"/>
+      <c r="P44" s="143"/>
       <c r="Q44" s="46"/>
-      <c r="R44" s="124"/>
-      <c r="S44" s="124"/>
+      <c r="R44" s="139"/>
+      <c r="S44" s="139"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="46"/>
       <c r="B45" s="46"/>
-      <c r="C45" s="117"/>
-      <c r="D45" s="117"/>
-      <c r="E45" s="117"/>
-      <c r="F45" s="117"/>
-      <c r="G45" s="117"/>
-      <c r="H45" s="118"/>
-      <c r="I45" s="119"/>
-      <c r="J45" s="119"/>
-      <c r="K45" s="119"/>
-      <c r="L45" s="119"/>
-      <c r="M45" s="120"/>
-      <c r="N45" s="121"/>
-      <c r="O45" s="122"/>
-      <c r="P45" s="123"/>
+      <c r="C45" s="140"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="144"/>
+      <c r="I45" s="145"/>
+      <c r="J45" s="145"/>
+      <c r="K45" s="145"/>
+      <c r="L45" s="145"/>
+      <c r="M45" s="146"/>
+      <c r="N45" s="141"/>
+      <c r="O45" s="142"/>
+      <c r="P45" s="143"/>
       <c r="Q45" s="46"/>
-      <c r="R45" s="124"/>
-      <c r="S45" s="124"/>
+      <c r="R45" s="139"/>
+      <c r="S45" s="139"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="46"/>
       <c r="B46" s="46"/>
-      <c r="C46" s="117"/>
-      <c r="D46" s="117"/>
-      <c r="E46" s="117"/>
-      <c r="F46" s="117"/>
-      <c r="G46" s="117"/>
-      <c r="H46" s="118"/>
-      <c r="I46" s="119"/>
-      <c r="J46" s="119"/>
-      <c r="K46" s="119"/>
-      <c r="L46" s="119"/>
-      <c r="M46" s="120"/>
-      <c r="N46" s="121"/>
-      <c r="O46" s="122"/>
-      <c r="P46" s="123"/>
+      <c r="C46" s="140"/>
+      <c r="D46" s="140"/>
+      <c r="E46" s="140"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="144"/>
+      <c r="I46" s="145"/>
+      <c r="J46" s="145"/>
+      <c r="K46" s="145"/>
+      <c r="L46" s="145"/>
+      <c r="M46" s="146"/>
+      <c r="N46" s="141"/>
+      <c r="O46" s="142"/>
+      <c r="P46" s="143"/>
       <c r="Q46" s="46"/>
-      <c r="R46" s="124"/>
-      <c r="S46" s="124"/>
+      <c r="R46" s="139"/>
+      <c r="S46" s="139"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="46"/>
       <c r="B47" s="46"/>
-      <c r="C47" s="117"/>
-      <c r="D47" s="117"/>
-      <c r="E47" s="117"/>
-      <c r="F47" s="117"/>
-      <c r="G47" s="117"/>
-      <c r="H47" s="118"/>
-      <c r="I47" s="119"/>
-      <c r="J47" s="119"/>
-      <c r="K47" s="119"/>
-      <c r="L47" s="119"/>
-      <c r="M47" s="120"/>
-      <c r="N47" s="121"/>
-      <c r="O47" s="122"/>
-      <c r="P47" s="123"/>
+      <c r="C47" s="140"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="144"/>
+      <c r="I47" s="145"/>
+      <c r="J47" s="145"/>
+      <c r="K47" s="145"/>
+      <c r="L47" s="145"/>
+      <c r="M47" s="146"/>
+      <c r="N47" s="141"/>
+      <c r="O47" s="142"/>
+      <c r="P47" s="143"/>
       <c r="Q47" s="46"/>
-      <c r="R47" s="124"/>
-      <c r="S47" s="124"/>
+      <c r="R47" s="139"/>
+      <c r="S47" s="139"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="46"/>
       <c r="B48" s="46"/>
-      <c r="C48" s="117"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="117"/>
-      <c r="F48" s="117"/>
-      <c r="G48" s="117"/>
-      <c r="H48" s="118"/>
-      <c r="I48" s="119"/>
-      <c r="J48" s="119"/>
-      <c r="K48" s="119"/>
-      <c r="L48" s="119"/>
-      <c r="M48" s="120"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="122"/>
-      <c r="P48" s="123"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="144"/>
+      <c r="I48" s="145"/>
+      <c r="J48" s="145"/>
+      <c r="K48" s="145"/>
+      <c r="L48" s="145"/>
+      <c r="M48" s="146"/>
+      <c r="N48" s="141"/>
+      <c r="O48" s="142"/>
+      <c r="P48" s="143"/>
       <c r="Q48" s="46"/>
-      <c r="R48" s="124"/>
-      <c r="S48" s="124"/>
+      <c r="R48" s="139"/>
+      <c r="S48" s="139"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="46"/>
       <c r="B49" s="46"/>
-      <c r="C49" s="117"/>
-      <c r="D49" s="117"/>
-      <c r="E49" s="117"/>
-      <c r="F49" s="117"/>
-      <c r="G49" s="117"/>
-      <c r="H49" s="118"/>
-      <c r="I49" s="119"/>
-      <c r="J49" s="119"/>
-      <c r="K49" s="119"/>
-      <c r="L49" s="119"/>
-      <c r="M49" s="120"/>
-      <c r="N49" s="121"/>
-      <c r="O49" s="122"/>
-      <c r="P49" s="123"/>
+      <c r="C49" s="140"/>
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="144"/>
+      <c r="I49" s="145"/>
+      <c r="J49" s="145"/>
+      <c r="K49" s="145"/>
+      <c r="L49" s="145"/>
+      <c r="M49" s="146"/>
+      <c r="N49" s="141"/>
+      <c r="O49" s="142"/>
+      <c r="P49" s="143"/>
       <c r="Q49" s="46"/>
-      <c r="R49" s="124"/>
-      <c r="S49" s="124"/>
+      <c r="R49" s="139"/>
+      <c r="S49" s="139"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="46"/>
       <c r="B50" s="46"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="117"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="117"/>
-      <c r="H50" s="118"/>
-      <c r="I50" s="119"/>
-      <c r="J50" s="119"/>
-      <c r="K50" s="119"/>
-      <c r="L50" s="119"/>
-      <c r="M50" s="120"/>
-      <c r="N50" s="121"/>
-      <c r="O50" s="122"/>
-      <c r="P50" s="123"/>
+      <c r="C50" s="140"/>
+      <c r="D50" s="140"/>
+      <c r="E50" s="140"/>
+      <c r="F50" s="140"/>
+      <c r="G50" s="140"/>
+      <c r="H50" s="144"/>
+      <c r="I50" s="145"/>
+      <c r="J50" s="145"/>
+      <c r="K50" s="145"/>
+      <c r="L50" s="145"/>
+      <c r="M50" s="146"/>
+      <c r="N50" s="141"/>
+      <c r="O50" s="142"/>
+      <c r="P50" s="143"/>
       <c r="Q50" s="46"/>
-      <c r="R50" s="124"/>
-      <c r="S50" s="124"/>
+      <c r="R50" s="139"/>
+      <c r="S50" s="139"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="46"/>
       <c r="B51" s="46"/>
-      <c r="C51" s="117"/>
-      <c r="D51" s="117"/>
-      <c r="E51" s="117"/>
-      <c r="F51" s="117"/>
-      <c r="G51" s="117"/>
-      <c r="H51" s="118"/>
-      <c r="I51" s="119"/>
-      <c r="J51" s="119"/>
-      <c r="K51" s="119"/>
-      <c r="L51" s="119"/>
-      <c r="M51" s="120"/>
-      <c r="N51" s="121"/>
-      <c r="O51" s="122"/>
-      <c r="P51" s="123"/>
+      <c r="C51" s="140"/>
+      <c r="D51" s="140"/>
+      <c r="E51" s="140"/>
+      <c r="F51" s="140"/>
+      <c r="G51" s="140"/>
+      <c r="H51" s="144"/>
+      <c r="I51" s="145"/>
+      <c r="J51" s="145"/>
+      <c r="K51" s="145"/>
+      <c r="L51" s="145"/>
+      <c r="M51" s="146"/>
+      <c r="N51" s="141"/>
+      <c r="O51" s="142"/>
+      <c r="P51" s="143"/>
       <c r="Q51" s="46"/>
-      <c r="R51" s="124"/>
-      <c r="S51" s="124"/>
+      <c r="R51" s="139"/>
+      <c r="S51" s="139"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="46"/>
       <c r="B52" s="46"/>
-      <c r="C52" s="117"/>
-      <c r="D52" s="117"/>
-      <c r="E52" s="117"/>
-      <c r="F52" s="117"/>
-      <c r="G52" s="117"/>
-      <c r="H52" s="118"/>
-      <c r="I52" s="119"/>
-      <c r="J52" s="119"/>
-      <c r="K52" s="119"/>
-      <c r="L52" s="119"/>
-      <c r="M52" s="120"/>
-      <c r="N52" s="121"/>
-      <c r="O52" s="122"/>
-      <c r="P52" s="123"/>
+      <c r="C52" s="140"/>
+      <c r="D52" s="140"/>
+      <c r="E52" s="140"/>
+      <c r="F52" s="140"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="144"/>
+      <c r="I52" s="145"/>
+      <c r="J52" s="145"/>
+      <c r="K52" s="145"/>
+      <c r="L52" s="145"/>
+      <c r="M52" s="146"/>
+      <c r="N52" s="141"/>
+      <c r="O52" s="142"/>
+      <c r="P52" s="143"/>
       <c r="Q52" s="46"/>
-      <c r="R52" s="124"/>
-      <c r="S52" s="124"/>
+      <c r="R52" s="139"/>
+      <c r="S52" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="204">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -10738,193 +10451,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/ログイン機能設計書.xlsx
+++ b/Documents/ログイン機能設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6CEBB7-D967-41E4-B62B-11643CFBE345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C269AB6-EC0E-4935-94DB-78752331D20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
@@ -239,72 +239,19 @@
     <t>事前条件</t>
   </si>
   <si>
-    <t>ユーザIDとパスワードが事前に登録されていること、ログイン画面が表示されていること</t>
-    <rPh sb="12" eb="14">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>イベントフロー</t>
   </si>
   <si>
     <t>基本フロー</t>
   </si>
   <si>
-    <t>①ユーザー：ログイン画面でユーザID、パスワードを入力し、入力が終わったらログインボタンを押下する
-②システム：ログインュー処理をしメニュー画面へ遷移する</t>
-    <rPh sb="62" eb="64">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>代替フロー</t>
   </si>
   <si>
     <t>例外フロー</t>
   </si>
   <si>
-    <t>①ログイン失敗画面へ遷移する</t>
-    <rPh sb="5" eb="7">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>事後条件</t>
-  </si>
-  <si>
-    <t>メニュー画面が表示される</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>テスト仕様書兼
@@ -673,6 +620,111 @@
 ログイン画面へ戻るリンクが表示される</t>
     <rPh sb="33" eb="35">
       <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時はメニュー画面が表示される、失敗時はログイン失敗画面が表示される</t>
+    <rPh sb="0" eb="3">
+      <t>セイコウジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>シッパイジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①ID、パスワードがデータベース上に存在していない、入力がされていない場合、もしくは最大文字数が超えている場合はログイン失敗画面へ遷移する</t>
+    <rPh sb="16" eb="17">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="42" eb="47">
+      <t>サイダイモジスウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①http://localhost:8080/taskUN/login.jsp　でログイン画面を表示させる
+②ユーザー：ログイン画面でユーザID、パスワードを入力し、入力が終わったらログインボタンを押下する
+②システム：入力されたID、パスワードがデータベース上に存在していればメニュー画面へ遷移する</t>
+    <rPh sb="45" eb="47">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="130" eb="131">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未ログイン状態であること、ユーザIDとパスワードが事前にデータベース上に登録されていること</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1778,6 +1830,51 @@
     <xf numFmtId="56" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,21 +1908,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1871,68 +1953,73 @@
     <xf numFmtId="56" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1940,40 +2027,41 @@
     <xf numFmtId="56" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1984,18 +2072,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2034,30 +2110,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2932,19 +2984,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="75"/>
       <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
@@ -2956,190 +3008,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="89"/>
+      <c r="F2" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="82">
+      <c r="G2" s="89"/>
+      <c r="H2" s="92">
         <v>45806</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="57"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="61" t="s">
+      <c r="B5" s="74"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="62"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="67"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="56"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="66" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="67"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="56"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="66" t="s">
+      <c r="B8" s="53"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="56"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="67"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="88" t="s">
+      <c r="B9" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="C9" s="54"/>
+      <c r="D9" s="66" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="56"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="63"/>
+      <c r="B10" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="92" t="s">
+      <c r="C10" s="54"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="56"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="64"/>
+      <c r="B11" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="67"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="89"/>
-      <c r="B10" s="91" t="s">
+      <c r="C11" s="54"/>
+      <c r="D11" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="56"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="67"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="67"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="67"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="87"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4130,6 +4182,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -4145,18 +4209,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4179,19 +4231,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="75"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -4203,190 +4255,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="89"/>
+      <c r="F2" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="82">
+      <c r="G2" s="89"/>
+      <c r="H2" s="92">
         <v>45806</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="56"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="96" t="s">
+      <c r="B5" s="74"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="62"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="56"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="101"/>
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="102"/>
+      <c r="A8" s="81"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="98"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="71"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="102"/>
+      <c r="A9" s="81"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="98"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="102"/>
+      <c r="A10" s="81"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="102"/>
+      <c r="A11" s="81"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="102"/>
+      <c r="A12" s="81"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="102"/>
+      <c r="A13" s="81"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="67"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="56"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="66" t="s">
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="54"/>
       <c r="I15" s="6" t="s">
         <v>6</v>
       </c>
@@ -4395,11 +4447,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="94" t="s">
+      <c r="A16" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="54"/>
       <c r="D16" s="6" t="s">
         <v>4</v>
       </c>
@@ -4412,18 +4464,18 @@
       <c r="G16" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H16" s="103" t="s">
+      <c r="H16" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="56"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="95">
+      <c r="A17" s="102">
         <v>1</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="5" t="s">
         <v>32</v>
       </c>
@@ -4436,18 +4488,18 @@
       <c r="G17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="66" t="s">
+      <c r="H17" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="67"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="56"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="95">
+      <c r="A18" s="102">
         <v>2</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="5" t="s">
         <v>33</v>
       </c>
@@ -4460,18 +4512,18 @@
       <c r="G18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="66" t="s">
+      <c r="H18" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="67"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="56"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="95">
+      <c r="A19" s="102">
         <v>3</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="5" t="s">
         <v>34</v>
       </c>
@@ -4484,16 +4536,16 @@
       <c r="G19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="66"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="67"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="56"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="95">
+      <c r="A20" s="102">
         <v>4</v>
       </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="5" t="s">
         <v>35</v>
       </c>
@@ -4504,45 +4556,45 @@
       <c r="G20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="66"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="67"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="56"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="95"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
+      <c r="A21" s="102"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="67"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="56"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="95"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
+      <c r="A22" s="102"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="67"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="56"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="93"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="87"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="61"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5523,21 +5575,6 @@
     <row r="1000" s="1" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
@@ -5554,6 +5591,21 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -5574,19 +5626,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="75"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -5598,48 +5650,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="89"/>
+      <c r="F2" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="82">
+      <c r="G2" s="89"/>
+      <c r="H2" s="92">
         <v>45810</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="57"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="11"/>
@@ -6990,190 +7042,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="78" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="87" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="87" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="75"/>
+      <c r="S1" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="77"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="88" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="88" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="118">
+        <v>45810</v>
+      </c>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="89"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="97"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="81"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="90"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="90"/>
+      <c r="T3" s="98"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="84"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="86"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="117"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="94" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="77"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="53"/>
+      <c r="P6" s="53"/>
+      <c r="Q6" s="53"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="56"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="77" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="60"/>
-      <c r="S1" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="T1" s="62"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="105">
-        <v>45810</v>
-      </c>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="79"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="101"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="102"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="81"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="81"/>
-      <c r="T4" s="104"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="61" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="59"/>
-      <c r="Q5" s="59"/>
-      <c r="R5" s="59"/>
-      <c r="S5" s="59"/>
-      <c r="T5" s="62"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="94" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="66" t="s">
-        <v>113</v>
-      </c>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="67"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="94" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="66" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="67"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="53"/>
+      <c r="S7" s="53"/>
+      <c r="T7" s="56"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="11"/>
@@ -7201,11 +7253,11 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="23"/>
@@ -7235,7 +7287,7 @@
       <c r="C10" s="25"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="26"/>
@@ -7265,7 +7317,7 @@
       <c r="C11" s="25"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="26"/>
@@ -7295,7 +7347,7 @@
       <c r="C12" s="25"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="26"/>
@@ -7325,7 +7377,7 @@
       <c r="C13" s="27"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" s="29"/>
@@ -7372,79 +7424,79 @@
       <c r="T14" s="13"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="99" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="54"/>
+      <c r="C15" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="54"/>
+      <c r="E15" s="100" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="54"/>
+      <c r="G15" s="100" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="53"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="K15" s="54"/>
+      <c r="L15" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="112" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="103" t="s">
+      <c r="M15" s="53"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="103" t="s">
+      <c r="P15" s="53"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="103" t="s">
+      <c r="S15" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="103" t="s">
+      <c r="T15" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="103" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="54.75" customHeight="1">
+      <c r="A16" s="109">
+        <v>1</v>
+      </c>
+      <c r="B16" s="54"/>
+      <c r="C16" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="6" t="s">
+      <c r="D16" s="54"/>
+      <c r="E16" s="110" t="s">
         <v>73</v>
       </c>
-      <c r="S15" s="6" t="s">
+      <c r="F16" s="54"/>
+      <c r="G16" s="111" t="s">
+        <v>108</v>
+      </c>
+      <c r="H16" s="53"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="T15" s="30" t="s">
+      <c r="K16" s="54"/>
+      <c r="L16" s="114" t="s">
+        <v>91</v>
+      </c>
+      <c r="M16" s="115"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="108" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="106">
-        <v>1</v>
-      </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="107" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="107" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="108" t="s">
-        <v>112</v>
-      </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="108" t="s">
-        <v>78</v>
-      </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="109" t="s">
-        <v>95</v>
-      </c>
-      <c r="M16" s="110"/>
-      <c r="N16" s="110"/>
-      <c r="O16" s="111" t="s">
-        <v>79</v>
-      </c>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="54"/>
       <c r="R16" s="51">
         <v>45810</v>
       </c>
@@ -7452,7 +7504,7 @@
         <v>20</v>
       </c>
       <c r="T16" s="32" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="U16" s="33"/>
       <c r="V16" s="33"/>
@@ -7462,37 +7514,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="75" customHeight="1">
-      <c r="A17" s="106">
+      <c r="A17" s="109">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="107" t="s">
+      <c r="B17" s="54"/>
+      <c r="C17" s="110" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="54"/>
+      <c r="E17" s="110" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="54"/>
+      <c r="G17" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="53"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="111" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="107" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="108" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="108" t="s">
-        <v>84</v>
-      </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="111" t="s">
-        <v>96</v>
-      </c>
-      <c r="M17" s="113"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="111" t="s">
-        <v>94</v>
-      </c>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="65"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="108" t="s">
+        <v>92</v>
+      </c>
+      <c r="M17" s="112"/>
+      <c r="N17" s="113"/>
+      <c r="O17" s="108" t="s">
+        <v>90</v>
+      </c>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="54"/>
       <c r="R17" s="51">
         <v>45810</v>
       </c>
@@ -7500,7 +7552,7 @@
         <v>20</v>
       </c>
       <c r="T17" s="32" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="U17" s="33"/>
       <c r="V17" s="33"/>
@@ -7510,37 +7562,37 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="79.5" customHeight="1">
-      <c r="A18" s="106">
+      <c r="A18" s="109">
         <v>3</v>
       </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="107" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="107" t="s">
-        <v>86</v>
-      </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="108" t="s">
-        <v>87</v>
-      </c>
-      <c r="H18" s="64"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="108" t="s">
-        <v>88</v>
-      </c>
-      <c r="K18" s="65"/>
-      <c r="L18" s="111" t="s">
+      <c r="B18" s="54"/>
+      <c r="C18" s="110" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="54"/>
+      <c r="E18" s="110" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="54"/>
+      <c r="G18" s="111" t="s">
         <v>83</v>
       </c>
-      <c r="M18" s="64"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="111" t="s">
-        <v>122</v>
-      </c>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="65"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="111" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="54"/>
+      <c r="L18" s="108" t="s">
+        <v>79</v>
+      </c>
+      <c r="M18" s="53"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="108" t="s">
+        <v>118</v>
+      </c>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="54"/>
       <c r="R18" s="51">
         <v>45810</v>
       </c>
@@ -7548,7 +7600,7 @@
         <v>20</v>
       </c>
       <c r="T18" s="32" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="U18" s="33"/>
       <c r="V18" s="33"/>
@@ -7558,37 +7610,37 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="42.75" customHeight="1">
-      <c r="A19" s="106">
+      <c r="A19" s="109">
         <v>4</v>
       </c>
-      <c r="B19" s="65"/>
-      <c r="C19" s="107" t="s">
+      <c r="B19" s="54"/>
+      <c r="C19" s="110" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="54"/>
+      <c r="E19" s="110" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="54"/>
+      <c r="G19" s="111" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="53"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="111" t="s">
+        <v>88</v>
+      </c>
+      <c r="K19" s="54"/>
+      <c r="L19" s="108" t="s">
+        <v>79</v>
+      </c>
+      <c r="M19" s="53"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="65"/>
-      <c r="E19" s="107" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="65"/>
-      <c r="G19" s="108" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="108" t="s">
-        <v>92</v>
-      </c>
-      <c r="K19" s="65"/>
-      <c r="L19" s="111" t="s">
-        <v>83</v>
-      </c>
-      <c r="M19" s="64"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="111" t="s">
-        <v>93</v>
-      </c>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="65"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="54"/>
       <c r="R19" s="51">
         <v>45810</v>
       </c>
@@ -7596,7 +7648,7 @@
         <v>20</v>
       </c>
       <c r="T19" s="32" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="U19" s="33"/>
       <c r="V19" s="33"/>
@@ -7606,23 +7658,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="106"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="108"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="109"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="108"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="54"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -7634,23 +7686,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="106"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="108"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="54"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -7662,23 +7714,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="106"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="107"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="108"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="108"/>
+      <c r="P22" s="53"/>
+      <c r="Q22" s="54"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -7690,23 +7742,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="106"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="108"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="109"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="108"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="108"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="54"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -7718,23 +7770,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="106"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="107"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="107"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="108"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="109"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="108"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="108"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="54"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -7746,23 +7798,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="106"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="107"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="108"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="109"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="108"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="108"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="54"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -7774,23 +7826,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="106"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="108"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="111"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="111"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="109"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="108"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="108"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="54"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -7802,23 +7854,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="106"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="107"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="111"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="109"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="108"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="108"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="54"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -7830,23 +7882,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="106"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="108"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="111"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="109"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="108"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="54"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -7858,23 +7910,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="106"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="107"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="107"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="109"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="53"/>
+      <c r="Q29" s="54"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -7886,23 +7938,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="106"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="107"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="107"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="111"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="109"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="53"/>
+      <c r="Q30" s="54"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -7914,23 +7966,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="116"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="84"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="115"/>
-      <c r="P31" s="84"/>
-      <c r="Q31" s="85"/>
+      <c r="A31" s="105"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="106"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="104"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="59"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -8928,6 +8980,121 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -8949,121 +9116,6 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -9089,72 +9141,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="129" t="s">
+      <c r="A1" s="136" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="137" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="138"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="O1" s="140" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="R1" s="140" t="s">
+        <v>96</v>
+      </c>
+      <c r="S1" s="142"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="136"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="137" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="130"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="132" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="37" t="s">
+      <c r="D2" s="138"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="140" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="142"/>
+      <c r="N2" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="132" t="s">
+      <c r="O2" s="143">
+        <v>45807</v>
+      </c>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="R2" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="R1" s="132" t="s">
-        <v>100</v>
-      </c>
-      <c r="S1" s="134"/>
-    </row>
-    <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="128"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="129" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" s="130"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="132" t="s">
-        <v>114</v>
-      </c>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="134"/>
-      <c r="N2" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="O2" s="135">
-        <v>45807</v>
-      </c>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="R2" s="137" t="s">
-        <v>20</v>
-      </c>
-      <c r="S2" s="138"/>
+      <c r="S2" s="146"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="40"/>
@@ -9179,1261 +9231,1074 @@
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
       <c r="A4" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="131" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="131" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="132"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="132"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="131" t="s">
+        <v>102</v>
+      </c>
+      <c r="O4" s="132"/>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="R4" s="131" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="119" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="119" t="s">
-        <v>111</v>
-      </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="119" t="s">
-        <v>106</v>
-      </c>
-      <c r="O4" s="120"/>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="R4" s="119" t="s">
-        <v>108</v>
-      </c>
-      <c r="S4" s="121"/>
+      <c r="S4" s="133"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="44">
         <v>1</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="122" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="127" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
-      <c r="K5" s="122"/>
-      <c r="L5" s="122"/>
-      <c r="M5" s="122"/>
-      <c r="N5" s="123" t="s">
-        <v>117</v>
-      </c>
-      <c r="O5" s="124"/>
-      <c r="P5" s="125"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
+      <c r="L5" s="127"/>
+      <c r="M5" s="127"/>
+      <c r="N5" s="128" t="s">
+        <v>113</v>
+      </c>
+      <c r="O5" s="129"/>
+      <c r="P5" s="130"/>
       <c r="Q5" s="50">
         <v>45810</v>
       </c>
-      <c r="R5" s="126"/>
-      <c r="S5" s="127"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="46">
         <v>2</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="122" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122" t="s">
-        <v>115</v>
-      </c>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="123" t="s">
-        <v>121</v>
-      </c>
-      <c r="O6" s="124"/>
-      <c r="P6" s="125"/>
+        <v>114</v>
+      </c>
+      <c r="C6" s="127" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="127" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="127"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="127"/>
+      <c r="M6" s="127"/>
+      <c r="N6" s="128" t="s">
+        <v>117</v>
+      </c>
+      <c r="O6" s="129"/>
+      <c r="P6" s="130"/>
       <c r="Q6" s="47">
         <v>45810</v>
       </c>
-      <c r="R6" s="139"/>
-      <c r="S6" s="139"/>
+      <c r="R6" s="126"/>
+      <c r="S6" s="126"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="46">
         <v>3</v>
       </c>
       <c r="B7" s="45"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="123"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="125"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="128"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="130"/>
       <c r="Q7" s="47"/>
-      <c r="R7" s="139"/>
-      <c r="S7" s="139"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="46">
         <v>4</v>
       </c>
       <c r="B8" s="46"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
-      <c r="H8" s="122"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="122"/>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="127"/>
+      <c r="K8" s="127"/>
+      <c r="L8" s="127"/>
+      <c r="M8" s="127"/>
       <c r="Q8" s="47"/>
-      <c r="R8" s="139"/>
-      <c r="S8" s="139"/>
+      <c r="R8" s="126"/>
+      <c r="S8" s="126"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="46"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="140"/>
-      <c r="E9" s="140"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="140"/>
-      <c r="L9" s="140"/>
-      <c r="M9" s="140"/>
-      <c r="N9" s="141"/>
-      <c r="O9" s="142"/>
-      <c r="P9" s="143"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="123"/>
+      <c r="O9" s="124"/>
+      <c r="P9" s="125"/>
       <c r="Q9" s="46"/>
-      <c r="R9" s="139"/>
-      <c r="S9" s="139"/>
+      <c r="R9" s="126"/>
+      <c r="S9" s="126"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="140"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="145"/>
-      <c r="J10" s="145"/>
-      <c r="K10" s="145"/>
-      <c r="L10" s="145"/>
-      <c r="M10" s="146"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="142"/>
-      <c r="P10" s="143"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="121"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="122"/>
+      <c r="N10" s="123"/>
+      <c r="O10" s="124"/>
+      <c r="P10" s="125"/>
       <c r="Q10" s="47"/>
-      <c r="R10" s="139"/>
-      <c r="S10" s="139"/>
+      <c r="R10" s="126"/>
+      <c r="S10" s="126"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="46"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="145"/>
-      <c r="K11" s="145"/>
-      <c r="L11" s="145"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="141"/>
-      <c r="O11" s="142"/>
-      <c r="P11" s="143"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="121"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="122"/>
+      <c r="N11" s="123"/>
+      <c r="O11" s="124"/>
+      <c r="P11" s="125"/>
       <c r="Q11" s="46"/>
-      <c r="R11" s="139"/>
-      <c r="S11" s="139"/>
+      <c r="R11" s="126"/>
+      <c r="S11" s="126"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="46"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="140"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="140"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="145"/>
-      <c r="J12" s="145"/>
-      <c r="K12" s="145"/>
-      <c r="L12" s="145"/>
-      <c r="M12" s="146"/>
-      <c r="N12" s="141"/>
-      <c r="O12" s="142"/>
-      <c r="P12" s="143"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="121"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="123"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="125"/>
       <c r="Q12" s="46"/>
-      <c r="R12" s="139"/>
-      <c r="S12" s="139"/>
+      <c r="R12" s="126"/>
+      <c r="S12" s="126"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="46"/>
-      <c r="C13" s="140"/>
-      <c r="D13" s="140"/>
-      <c r="E13" s="140"/>
-      <c r="F13" s="140"/>
-      <c r="G13" s="140"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="145"/>
-      <c r="J13" s="145"/>
-      <c r="K13" s="145"/>
-      <c r="L13" s="145"/>
-      <c r="M13" s="146"/>
-      <c r="N13" s="141"/>
-      <c r="O13" s="142"/>
-      <c r="P13" s="143"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="119"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="119"/>
+      <c r="H13" s="120"/>
+      <c r="I13" s="121"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="121"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="122"/>
+      <c r="N13" s="123"/>
+      <c r="O13" s="124"/>
+      <c r="P13" s="125"/>
       <c r="Q13" s="46"/>
-      <c r="R13" s="139"/>
-      <c r="S13" s="139"/>
+      <c r="R13" s="126"/>
+      <c r="S13" s="126"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="140"/>
-      <c r="D14" s="140"/>
-      <c r="E14" s="140"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="145"/>
-      <c r="J14" s="145"/>
-      <c r="K14" s="145"/>
-      <c r="L14" s="145"/>
-      <c r="M14" s="146"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="142"/>
-      <c r="P14" s="143"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="121"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="122"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="124"/>
+      <c r="P14" s="125"/>
       <c r="Q14" s="46"/>
-      <c r="R14" s="139"/>
-      <c r="S14" s="139"/>
+      <c r="R14" s="126"/>
+      <c r="S14" s="126"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="46"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="140"/>
-      <c r="F15" s="140"/>
-      <c r="G15" s="140"/>
-      <c r="H15" s="144"/>
-      <c r="I15" s="145"/>
-      <c r="J15" s="145"/>
-      <c r="K15" s="145"/>
-      <c r="L15" s="145"/>
-      <c r="M15" s="146"/>
-      <c r="N15" s="141"/>
-      <c r="O15" s="142"/>
-      <c r="P15" s="143"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="120"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="122"/>
+      <c r="N15" s="123"/>
+      <c r="O15" s="124"/>
+      <c r="P15" s="125"/>
       <c r="Q15" s="46"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
+      <c r="R15" s="126"/>
+      <c r="S15" s="126"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="46"/>
-      <c r="C16" s="140"/>
-      <c r="D16" s="140"/>
-      <c r="E16" s="140"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="145"/>
-      <c r="K16" s="145"/>
-      <c r="L16" s="145"/>
-      <c r="M16" s="146"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="142"/>
-      <c r="P16" s="143"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="121"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="121"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="122"/>
+      <c r="N16" s="123"/>
+      <c r="O16" s="124"/>
+      <c r="P16" s="125"/>
       <c r="Q16" s="46"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="139"/>
+      <c r="R16" s="126"/>
+      <c r="S16" s="126"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="46"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="140"/>
-      <c r="E17" s="140"/>
-      <c r="F17" s="140"/>
-      <c r="G17" s="140"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="145"/>
-      <c r="J17" s="145"/>
-      <c r="K17" s="145"/>
-      <c r="L17" s="145"/>
-      <c r="M17" s="146"/>
-      <c r="N17" s="141"/>
-      <c r="O17" s="142"/>
-      <c r="P17" s="143"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="124"/>
+      <c r="P17" s="125"/>
       <c r="Q17" s="46"/>
-      <c r="R17" s="139"/>
-      <c r="S17" s="139"/>
+      <c r="R17" s="126"/>
+      <c r="S17" s="126"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="46"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="140"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="140"/>
-      <c r="G18" s="140"/>
-      <c r="H18" s="144"/>
-      <c r="I18" s="145"/>
-      <c r="J18" s="145"/>
-      <c r="K18" s="145"/>
-      <c r="L18" s="145"/>
-      <c r="M18" s="146"/>
-      <c r="N18" s="141"/>
-      <c r="O18" s="142"/>
-      <c r="P18" s="143"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="121"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="125"/>
       <c r="Q18" s="46"/>
-      <c r="R18" s="139"/>
-      <c r="S18" s="139"/>
+      <c r="R18" s="126"/>
+      <c r="S18" s="126"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="46"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="140"/>
-      <c r="E19" s="140"/>
-      <c r="F19" s="140"/>
-      <c r="G19" s="140"/>
-      <c r="H19" s="144"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="146"/>
-      <c r="N19" s="141"/>
-      <c r="O19" s="142"/>
-      <c r="P19" s="143"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="121"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="122"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="124"/>
+      <c r="P19" s="125"/>
       <c r="Q19" s="46"/>
-      <c r="R19" s="139"/>
-      <c r="S19" s="139"/>
+      <c r="R19" s="126"/>
+      <c r="S19" s="126"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="46"/>
       <c r="B20" s="46"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="144"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="146"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="142"/>
-      <c r="P20" s="143"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="121"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="124"/>
+      <c r="P20" s="125"/>
       <c r="Q20" s="46"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="139"/>
+      <c r="R20" s="126"/>
+      <c r="S20" s="126"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="46"/>
       <c r="B21" s="46"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="140"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="145"/>
-      <c r="J21" s="145"/>
-      <c r="K21" s="145"/>
-      <c r="L21" s="145"/>
-      <c r="M21" s="146"/>
-      <c r="N21" s="141"/>
-      <c r="O21" s="142"/>
-      <c r="P21" s="143"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="121"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="122"/>
+      <c r="N21" s="123"/>
+      <c r="O21" s="124"/>
+      <c r="P21" s="125"/>
       <c r="Q21" s="46"/>
-      <c r="R21" s="139"/>
-      <c r="S21" s="139"/>
+      <c r="R21" s="126"/>
+      <c r="S21" s="126"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="46"/>
       <c r="B22" s="46"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="140"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="140"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="144"/>
-      <c r="I22" s="145"/>
-      <c r="J22" s="145"/>
-      <c r="K22" s="145"/>
-      <c r="L22" s="145"/>
-      <c r="M22" s="146"/>
-      <c r="N22" s="141"/>
-      <c r="O22" s="142"/>
-      <c r="P22" s="143"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="121"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="121"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="122"/>
+      <c r="N22" s="123"/>
+      <c r="O22" s="124"/>
+      <c r="P22" s="125"/>
       <c r="Q22" s="46"/>
-      <c r="R22" s="139"/>
-      <c r="S22" s="139"/>
+      <c r="R22" s="126"/>
+      <c r="S22" s="126"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="46"/>
       <c r="B23" s="46"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="140"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="140"/>
-      <c r="G23" s="140"/>
-      <c r="H23" s="144"/>
-      <c r="I23" s="145"/>
-      <c r="J23" s="145"/>
-      <c r="K23" s="145"/>
-      <c r="L23" s="145"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="141"/>
-      <c r="O23" s="142"/>
-      <c r="P23" s="143"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="121"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="122"/>
+      <c r="N23" s="123"/>
+      <c r="O23" s="124"/>
+      <c r="P23" s="125"/>
       <c r="Q23" s="46"/>
-      <c r="R23" s="139"/>
-      <c r="S23" s="139"/>
+      <c r="R23" s="126"/>
+      <c r="S23" s="126"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="46"/>
       <c r="B24" s="46"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="140"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="140"/>
-      <c r="G24" s="140"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="145"/>
-      <c r="J24" s="145"/>
-      <c r="K24" s="145"/>
-      <c r="L24" s="145"/>
-      <c r="M24" s="146"/>
-      <c r="N24" s="141"/>
-      <c r="O24" s="142"/>
-      <c r="P24" s="143"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="120"/>
+      <c r="I24" s="121"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="121"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="124"/>
+      <c r="P24" s="125"/>
       <c r="Q24" s="46"/>
-      <c r="R24" s="139"/>
-      <c r="S24" s="139"/>
+      <c r="R24" s="126"/>
+      <c r="S24" s="126"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="46"/>
       <c r="B25" s="46"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="144"/>
-      <c r="I25" s="145"/>
-      <c r="J25" s="145"/>
-      <c r="K25" s="145"/>
-      <c r="L25" s="145"/>
-      <c r="M25" s="146"/>
-      <c r="N25" s="141"/>
-      <c r="O25" s="142"/>
-      <c r="P25" s="143"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="120"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="122"/>
+      <c r="N25" s="123"/>
+      <c r="O25" s="124"/>
+      <c r="P25" s="125"/>
       <c r="Q25" s="46"/>
-      <c r="R25" s="139"/>
-      <c r="S25" s="139"/>
+      <c r="R25" s="126"/>
+      <c r="S25" s="126"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="46"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="144"/>
-      <c r="I26" s="145"/>
-      <c r="J26" s="145"/>
-      <c r="K26" s="145"/>
-      <c r="L26" s="145"/>
-      <c r="M26" s="146"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="142"/>
-      <c r="P26" s="143"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="121"/>
+      <c r="J26" s="121"/>
+      <c r="K26" s="121"/>
+      <c r="L26" s="121"/>
+      <c r="M26" s="122"/>
+      <c r="N26" s="123"/>
+      <c r="O26" s="124"/>
+      <c r="P26" s="125"/>
       <c r="Q26" s="46"/>
-      <c r="R26" s="139"/>
-      <c r="S26" s="139"/>
+      <c r="R26" s="126"/>
+      <c r="S26" s="126"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="46"/>
       <c r="B27" s="46"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="144"/>
-      <c r="I27" s="145"/>
-      <c r="J27" s="145"/>
-      <c r="K27" s="145"/>
-      <c r="L27" s="145"/>
-      <c r="M27" s="146"/>
-      <c r="N27" s="141"/>
-      <c r="O27" s="142"/>
-      <c r="P27" s="143"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="121"/>
+      <c r="J27" s="121"/>
+      <c r="K27" s="121"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="122"/>
+      <c r="N27" s="123"/>
+      <c r="O27" s="124"/>
+      <c r="P27" s="125"/>
       <c r="Q27" s="46"/>
-      <c r="R27" s="139"/>
-      <c r="S27" s="139"/>
+      <c r="R27" s="126"/>
+      <c r="S27" s="126"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="46"/>
       <c r="B28" s="46"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="144"/>
-      <c r="I28" s="145"/>
-      <c r="J28" s="145"/>
-      <c r="K28" s="145"/>
-      <c r="L28" s="145"/>
-      <c r="M28" s="146"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="142"/>
-      <c r="P28" s="143"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="121"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="121"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="122"/>
+      <c r="N28" s="123"/>
+      <c r="O28" s="124"/>
+      <c r="P28" s="125"/>
       <c r="Q28" s="46"/>
-      <c r="R28" s="139"/>
-      <c r="S28" s="139"/>
+      <c r="R28" s="126"/>
+      <c r="S28" s="126"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="46"/>
       <c r="B29" s="46"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="140"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="140"/>
-      <c r="H29" s="144"/>
-      <c r="I29" s="145"/>
-      <c r="J29" s="145"/>
-      <c r="K29" s="145"/>
-      <c r="L29" s="145"/>
-      <c r="M29" s="146"/>
-      <c r="N29" s="141"/>
-      <c r="O29" s="142"/>
-      <c r="P29" s="143"/>
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="121"/>
+      <c r="J29" s="121"/>
+      <c r="K29" s="121"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="122"/>
+      <c r="N29" s="123"/>
+      <c r="O29" s="124"/>
+      <c r="P29" s="125"/>
       <c r="Q29" s="46"/>
-      <c r="R29" s="139"/>
-      <c r="S29" s="139"/>
+      <c r="R29" s="126"/>
+      <c r="S29" s="126"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="46"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="140"/>
-      <c r="H30" s="144"/>
-      <c r="I30" s="145"/>
-      <c r="J30" s="145"/>
-      <c r="K30" s="145"/>
-      <c r="L30" s="145"/>
-      <c r="M30" s="146"/>
-      <c r="N30" s="141"/>
-      <c r="O30" s="142"/>
-      <c r="P30" s="143"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="120"/>
+      <c r="I30" s="121"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="121"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="122"/>
+      <c r="N30" s="123"/>
+      <c r="O30" s="124"/>
+      <c r="P30" s="125"/>
       <c r="Q30" s="46"/>
-      <c r="R30" s="139"/>
-      <c r="S30" s="139"/>
+      <c r="R30" s="126"/>
+      <c r="S30" s="126"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="144"/>
-      <c r="I31" s="145"/>
-      <c r="J31" s="145"/>
-      <c r="K31" s="145"/>
-      <c r="L31" s="145"/>
-      <c r="M31" s="146"/>
-      <c r="N31" s="141"/>
-      <c r="O31" s="142"/>
-      <c r="P31" s="143"/>
+      <c r="C31" s="119"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="119"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="121"/>
+      <c r="J31" s="121"/>
+      <c r="K31" s="121"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="122"/>
+      <c r="N31" s="123"/>
+      <c r="O31" s="124"/>
+      <c r="P31" s="125"/>
       <c r="Q31" s="46"/>
-      <c r="R31" s="139"/>
-      <c r="S31" s="139"/>
+      <c r="R31" s="126"/>
+      <c r="S31" s="126"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="140"/>
-      <c r="G32" s="140"/>
-      <c r="H32" s="144"/>
-      <c r="I32" s="145"/>
-      <c r="J32" s="145"/>
-      <c r="K32" s="145"/>
-      <c r="L32" s="145"/>
-      <c r="M32" s="146"/>
-      <c r="N32" s="141"/>
-      <c r="O32" s="142"/>
-      <c r="P32" s="143"/>
+      <c r="C32" s="119"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="119"/>
+      <c r="H32" s="120"/>
+      <c r="I32" s="121"/>
+      <c r="J32" s="121"/>
+      <c r="K32" s="121"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="122"/>
+      <c r="N32" s="123"/>
+      <c r="O32" s="124"/>
+      <c r="P32" s="125"/>
       <c r="Q32" s="46"/>
-      <c r="R32" s="139"/>
-      <c r="S32" s="139"/>
+      <c r="R32" s="126"/>
+      <c r="S32" s="126"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="46"/>
       <c r="B33" s="46"/>
-      <c r="C33" s="140"/>
-      <c r="D33" s="140"/>
-      <c r="E33" s="140"/>
-      <c r="F33" s="140"/>
-      <c r="G33" s="140"/>
-      <c r="H33" s="144"/>
-      <c r="I33" s="145"/>
-      <c r="J33" s="145"/>
-      <c r="K33" s="145"/>
-      <c r="L33" s="145"/>
-      <c r="M33" s="146"/>
-      <c r="N33" s="141"/>
-      <c r="O33" s="142"/>
-      <c r="P33" s="143"/>
+      <c r="C33" s="119"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="119"/>
+      <c r="F33" s="119"/>
+      <c r="G33" s="119"/>
+      <c r="H33" s="120"/>
+      <c r="I33" s="121"/>
+      <c r="J33" s="121"/>
+      <c r="K33" s="121"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="122"/>
+      <c r="N33" s="123"/>
+      <c r="O33" s="124"/>
+      <c r="P33" s="125"/>
       <c r="Q33" s="46"/>
-      <c r="R33" s="139"/>
-      <c r="S33" s="139"/>
+      <c r="R33" s="126"/>
+      <c r="S33" s="126"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="46"/>
       <c r="B34" s="46"/>
-      <c r="C34" s="140"/>
-      <c r="D34" s="140"/>
-      <c r="E34" s="140"/>
-      <c r="F34" s="140"/>
-      <c r="G34" s="140"/>
-      <c r="H34" s="144"/>
-      <c r="I34" s="145"/>
-      <c r="J34" s="145"/>
-      <c r="K34" s="145"/>
-      <c r="L34" s="145"/>
-      <c r="M34" s="146"/>
-      <c r="N34" s="141"/>
-      <c r="O34" s="142"/>
-      <c r="P34" s="143"/>
+      <c r="C34" s="119"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="119"/>
+      <c r="F34" s="119"/>
+      <c r="G34" s="119"/>
+      <c r="H34" s="120"/>
+      <c r="I34" s="121"/>
+      <c r="J34" s="121"/>
+      <c r="K34" s="121"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="122"/>
+      <c r="N34" s="123"/>
+      <c r="O34" s="124"/>
+      <c r="P34" s="125"/>
       <c r="Q34" s="46"/>
-      <c r="R34" s="139"/>
-      <c r="S34" s="139"/>
+      <c r="R34" s="126"/>
+      <c r="S34" s="126"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
-      <c r="C35" s="140"/>
-      <c r="D35" s="140"/>
-      <c r="E35" s="140"/>
-      <c r="F35" s="140"/>
-      <c r="G35" s="140"/>
-      <c r="H35" s="144"/>
-      <c r="I35" s="145"/>
-      <c r="J35" s="145"/>
-      <c r="K35" s="145"/>
-      <c r="L35" s="145"/>
-      <c r="M35" s="146"/>
-      <c r="N35" s="141"/>
-      <c r="O35" s="142"/>
-      <c r="P35" s="143"/>
+      <c r="C35" s="119"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="119"/>
+      <c r="G35" s="119"/>
+      <c r="H35" s="120"/>
+      <c r="I35" s="121"/>
+      <c r="J35" s="121"/>
+      <c r="K35" s="121"/>
+      <c r="L35" s="121"/>
+      <c r="M35" s="122"/>
+      <c r="N35" s="123"/>
+      <c r="O35" s="124"/>
+      <c r="P35" s="125"/>
       <c r="Q35" s="46"/>
-      <c r="R35" s="139"/>
-      <c r="S35" s="139"/>
+      <c r="R35" s="126"/>
+      <c r="S35" s="126"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="46"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="140"/>
-      <c r="D36" s="140"/>
-      <c r="E36" s="140"/>
-      <c r="F36" s="140"/>
-      <c r="G36" s="140"/>
-      <c r="H36" s="144"/>
-      <c r="I36" s="145"/>
-      <c r="J36" s="145"/>
-      <c r="K36" s="145"/>
-      <c r="L36" s="145"/>
-      <c r="M36" s="146"/>
-      <c r="N36" s="141"/>
-      <c r="O36" s="142"/>
-      <c r="P36" s="143"/>
+      <c r="C36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="119"/>
+      <c r="H36" s="120"/>
+      <c r="I36" s="121"/>
+      <c r="J36" s="121"/>
+      <c r="K36" s="121"/>
+      <c r="L36" s="121"/>
+      <c r="M36" s="122"/>
+      <c r="N36" s="123"/>
+      <c r="O36" s="124"/>
+      <c r="P36" s="125"/>
       <c r="Q36" s="46"/>
-      <c r="R36" s="139"/>
-      <c r="S36" s="139"/>
+      <c r="R36" s="126"/>
+      <c r="S36" s="126"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="46"/>
       <c r="B37" s="46"/>
-      <c r="C37" s="140"/>
-      <c r="D37" s="140"/>
-      <c r="E37" s="140"/>
-      <c r="F37" s="140"/>
-      <c r="G37" s="140"/>
-      <c r="H37" s="144"/>
-      <c r="I37" s="145"/>
-      <c r="J37" s="145"/>
-      <c r="K37" s="145"/>
-      <c r="L37" s="145"/>
-      <c r="M37" s="146"/>
-      <c r="N37" s="141"/>
-      <c r="O37" s="142"/>
-      <c r="P37" s="143"/>
+      <c r="C37" s="119"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="119"/>
+      <c r="G37" s="119"/>
+      <c r="H37" s="120"/>
+      <c r="I37" s="121"/>
+      <c r="J37" s="121"/>
+      <c r="K37" s="121"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="122"/>
+      <c r="N37" s="123"/>
+      <c r="O37" s="124"/>
+      <c r="P37" s="125"/>
       <c r="Q37" s="46"/>
-      <c r="R37" s="139"/>
-      <c r="S37" s="139"/>
+      <c r="R37" s="126"/>
+      <c r="S37" s="126"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="46"/>
       <c r="B38" s="46"/>
-      <c r="C38" s="140"/>
-      <c r="D38" s="140"/>
-      <c r="E38" s="140"/>
-      <c r="F38" s="140"/>
-      <c r="G38" s="140"/>
-      <c r="H38" s="144"/>
-      <c r="I38" s="145"/>
-      <c r="J38" s="145"/>
-      <c r="K38" s="145"/>
-      <c r="L38" s="145"/>
-      <c r="M38" s="146"/>
-      <c r="N38" s="141"/>
-      <c r="O38" s="142"/>
-      <c r="P38" s="143"/>
+      <c r="C38" s="119"/>
+      <c r="D38" s="119"/>
+      <c r="E38" s="119"/>
+      <c r="F38" s="119"/>
+      <c r="G38" s="119"/>
+      <c r="H38" s="120"/>
+      <c r="I38" s="121"/>
+      <c r="J38" s="121"/>
+      <c r="K38" s="121"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="122"/>
+      <c r="N38" s="123"/>
+      <c r="O38" s="124"/>
+      <c r="P38" s="125"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="139"/>
+      <c r="R38" s="126"/>
+      <c r="S38" s="126"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="46"/>
       <c r="B39" s="46"/>
-      <c r="C39" s="140"/>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="144"/>
-      <c r="I39" s="145"/>
-      <c r="J39" s="145"/>
-      <c r="K39" s="145"/>
-      <c r="L39" s="145"/>
-      <c r="M39" s="146"/>
-      <c r="N39" s="141"/>
-      <c r="O39" s="142"/>
-      <c r="P39" s="143"/>
+      <c r="C39" s="119"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="119"/>
+      <c r="H39" s="120"/>
+      <c r="I39" s="121"/>
+      <c r="J39" s="121"/>
+      <c r="K39" s="121"/>
+      <c r="L39" s="121"/>
+      <c r="M39" s="122"/>
+      <c r="N39" s="123"/>
+      <c r="O39" s="124"/>
+      <c r="P39" s="125"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="139"/>
-      <c r="S39" s="139"/>
+      <c r="R39" s="126"/>
+      <c r="S39" s="126"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="140"/>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="140"/>
-      <c r="H40" s="144"/>
-      <c r="I40" s="145"/>
-      <c r="J40" s="145"/>
-      <c r="K40" s="145"/>
-      <c r="L40" s="145"/>
-      <c r="M40" s="146"/>
-      <c r="N40" s="141"/>
-      <c r="O40" s="142"/>
-      <c r="P40" s="143"/>
+      <c r="C40" s="119"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="119"/>
+      <c r="G40" s="119"/>
+      <c r="H40" s="120"/>
+      <c r="I40" s="121"/>
+      <c r="J40" s="121"/>
+      <c r="K40" s="121"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="122"/>
+      <c r="N40" s="123"/>
+      <c r="O40" s="124"/>
+      <c r="P40" s="125"/>
       <c r="Q40" s="46"/>
-      <c r="R40" s="139"/>
-      <c r="S40" s="139"/>
+      <c r="R40" s="126"/>
+      <c r="S40" s="126"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="46"/>
       <c r="B41" s="46"/>
-      <c r="C41" s="140"/>
-      <c r="D41" s="140"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="140"/>
-      <c r="G41" s="140"/>
-      <c r="H41" s="144"/>
-      <c r="I41" s="145"/>
-      <c r="J41" s="145"/>
-      <c r="K41" s="145"/>
-      <c r="L41" s="145"/>
-      <c r="M41" s="146"/>
-      <c r="N41" s="141"/>
-      <c r="O41" s="142"/>
-      <c r="P41" s="143"/>
+      <c r="C41" s="119"/>
+      <c r="D41" s="119"/>
+      <c r="E41" s="119"/>
+      <c r="F41" s="119"/>
+      <c r="G41" s="119"/>
+      <c r="H41" s="120"/>
+      <c r="I41" s="121"/>
+      <c r="J41" s="121"/>
+      <c r="K41" s="121"/>
+      <c r="L41" s="121"/>
+      <c r="M41" s="122"/>
+      <c r="N41" s="123"/>
+      <c r="O41" s="124"/>
+      <c r="P41" s="125"/>
       <c r="Q41" s="46"/>
-      <c r="R41" s="139"/>
-      <c r="S41" s="139"/>
+      <c r="R41" s="126"/>
+      <c r="S41" s="126"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="46"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="140"/>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="140"/>
-      <c r="H42" s="144"/>
-      <c r="I42" s="145"/>
-      <c r="J42" s="145"/>
-      <c r="K42" s="145"/>
-      <c r="L42" s="145"/>
-      <c r="M42" s="146"/>
-      <c r="N42" s="141"/>
-      <c r="O42" s="142"/>
-      <c r="P42" s="143"/>
+      <c r="C42" s="119"/>
+      <c r="D42" s="119"/>
+      <c r="E42" s="119"/>
+      <c r="F42" s="119"/>
+      <c r="G42" s="119"/>
+      <c r="H42" s="120"/>
+      <c r="I42" s="121"/>
+      <c r="J42" s="121"/>
+      <c r="K42" s="121"/>
+      <c r="L42" s="121"/>
+      <c r="M42" s="122"/>
+      <c r="N42" s="123"/>
+      <c r="O42" s="124"/>
+      <c r="P42" s="125"/>
       <c r="Q42" s="46"/>
-      <c r="R42" s="139"/>
-      <c r="S42" s="139"/>
+      <c r="R42" s="126"/>
+      <c r="S42" s="126"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="46"/>
       <c r="B43" s="46"/>
-      <c r="C43" s="140"/>
-      <c r="D43" s="140"/>
-      <c r="E43" s="140"/>
-      <c r="F43" s="140"/>
-      <c r="G43" s="140"/>
-      <c r="H43" s="144"/>
-      <c r="I43" s="145"/>
-      <c r="J43" s="145"/>
-      <c r="K43" s="145"/>
-      <c r="L43" s="145"/>
-      <c r="M43" s="146"/>
-      <c r="N43" s="141"/>
-      <c r="O43" s="142"/>
-      <c r="P43" s="143"/>
+      <c r="C43" s="119"/>
+      <c r="D43" s="119"/>
+      <c r="E43" s="119"/>
+      <c r="F43" s="119"/>
+      <c r="G43" s="119"/>
+      <c r="H43" s="120"/>
+      <c r="I43" s="121"/>
+      <c r="J43" s="121"/>
+      <c r="K43" s="121"/>
+      <c r="L43" s="121"/>
+      <c r="M43" s="122"/>
+      <c r="N43" s="123"/>
+      <c r="O43" s="124"/>
+      <c r="P43" s="125"/>
       <c r="Q43" s="46"/>
-      <c r="R43" s="139"/>
-      <c r="S43" s="139"/>
+      <c r="R43" s="126"/>
+      <c r="S43" s="126"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="46"/>
       <c r="B44" s="46"/>
-      <c r="C44" s="140"/>
-      <c r="D44" s="140"/>
-      <c r="E44" s="140"/>
-      <c r="F44" s="140"/>
-      <c r="G44" s="140"/>
-      <c r="H44" s="144"/>
-      <c r="I44" s="145"/>
-      <c r="J44" s="145"/>
-      <c r="K44" s="145"/>
-      <c r="L44" s="145"/>
-      <c r="M44" s="146"/>
-      <c r="N44" s="141"/>
-      <c r="O44" s="142"/>
-      <c r="P44" s="143"/>
+      <c r="C44" s="119"/>
+      <c r="D44" s="119"/>
+      <c r="E44" s="119"/>
+      <c r="F44" s="119"/>
+      <c r="G44" s="119"/>
+      <c r="H44" s="120"/>
+      <c r="I44" s="121"/>
+      <c r="J44" s="121"/>
+      <c r="K44" s="121"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="122"/>
+      <c r="N44" s="123"/>
+      <c r="O44" s="124"/>
+      <c r="P44" s="125"/>
       <c r="Q44" s="46"/>
-      <c r="R44" s="139"/>
-      <c r="S44" s="139"/>
+      <c r="R44" s="126"/>
+      <c r="S44" s="126"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="46"/>
       <c r="B45" s="46"/>
-      <c r="C45" s="140"/>
-      <c r="D45" s="140"/>
-      <c r="E45" s="140"/>
-      <c r="F45" s="140"/>
-      <c r="G45" s="140"/>
-      <c r="H45" s="144"/>
-      <c r="I45" s="145"/>
-      <c r="J45" s="145"/>
-      <c r="K45" s="145"/>
-      <c r="L45" s="145"/>
-      <c r="M45" s="146"/>
-      <c r="N45" s="141"/>
-      <c r="O45" s="142"/>
-      <c r="P45" s="143"/>
+      <c r="C45" s="119"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="119"/>
+      <c r="G45" s="119"/>
+      <c r="H45" s="120"/>
+      <c r="I45" s="121"/>
+      <c r="J45" s="121"/>
+      <c r="K45" s="121"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="122"/>
+      <c r="N45" s="123"/>
+      <c r="O45" s="124"/>
+      <c r="P45" s="125"/>
       <c r="Q45" s="46"/>
-      <c r="R45" s="139"/>
-      <c r="S45" s="139"/>
+      <c r="R45" s="126"/>
+      <c r="S45" s="126"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="46"/>
       <c r="B46" s="46"/>
-      <c r="C46" s="140"/>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="140"/>
-      <c r="H46" s="144"/>
-      <c r="I46" s="145"/>
-      <c r="J46" s="145"/>
-      <c r="K46" s="145"/>
-      <c r="L46" s="145"/>
-      <c r="M46" s="146"/>
-      <c r="N46" s="141"/>
-      <c r="O46" s="142"/>
-      <c r="P46" s="143"/>
+      <c r="C46" s="119"/>
+      <c r="D46" s="119"/>
+      <c r="E46" s="119"/>
+      <c r="F46" s="119"/>
+      <c r="G46" s="119"/>
+      <c r="H46" s="120"/>
+      <c r="I46" s="121"/>
+      <c r="J46" s="121"/>
+      <c r="K46" s="121"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="122"/>
+      <c r="N46" s="123"/>
+      <c r="O46" s="124"/>
+      <c r="P46" s="125"/>
       <c r="Q46" s="46"/>
-      <c r="R46" s="139"/>
-      <c r="S46" s="139"/>
+      <c r="R46" s="126"/>
+      <c r="S46" s="126"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="46"/>
       <c r="B47" s="46"/>
-      <c r="C47" s="140"/>
-      <c r="D47" s="140"/>
-      <c r="E47" s="140"/>
-      <c r="F47" s="140"/>
-      <c r="G47" s="140"/>
-      <c r="H47" s="144"/>
-      <c r="I47" s="145"/>
-      <c r="J47" s="145"/>
-      <c r="K47" s="145"/>
-      <c r="L47" s="145"/>
-      <c r="M47" s="146"/>
-      <c r="N47" s="141"/>
-      <c r="O47" s="142"/>
-      <c r="P47" s="143"/>
+      <c r="C47" s="119"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="119"/>
+      <c r="F47" s="119"/>
+      <c r="G47" s="119"/>
+      <c r="H47" s="120"/>
+      <c r="I47" s="121"/>
+      <c r="J47" s="121"/>
+      <c r="K47" s="121"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="122"/>
+      <c r="N47" s="123"/>
+      <c r="O47" s="124"/>
+      <c r="P47" s="125"/>
       <c r="Q47" s="46"/>
-      <c r="R47" s="139"/>
-      <c r="S47" s="139"/>
+      <c r="R47" s="126"/>
+      <c r="S47" s="126"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="46"/>
       <c r="B48" s="46"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
-      <c r="F48" s="140"/>
-      <c r="G48" s="140"/>
-      <c r="H48" s="144"/>
-      <c r="I48" s="145"/>
-      <c r="J48" s="145"/>
-      <c r="K48" s="145"/>
-      <c r="L48" s="145"/>
-      <c r="M48" s="146"/>
-      <c r="N48" s="141"/>
-      <c r="O48" s="142"/>
-      <c r="P48" s="143"/>
+      <c r="C48" s="119"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="119"/>
+      <c r="F48" s="119"/>
+      <c r="G48" s="119"/>
+      <c r="H48" s="120"/>
+      <c r="I48" s="121"/>
+      <c r="J48" s="121"/>
+      <c r="K48" s="121"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="123"/>
+      <c r="O48" s="124"/>
+      <c r="P48" s="125"/>
       <c r="Q48" s="46"/>
-      <c r="R48" s="139"/>
-      <c r="S48" s="139"/>
+      <c r="R48" s="126"/>
+      <c r="S48" s="126"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="46"/>
       <c r="B49" s="46"/>
-      <c r="C49" s="140"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="140"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="140"/>
-      <c r="H49" s="144"/>
-      <c r="I49" s="145"/>
-      <c r="J49" s="145"/>
-      <c r="K49" s="145"/>
-      <c r="L49" s="145"/>
-      <c r="M49" s="146"/>
-      <c r="N49" s="141"/>
-      <c r="O49" s="142"/>
-      <c r="P49" s="143"/>
+      <c r="C49" s="119"/>
+      <c r="D49" s="119"/>
+      <c r="E49" s="119"/>
+      <c r="F49" s="119"/>
+      <c r="G49" s="119"/>
+      <c r="H49" s="120"/>
+      <c r="I49" s="121"/>
+      <c r="J49" s="121"/>
+      <c r="K49" s="121"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="122"/>
+      <c r="N49" s="123"/>
+      <c r="O49" s="124"/>
+      <c r="P49" s="125"/>
       <c r="Q49" s="46"/>
-      <c r="R49" s="139"/>
-      <c r="S49" s="139"/>
+      <c r="R49" s="126"/>
+      <c r="S49" s="126"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="46"/>
       <c r="B50" s="46"/>
-      <c r="C50" s="140"/>
-      <c r="D50" s="140"/>
-      <c r="E50" s="140"/>
-      <c r="F50" s="140"/>
-      <c r="G50" s="140"/>
-      <c r="H50" s="144"/>
-      <c r="I50" s="145"/>
-      <c r="J50" s="145"/>
-      <c r="K50" s="145"/>
-      <c r="L50" s="145"/>
-      <c r="M50" s="146"/>
-      <c r="N50" s="141"/>
-      <c r="O50" s="142"/>
-      <c r="P50" s="143"/>
+      <c r="C50" s="119"/>
+      <c r="D50" s="119"/>
+      <c r="E50" s="119"/>
+      <c r="F50" s="119"/>
+      <c r="G50" s="119"/>
+      <c r="H50" s="120"/>
+      <c r="I50" s="121"/>
+      <c r="J50" s="121"/>
+      <c r="K50" s="121"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="122"/>
+      <c r="N50" s="123"/>
+      <c r="O50" s="124"/>
+      <c r="P50" s="125"/>
       <c r="Q50" s="46"/>
-      <c r="R50" s="139"/>
-      <c r="S50" s="139"/>
+      <c r="R50" s="126"/>
+      <c r="S50" s="126"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="46"/>
       <c r="B51" s="46"/>
-      <c r="C51" s="140"/>
-      <c r="D51" s="140"/>
-      <c r="E51" s="140"/>
-      <c r="F51" s="140"/>
-      <c r="G51" s="140"/>
-      <c r="H51" s="144"/>
-      <c r="I51" s="145"/>
-      <c r="J51" s="145"/>
-      <c r="K51" s="145"/>
-      <c r="L51" s="145"/>
-      <c r="M51" s="146"/>
-      <c r="N51" s="141"/>
-      <c r="O51" s="142"/>
-      <c r="P51" s="143"/>
+      <c r="C51" s="119"/>
+      <c r="D51" s="119"/>
+      <c r="E51" s="119"/>
+      <c r="F51" s="119"/>
+      <c r="G51" s="119"/>
+      <c r="H51" s="120"/>
+      <c r="I51" s="121"/>
+      <c r="J51" s="121"/>
+      <c r="K51" s="121"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="122"/>
+      <c r="N51" s="123"/>
+      <c r="O51" s="124"/>
+      <c r="P51" s="125"/>
       <c r="Q51" s="46"/>
-      <c r="R51" s="139"/>
-      <c r="S51" s="139"/>
+      <c r="R51" s="126"/>
+      <c r="S51" s="126"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="46"/>
       <c r="B52" s="46"/>
-      <c r="C52" s="140"/>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="140"/>
-      <c r="H52" s="144"/>
-      <c r="I52" s="145"/>
-      <c r="J52" s="145"/>
-      <c r="K52" s="145"/>
-      <c r="L52" s="145"/>
-      <c r="M52" s="146"/>
-      <c r="N52" s="141"/>
-      <c r="O52" s="142"/>
-      <c r="P52" s="143"/>
+      <c r="C52" s="119"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="119"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="119"/>
+      <c r="H52" s="120"/>
+      <c r="I52" s="121"/>
+      <c r="J52" s="121"/>
+      <c r="K52" s="121"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="122"/>
+      <c r="N52" s="123"/>
+      <c r="O52" s="124"/>
+      <c r="P52" s="125"/>
       <c r="Q52" s="46"/>
-      <c r="R52" s="139"/>
-      <c r="S52" s="139"/>
+      <c r="R52" s="126"/>
+      <c r="S52" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="204">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -10451,6 +10316,193 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/ログイン機能設計書.xlsx
+++ b/Documents/ログイン機能設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C269AB6-EC0E-4935-94DB-78752331D20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC49AD79-DA41-43EE-BB62-23BCFF4FDE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
   </bookViews>
@@ -1830,6 +1830,39 @@
     <xf numFmtId="56" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1845,6 +1878,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1875,83 +1953,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1971,20 +1983,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1998,39 +2027,82 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2038,78 +2110,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2984,19 +2984,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="87" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="75"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
@@ -3008,190 +3008,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="88" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="89"/>
-      <c r="F2" s="88" t="s">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="92">
+      <c r="G2" s="79"/>
+      <c r="H2" s="82">
         <v>45806</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="84"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="76" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="77"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="62"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="55" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="56"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="55" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="56"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="55" t="s">
+      <c r="B8" s="64"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="56"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="66" t="s">
+      <c r="C9" s="65"/>
+      <c r="D9" s="92" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="56"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="67"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="65" t="s">
+      <c r="A10" s="89"/>
+      <c r="B10" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="56"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="64"/>
-      <c r="B11" s="65" t="s">
+      <c r="A11" s="90"/>
+      <c r="B11" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="66" t="s">
+      <c r="C11" s="65"/>
+      <c r="D11" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="56"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="55" t="s">
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="56"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="61"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="87"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4182,18 +4182,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -4209,6 +4197,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4231,19 +4231,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="87" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="75"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -4255,190 +4255,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="88" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="89"/>
-      <c r="F2" s="88" t="s">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="92">
+      <c r="G2" s="79"/>
+      <c r="H2" s="82">
         <v>45806</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="103" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="77"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="62"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="56"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="95"/>
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="97"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="81"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="98"/>
+      <c r="A8" s="71"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="102"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="81"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="98"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="102"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="98"/>
+      <c r="A10" s="71"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="102"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="81"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="98"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="102"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="81"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="98"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="102"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="81"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="98"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="102"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="99" t="s">
+      <c r="A14" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="56"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="55" t="s">
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="54"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="6" t="s">
         <v>6</v>
       </c>
@@ -4447,11 +4447,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="54"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="6" t="s">
         <v>4</v>
       </c>
@@ -4464,18 +4464,18 @@
       <c r="G16" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H16" s="100" t="s">
+      <c r="H16" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="53"/>
-      <c r="J16" s="56"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="102">
+      <c r="A17" s="95">
         <v>1</v>
       </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="54"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="5" t="s">
         <v>32</v>
       </c>
@@ -4488,18 +4488,18 @@
       <c r="G17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="55" t="s">
+      <c r="H17" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="53"/>
-      <c r="J17" s="56"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="67"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="102">
+      <c r="A18" s="95">
         <v>2</v>
       </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="54"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="65"/>
       <c r="D18" s="5" t="s">
         <v>33</v>
       </c>
@@ -4512,18 +4512,18 @@
       <c r="G18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="55" t="s">
+      <c r="H18" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="53"/>
-      <c r="J18" s="56"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="102">
+      <c r="A19" s="95">
         <v>3</v>
       </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="54"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
       <c r="D19" s="5" t="s">
         <v>34</v>
       </c>
@@ -4536,16 +4536,16 @@
       <c r="G19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="55"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="56"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="67"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="102">
+      <c r="A20" s="95">
         <v>4</v>
       </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="54"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65"/>
       <c r="D20" s="5" t="s">
         <v>35</v>
       </c>
@@ -4556,45 +4556,45 @@
       <c r="G20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="55"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="56"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="54"/>
+      <c r="A21" s="95"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="56"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="102"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="54"/>
+      <c r="A22" s="95"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="65"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="56"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="101"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="61"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="87"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5575,6 +5575,21 @@
     <row r="1000" s="1" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
@@ -5591,21 +5606,6 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -5626,19 +5626,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="87" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="75"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -5650,48 +5650,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="88" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="89"/>
-      <c r="F2" s="88" t="s">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="92">
+      <c r="G2" s="79"/>
+      <c r="H2" s="82">
         <v>45810</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="84"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="11"/>
@@ -7042,190 +7042,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="87" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="87" t="s">
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="87" t="s">
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="87" t="s">
+      <c r="P1" s="60"/>
+      <c r="Q1" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="75"/>
-      <c r="S1" s="87" t="s">
+      <c r="R1" s="60"/>
+      <c r="S1" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="77"/>
+      <c r="T1" s="62"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="88" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="88" t="s">
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="118">
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="105">
         <v>45810</v>
       </c>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="88" t="s">
+      <c r="P2" s="79"/>
+      <c r="Q2" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="89"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="97"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="101"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="98"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="102"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="84"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="86"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="117"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="104"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="76" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="77"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="62"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="55" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="53"/>
-      <c r="P6" s="53"/>
-      <c r="Q6" s="53"/>
-      <c r="R6" s="53"/>
-      <c r="S6" s="53"/>
-      <c r="T6" s="56"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="67"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="55" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="53"/>
-      <c r="T7" s="56"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="67"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="11"/>
@@ -7424,37 +7424,37 @@
       <c r="T14" s="13"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="94" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="116" t="s">
+      <c r="B15" s="65"/>
+      <c r="C15" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="54"/>
-      <c r="E15" s="100" t="s">
+      <c r="D15" s="65"/>
+      <c r="E15" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="54"/>
-      <c r="G15" s="100" t="s">
+      <c r="F15" s="65"/>
+      <c r="G15" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="53"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="100" t="s">
+      <c r="H15" s="64"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="K15" s="54"/>
-      <c r="L15" s="100" t="s">
+      <c r="K15" s="65"/>
+      <c r="L15" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="M15" s="53"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="100" t="s">
+      <c r="M15" s="64"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="P15" s="53"/>
-      <c r="Q15" s="54"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="65"/>
       <c r="R15" s="6" t="s">
         <v>69</v>
       </c>
@@ -7466,37 +7466,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="109">
+      <c r="A16" s="106">
         <v>1</v>
       </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="110" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="110" t="s">
+      <c r="D16" s="65"/>
+      <c r="E16" s="107" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="54"/>
-      <c r="G16" s="111" t="s">
+      <c r="F16" s="65"/>
+      <c r="G16" s="108" t="s">
         <v>108</v>
       </c>
-      <c r="H16" s="53"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="111" t="s">
+      <c r="H16" s="64"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="108" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="54"/>
-      <c r="L16" s="114" t="s">
+      <c r="K16" s="65"/>
+      <c r="L16" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="M16" s="115"/>
-      <c r="N16" s="115"/>
-      <c r="O16" s="108" t="s">
+      <c r="M16" s="110"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="111" t="s">
         <v>75</v>
       </c>
-      <c r="P16" s="53"/>
-      <c r="Q16" s="54"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="65"/>
       <c r="R16" s="51">
         <v>45810</v>
       </c>
@@ -7514,37 +7514,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="75" customHeight="1">
-      <c r="A17" s="109">
+      <c r="A17" s="106">
         <v>2</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="110" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="107" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="110" t="s">
+      <c r="D17" s="65"/>
+      <c r="E17" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="54"/>
-      <c r="G17" s="111" t="s">
+      <c r="F17" s="65"/>
+      <c r="G17" s="108" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="53"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="111" t="s">
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="108" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="54"/>
-      <c r="L17" s="108" t="s">
+      <c r="K17" s="65"/>
+      <c r="L17" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="M17" s="112"/>
-      <c r="N17" s="113"/>
-      <c r="O17" s="108" t="s">
+      <c r="M17" s="113"/>
+      <c r="N17" s="114"/>
+      <c r="O17" s="111" t="s">
         <v>90</v>
       </c>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="54"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="65"/>
       <c r="R17" s="51">
         <v>45810</v>
       </c>
@@ -7562,37 +7562,37 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="79.5" customHeight="1">
-      <c r="A18" s="109">
+      <c r="A18" s="106">
         <v>3</v>
       </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="110" t="s">
+      <c r="B18" s="65"/>
+      <c r="C18" s="107" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="54"/>
-      <c r="E18" s="110" t="s">
+      <c r="D18" s="65"/>
+      <c r="E18" s="107" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="54"/>
-      <c r="G18" s="111" t="s">
+      <c r="F18" s="65"/>
+      <c r="G18" s="108" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="53"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="111" t="s">
+      <c r="H18" s="64"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="K18" s="54"/>
-      <c r="L18" s="108" t="s">
+      <c r="K18" s="65"/>
+      <c r="L18" s="111" t="s">
         <v>79</v>
       </c>
-      <c r="M18" s="53"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="108" t="s">
+      <c r="M18" s="64"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="111" t="s">
         <v>118</v>
       </c>
-      <c r="P18" s="53"/>
-      <c r="Q18" s="54"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="65"/>
       <c r="R18" s="51">
         <v>45810</v>
       </c>
@@ -7610,37 +7610,37 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="42.75" customHeight="1">
-      <c r="A19" s="109">
+      <c r="A19" s="106">
         <v>4</v>
       </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="110" t="s">
+      <c r="B19" s="65"/>
+      <c r="C19" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="110" t="s">
+      <c r="D19" s="65"/>
+      <c r="E19" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="54"/>
-      <c r="G19" s="111" t="s">
+      <c r="F19" s="65"/>
+      <c r="G19" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="53"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="111" t="s">
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="K19" s="54"/>
-      <c r="L19" s="108" t="s">
+      <c r="K19" s="65"/>
+      <c r="L19" s="111" t="s">
         <v>79</v>
       </c>
-      <c r="M19" s="53"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="108" t="s">
+      <c r="M19" s="64"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="111" t="s">
         <v>89</v>
       </c>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="54"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="65"/>
       <c r="R19" s="51">
         <v>45810</v>
       </c>
@@ -7658,23 +7658,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="109"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="108"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="108"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="54"/>
+      <c r="A20" s="106"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="65"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -7686,23 +7686,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="110"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="108"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="108"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="54"/>
+      <c r="A21" s="106"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="65"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -7714,23 +7714,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="109"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="110"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="108"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="108"/>
-      <c r="P22" s="53"/>
-      <c r="Q22" s="54"/>
+      <c r="A22" s="106"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="111"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="65"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -7742,23 +7742,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="109"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="110"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="108"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="108"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="54"/>
+      <c r="A23" s="106"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="108"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="111"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="65"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -7770,23 +7770,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="109"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="110"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="108"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="108"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="54"/>
+      <c r="A24" s="106"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="108"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="65"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -7798,23 +7798,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="109"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="110"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="108"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="54"/>
-      <c r="O25" s="108"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="54"/>
+      <c r="A25" s="106"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="108"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="64"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -7826,23 +7826,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="109"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="110"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="108"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="108"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="54"/>
+      <c r="A26" s="106"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="108"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="111"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="65"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -7854,23 +7854,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="109"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="108"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="54"/>
+      <c r="A27" s="106"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="108"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="111"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -7882,23 +7882,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="109"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="108"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="108"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="54"/>
+      <c r="A28" s="106"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="108"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="111"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="65"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -7910,23 +7910,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="109"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="110"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="53"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="53"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="53"/>
-      <c r="Q29" s="54"/>
+      <c r="A29" s="106"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="107"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="111"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="65"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -7938,23 +7938,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="109"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="110"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="54"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="54"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="53"/>
-      <c r="N30" s="54"/>
-      <c r="O30" s="108"/>
-      <c r="P30" s="53"/>
-      <c r="Q30" s="54"/>
+      <c r="A30" s="106"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="107"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="111"/>
+      <c r="P30" s="64"/>
+      <c r="Q30" s="65"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -7966,23 +7966,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="105"/>
-      <c r="B31" s="59"/>
-      <c r="C31" s="106"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="107"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="104"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="59"/>
+      <c r="A31" s="116"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="118"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="115"/>
+      <c r="P31" s="84"/>
+      <c r="Q31" s="85"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -8980,121 +8980,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -9116,6 +9001,121 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -9141,72 +9141,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="128" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="129" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="138"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140" t="s">
+      <c r="D1" s="130"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="132" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="142"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="134"/>
       <c r="N1" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="140" t="s">
+      <c r="O1" s="132" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="142"/>
+      <c r="P1" s="134"/>
       <c r="Q1" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="R1" s="140" t="s">
+      <c r="R1" s="132" t="s">
         <v>96</v>
       </c>
-      <c r="S1" s="142"/>
+      <c r="S1" s="134"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="137" t="s">
+      <c r="A2" s="128"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="138"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="140" t="s">
+      <c r="D2" s="130"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="132" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="142"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="134"/>
       <c r="N2" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="143">
+      <c r="O2" s="135">
         <v>45807</v>
       </c>
-      <c r="P2" s="144"/>
+      <c r="P2" s="136"/>
       <c r="Q2" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="R2" s="145" t="s">
+      <c r="R2" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="146"/>
+      <c r="S2" s="138"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="40"/>
@@ -9236,33 +9236,33 @@
       <c r="B4" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="131" t="s">
+      <c r="C4" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="132"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="131" t="s">
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="119" t="s">
         <v>107</v>
       </c>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="133"/>
-      <c r="N4" s="131" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="119" t="s">
         <v>102</v>
       </c>
-      <c r="O4" s="132"/>
-      <c r="P4" s="133"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="121"/>
       <c r="Q4" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="R4" s="131" t="s">
+      <c r="R4" s="119" t="s">
         <v>104</v>
       </c>
-      <c r="S4" s="133"/>
+      <c r="S4" s="121"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="44">
@@ -9271,31 +9271,31 @@
       <c r="B5" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="127" t="s">
+      <c r="C5" s="122" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127" t="s">
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
-      <c r="L5" s="127"/>
-      <c r="M5" s="127"/>
-      <c r="N5" s="128" t="s">
+      <c r="I5" s="122"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
+      <c r="M5" s="122"/>
+      <c r="N5" s="123" t="s">
         <v>113</v>
       </c>
-      <c r="O5" s="129"/>
-      <c r="P5" s="130"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="125"/>
       <c r="Q5" s="50">
         <v>45810</v>
       </c>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
+      <c r="R5" s="126"/>
+      <c r="S5" s="127"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="46">
@@ -9304,1001 +9304,1188 @@
       <c r="B6" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="127" t="s">
+      <c r="C6" s="122" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="127"/>
-      <c r="E6" s="127"/>
-      <c r="F6" s="127"/>
-      <c r="G6" s="127"/>
-      <c r="H6" s="127" t="s">
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="I6" s="127"/>
-      <c r="J6" s="127"/>
-      <c r="K6" s="127"/>
-      <c r="L6" s="127"/>
-      <c r="M6" s="127"/>
-      <c r="N6" s="128" t="s">
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="123" t="s">
         <v>117</v>
       </c>
-      <c r="O6" s="129"/>
-      <c r="P6" s="130"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="125"/>
       <c r="Q6" s="47">
         <v>45810</v>
       </c>
-      <c r="R6" s="126"/>
-      <c r="S6" s="126"/>
+      <c r="R6" s="139"/>
+      <c r="S6" s="139"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="46">
         <v>3</v>
       </c>
       <c r="B7" s="45"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="127"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="127"/>
-      <c r="M7" s="127"/>
-      <c r="N7" s="128"/>
-      <c r="O7" s="129"/>
-      <c r="P7" s="130"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
+      <c r="N7" s="123"/>
+      <c r="O7" s="124"/>
+      <c r="P7" s="125"/>
       <c r="Q7" s="47"/>
-      <c r="R7" s="126"/>
-      <c r="S7" s="126"/>
+      <c r="R7" s="139"/>
+      <c r="S7" s="139"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="46">
         <v>4</v>
       </c>
       <c r="B8" s="46"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
-      <c r="J8" s="127"/>
-      <c r="K8" s="127"/>
-      <c r="L8" s="127"/>
-      <c r="M8" s="127"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="122"/>
+      <c r="H8" s="122"/>
+      <c r="I8" s="122"/>
+      <c r="J8" s="122"/>
+      <c r="K8" s="122"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
       <c r="Q8" s="47"/>
-      <c r="R8" s="126"/>
-      <c r="S8" s="126"/>
+      <c r="R8" s="139"/>
+      <c r="S8" s="139"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="46"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
-      <c r="L9" s="119"/>
-      <c r="M9" s="119"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="124"/>
-      <c r="P9" s="125"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="140"/>
+      <c r="L9" s="140"/>
+      <c r="M9" s="140"/>
+      <c r="N9" s="141"/>
+      <c r="O9" s="142"/>
+      <c r="P9" s="143"/>
       <c r="Q9" s="46"/>
-      <c r="R9" s="126"/>
-      <c r="S9" s="126"/>
+      <c r="R9" s="139"/>
+      <c r="S9" s="139"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="121"/>
-      <c r="L10" s="121"/>
-      <c r="M10" s="122"/>
-      <c r="N10" s="123"/>
-      <c r="O10" s="124"/>
-      <c r="P10" s="125"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="145"/>
+      <c r="K10" s="145"/>
+      <c r="L10" s="145"/>
+      <c r="M10" s="146"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="142"/>
+      <c r="P10" s="143"/>
       <c r="Q10" s="47"/>
-      <c r="R10" s="126"/>
-      <c r="S10" s="126"/>
+      <c r="R10" s="139"/>
+      <c r="S10" s="139"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="46"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="121"/>
-      <c r="K11" s="121"/>
-      <c r="L11" s="121"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="124"/>
-      <c r="P11" s="125"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="141"/>
+      <c r="O11" s="142"/>
+      <c r="P11" s="143"/>
       <c r="Q11" s="46"/>
-      <c r="R11" s="126"/>
-      <c r="S11" s="126"/>
+      <c r="R11" s="139"/>
+      <c r="S11" s="139"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="46"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="123"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="125"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="145"/>
+      <c r="K12" s="145"/>
+      <c r="L12" s="145"/>
+      <c r="M12" s="146"/>
+      <c r="N12" s="141"/>
+      <c r="O12" s="142"/>
+      <c r="P12" s="143"/>
       <c r="Q12" s="46"/>
-      <c r="R12" s="126"/>
-      <c r="S12" s="126"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="139"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="46"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="119"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="119"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="123"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="125"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="145"/>
+      <c r="L13" s="145"/>
+      <c r="M13" s="146"/>
+      <c r="N13" s="141"/>
+      <c r="O13" s="142"/>
+      <c r="P13" s="143"/>
       <c r="Q13" s="46"/>
-      <c r="R13" s="126"/>
-      <c r="S13" s="126"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="119"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="121"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="122"/>
-      <c r="N14" s="123"/>
-      <c r="O14" s="124"/>
-      <c r="P14" s="125"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="145"/>
+      <c r="J14" s="145"/>
+      <c r="K14" s="145"/>
+      <c r="L14" s="145"/>
+      <c r="M14" s="146"/>
+      <c r="N14" s="141"/>
+      <c r="O14" s="142"/>
+      <c r="P14" s="143"/>
       <c r="Q14" s="46"/>
-      <c r="R14" s="126"/>
-      <c r="S14" s="126"/>
+      <c r="R14" s="139"/>
+      <c r="S14" s="139"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="46"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="122"/>
-      <c r="N15" s="123"/>
-      <c r="O15" s="124"/>
-      <c r="P15" s="125"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="145"/>
+      <c r="J15" s="145"/>
+      <c r="K15" s="145"/>
+      <c r="L15" s="145"/>
+      <c r="M15" s="146"/>
+      <c r="N15" s="141"/>
+      <c r="O15" s="142"/>
+      <c r="P15" s="143"/>
       <c r="Q15" s="46"/>
-      <c r="R15" s="126"/>
-      <c r="S15" s="126"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="46"/>
-      <c r="C16" s="119"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="121"/>
-      <c r="J16" s="121"/>
-      <c r="K16" s="121"/>
-      <c r="L16" s="121"/>
-      <c r="M16" s="122"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="124"/>
-      <c r="P16" s="125"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="145"/>
+      <c r="K16" s="145"/>
+      <c r="L16" s="145"/>
+      <c r="M16" s="146"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="142"/>
+      <c r="P16" s="143"/>
       <c r="Q16" s="46"/>
-      <c r="R16" s="126"/>
-      <c r="S16" s="126"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="139"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="46"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="119"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="122"/>
-      <c r="N17" s="123"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="125"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="140"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="145"/>
+      <c r="K17" s="145"/>
+      <c r="L17" s="145"/>
+      <c r="M17" s="146"/>
+      <c r="N17" s="141"/>
+      <c r="O17" s="142"/>
+      <c r="P17" s="143"/>
       <c r="Q17" s="46"/>
-      <c r="R17" s="126"/>
-      <c r="S17" s="126"/>
+      <c r="R17" s="139"/>
+      <c r="S17" s="139"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="46"/>
-      <c r="C18" s="119"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="121"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="125"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="140"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="140"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="144"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="146"/>
+      <c r="N18" s="141"/>
+      <c r="O18" s="142"/>
+      <c r="P18" s="143"/>
       <c r="Q18" s="46"/>
-      <c r="R18" s="126"/>
-      <c r="S18" s="126"/>
+      <c r="R18" s="139"/>
+      <c r="S18" s="139"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="46"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="121"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="122"/>
-      <c r="N19" s="123"/>
-      <c r="O19" s="124"/>
-      <c r="P19" s="125"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="140"/>
+      <c r="F19" s="140"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="144"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="146"/>
+      <c r="N19" s="141"/>
+      <c r="O19" s="142"/>
+      <c r="P19" s="143"/>
       <c r="Q19" s="46"/>
-      <c r="R19" s="126"/>
-      <c r="S19" s="126"/>
+      <c r="R19" s="139"/>
+      <c r="S19" s="139"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="46"/>
       <c r="B20" s="46"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="119"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="121"/>
-      <c r="J20" s="121"/>
-      <c r="K20" s="121"/>
-      <c r="L20" s="121"/>
-      <c r="M20" s="122"/>
-      <c r="N20" s="123"/>
-      <c r="O20" s="124"/>
-      <c r="P20" s="125"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="144"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="146"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="142"/>
+      <c r="P20" s="143"/>
       <c r="Q20" s="46"/>
-      <c r="R20" s="126"/>
-      <c r="S20" s="126"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="139"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="46"/>
       <c r="B21" s="46"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="119"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="121"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="122"/>
-      <c r="N21" s="123"/>
-      <c r="O21" s="124"/>
-      <c r="P21" s="125"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="145"/>
+      <c r="L21" s="145"/>
+      <c r="M21" s="146"/>
+      <c r="N21" s="141"/>
+      <c r="O21" s="142"/>
+      <c r="P21" s="143"/>
       <c r="Q21" s="46"/>
-      <c r="R21" s="126"/>
-      <c r="S21" s="126"/>
+      <c r="R21" s="139"/>
+      <c r="S21" s="139"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="46"/>
       <c r="B22" s="46"/>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="121"/>
-      <c r="J22" s="121"/>
-      <c r="K22" s="121"/>
-      <c r="L22" s="121"/>
-      <c r="M22" s="122"/>
-      <c r="N22" s="123"/>
-      <c r="O22" s="124"/>
-      <c r="P22" s="125"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="140"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="145"/>
+      <c r="J22" s="145"/>
+      <c r="K22" s="145"/>
+      <c r="L22" s="145"/>
+      <c r="M22" s="146"/>
+      <c r="N22" s="141"/>
+      <c r="O22" s="142"/>
+      <c r="P22" s="143"/>
       <c r="Q22" s="46"/>
-      <c r="R22" s="126"/>
-      <c r="S22" s="126"/>
+      <c r="R22" s="139"/>
+      <c r="S22" s="139"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="46"/>
       <c r="B23" s="46"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="121"/>
-      <c r="J23" s="121"/>
-      <c r="K23" s="121"/>
-      <c r="L23" s="121"/>
-      <c r="M23" s="122"/>
-      <c r="N23" s="123"/>
-      <c r="O23" s="124"/>
-      <c r="P23" s="125"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="140"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="145"/>
+      <c r="J23" s="145"/>
+      <c r="K23" s="145"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="141"/>
+      <c r="O23" s="142"/>
+      <c r="P23" s="143"/>
       <c r="Q23" s="46"/>
-      <c r="R23" s="126"/>
-      <c r="S23" s="126"/>
+      <c r="R23" s="139"/>
+      <c r="S23" s="139"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="46"/>
       <c r="B24" s="46"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="120"/>
-      <c r="I24" s="121"/>
-      <c r="J24" s="121"/>
-      <c r="K24" s="121"/>
-      <c r="L24" s="121"/>
-      <c r="M24" s="122"/>
-      <c r="N24" s="123"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="125"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="145"/>
+      <c r="J24" s="145"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="145"/>
+      <c r="M24" s="146"/>
+      <c r="N24" s="141"/>
+      <c r="O24" s="142"/>
+      <c r="P24" s="143"/>
       <c r="Q24" s="46"/>
-      <c r="R24" s="126"/>
-      <c r="S24" s="126"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="46"/>
       <c r="B25" s="46"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="120"/>
-      <c r="I25" s="121"/>
-      <c r="J25" s="121"/>
-      <c r="K25" s="121"/>
-      <c r="L25" s="121"/>
-      <c r="M25" s="122"/>
-      <c r="N25" s="123"/>
-      <c r="O25" s="124"/>
-      <c r="P25" s="125"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="144"/>
+      <c r="I25" s="145"/>
+      <c r="J25" s="145"/>
+      <c r="K25" s="145"/>
+      <c r="L25" s="145"/>
+      <c r="M25" s="146"/>
+      <c r="N25" s="141"/>
+      <c r="O25" s="142"/>
+      <c r="P25" s="143"/>
       <c r="Q25" s="46"/>
-      <c r="R25" s="126"/>
-      <c r="S25" s="126"/>
+      <c r="R25" s="139"/>
+      <c r="S25" s="139"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="46"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="120"/>
-      <c r="I26" s="121"/>
-      <c r="J26" s="121"/>
-      <c r="K26" s="121"/>
-      <c r="L26" s="121"/>
-      <c r="M26" s="122"/>
-      <c r="N26" s="123"/>
-      <c r="O26" s="124"/>
-      <c r="P26" s="125"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="144"/>
+      <c r="I26" s="145"/>
+      <c r="J26" s="145"/>
+      <c r="K26" s="145"/>
+      <c r="L26" s="145"/>
+      <c r="M26" s="146"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="142"/>
+      <c r="P26" s="143"/>
       <c r="Q26" s="46"/>
-      <c r="R26" s="126"/>
-      <c r="S26" s="126"/>
+      <c r="R26" s="139"/>
+      <c r="S26" s="139"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="46"/>
       <c r="B27" s="46"/>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="120"/>
-      <c r="I27" s="121"/>
-      <c r="J27" s="121"/>
-      <c r="K27" s="121"/>
-      <c r="L27" s="121"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="123"/>
-      <c r="O27" s="124"/>
-      <c r="P27" s="125"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="144"/>
+      <c r="I27" s="145"/>
+      <c r="J27" s="145"/>
+      <c r="K27" s="145"/>
+      <c r="L27" s="145"/>
+      <c r="M27" s="146"/>
+      <c r="N27" s="141"/>
+      <c r="O27" s="142"/>
+      <c r="P27" s="143"/>
       <c r="Q27" s="46"/>
-      <c r="R27" s="126"/>
-      <c r="S27" s="126"/>
+      <c r="R27" s="139"/>
+      <c r="S27" s="139"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="46"/>
       <c r="B28" s="46"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="120"/>
-      <c r="I28" s="121"/>
-      <c r="J28" s="121"/>
-      <c r="K28" s="121"/>
-      <c r="L28" s="121"/>
-      <c r="M28" s="122"/>
-      <c r="N28" s="123"/>
-      <c r="O28" s="124"/>
-      <c r="P28" s="125"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="144"/>
+      <c r="I28" s="145"/>
+      <c r="J28" s="145"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="146"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="142"/>
+      <c r="P28" s="143"/>
       <c r="Q28" s="46"/>
-      <c r="R28" s="126"/>
-      <c r="S28" s="126"/>
+      <c r="R28" s="139"/>
+      <c r="S28" s="139"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="46"/>
       <c r="B29" s="46"/>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="120"/>
-      <c r="I29" s="121"/>
-      <c r="J29" s="121"/>
-      <c r="K29" s="121"/>
-      <c r="L29" s="121"/>
-      <c r="M29" s="122"/>
-      <c r="N29" s="123"/>
-      <c r="O29" s="124"/>
-      <c r="P29" s="125"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="144"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="145"/>
+      <c r="K29" s="145"/>
+      <c r="L29" s="145"/>
+      <c r="M29" s="146"/>
+      <c r="N29" s="141"/>
+      <c r="O29" s="142"/>
+      <c r="P29" s="143"/>
       <c r="Q29" s="46"/>
-      <c r="R29" s="126"/>
-      <c r="S29" s="126"/>
+      <c r="R29" s="139"/>
+      <c r="S29" s="139"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="46"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="120"/>
-      <c r="I30" s="121"/>
-      <c r="J30" s="121"/>
-      <c r="K30" s="121"/>
-      <c r="L30" s="121"/>
-      <c r="M30" s="122"/>
-      <c r="N30" s="123"/>
-      <c r="O30" s="124"/>
-      <c r="P30" s="125"/>
+      <c r="C30" s="140"/>
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="144"/>
+      <c r="I30" s="145"/>
+      <c r="J30" s="145"/>
+      <c r="K30" s="145"/>
+      <c r="L30" s="145"/>
+      <c r="M30" s="146"/>
+      <c r="N30" s="141"/>
+      <c r="O30" s="142"/>
+      <c r="P30" s="143"/>
       <c r="Q30" s="46"/>
-      <c r="R30" s="126"/>
-      <c r="S30" s="126"/>
+      <c r="R30" s="139"/>
+      <c r="S30" s="139"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="119"/>
-      <c r="H31" s="120"/>
-      <c r="I31" s="121"/>
-      <c r="J31" s="121"/>
-      <c r="K31" s="121"/>
-      <c r="L31" s="121"/>
-      <c r="M31" s="122"/>
-      <c r="N31" s="123"/>
-      <c r="O31" s="124"/>
-      <c r="P31" s="125"/>
+      <c r="C31" s="140"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="144"/>
+      <c r="I31" s="145"/>
+      <c r="J31" s="145"/>
+      <c r="K31" s="145"/>
+      <c r="L31" s="145"/>
+      <c r="M31" s="146"/>
+      <c r="N31" s="141"/>
+      <c r="O31" s="142"/>
+      <c r="P31" s="143"/>
       <c r="Q31" s="46"/>
-      <c r="R31" s="126"/>
-      <c r="S31" s="126"/>
+      <c r="R31" s="139"/>
+      <c r="S31" s="139"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="119"/>
-      <c r="H32" s="120"/>
-      <c r="I32" s="121"/>
-      <c r="J32" s="121"/>
-      <c r="K32" s="121"/>
-      <c r="L32" s="121"/>
-      <c r="M32" s="122"/>
-      <c r="N32" s="123"/>
-      <c r="O32" s="124"/>
-      <c r="P32" s="125"/>
+      <c r="C32" s="140"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="140"/>
+      <c r="G32" s="140"/>
+      <c r="H32" s="144"/>
+      <c r="I32" s="145"/>
+      <c r="J32" s="145"/>
+      <c r="K32" s="145"/>
+      <c r="L32" s="145"/>
+      <c r="M32" s="146"/>
+      <c r="N32" s="141"/>
+      <c r="O32" s="142"/>
+      <c r="P32" s="143"/>
       <c r="Q32" s="46"/>
-      <c r="R32" s="126"/>
-      <c r="S32" s="126"/>
+      <c r="R32" s="139"/>
+      <c r="S32" s="139"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="46"/>
       <c r="B33" s="46"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="119"/>
-      <c r="H33" s="120"/>
-      <c r="I33" s="121"/>
-      <c r="J33" s="121"/>
-      <c r="K33" s="121"/>
-      <c r="L33" s="121"/>
-      <c r="M33" s="122"/>
-      <c r="N33" s="123"/>
-      <c r="O33" s="124"/>
-      <c r="P33" s="125"/>
+      <c r="C33" s="140"/>
+      <c r="D33" s="140"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="140"/>
+      <c r="G33" s="140"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="145"/>
+      <c r="J33" s="145"/>
+      <c r="K33" s="145"/>
+      <c r="L33" s="145"/>
+      <c r="M33" s="146"/>
+      <c r="N33" s="141"/>
+      <c r="O33" s="142"/>
+      <c r="P33" s="143"/>
       <c r="Q33" s="46"/>
-      <c r="R33" s="126"/>
-      <c r="S33" s="126"/>
+      <c r="R33" s="139"/>
+      <c r="S33" s="139"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="46"/>
       <c r="B34" s="46"/>
-      <c r="C34" s="119"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="119"/>
-      <c r="F34" s="119"/>
-      <c r="G34" s="119"/>
-      <c r="H34" s="120"/>
-      <c r="I34" s="121"/>
-      <c r="J34" s="121"/>
-      <c r="K34" s="121"/>
-      <c r="L34" s="121"/>
-      <c r="M34" s="122"/>
-      <c r="N34" s="123"/>
-      <c r="O34" s="124"/>
-      <c r="P34" s="125"/>
+      <c r="C34" s="140"/>
+      <c r="D34" s="140"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="140"/>
+      <c r="H34" s="144"/>
+      <c r="I34" s="145"/>
+      <c r="J34" s="145"/>
+      <c r="K34" s="145"/>
+      <c r="L34" s="145"/>
+      <c r="M34" s="146"/>
+      <c r="N34" s="141"/>
+      <c r="O34" s="142"/>
+      <c r="P34" s="143"/>
       <c r="Q34" s="46"/>
-      <c r="R34" s="126"/>
-      <c r="S34" s="126"/>
+      <c r="R34" s="139"/>
+      <c r="S34" s="139"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
-      <c r="C35" s="119"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="119"/>
-      <c r="G35" s="119"/>
-      <c r="H35" s="120"/>
-      <c r="I35" s="121"/>
-      <c r="J35" s="121"/>
-      <c r="K35" s="121"/>
-      <c r="L35" s="121"/>
-      <c r="M35" s="122"/>
-      <c r="N35" s="123"/>
-      <c r="O35" s="124"/>
-      <c r="P35" s="125"/>
+      <c r="C35" s="140"/>
+      <c r="D35" s="140"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="140"/>
+      <c r="G35" s="140"/>
+      <c r="H35" s="144"/>
+      <c r="I35" s="145"/>
+      <c r="J35" s="145"/>
+      <c r="K35" s="145"/>
+      <c r="L35" s="145"/>
+      <c r="M35" s="146"/>
+      <c r="N35" s="141"/>
+      <c r="O35" s="142"/>
+      <c r="P35" s="143"/>
       <c r="Q35" s="46"/>
-      <c r="R35" s="126"/>
-      <c r="S35" s="126"/>
+      <c r="R35" s="139"/>
+      <c r="S35" s="139"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="46"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="119"/>
-      <c r="H36" s="120"/>
-      <c r="I36" s="121"/>
-      <c r="J36" s="121"/>
-      <c r="K36" s="121"/>
-      <c r="L36" s="121"/>
-      <c r="M36" s="122"/>
-      <c r="N36" s="123"/>
-      <c r="O36" s="124"/>
-      <c r="P36" s="125"/>
+      <c r="C36" s="140"/>
+      <c r="D36" s="140"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="140"/>
+      <c r="G36" s="140"/>
+      <c r="H36" s="144"/>
+      <c r="I36" s="145"/>
+      <c r="J36" s="145"/>
+      <c r="K36" s="145"/>
+      <c r="L36" s="145"/>
+      <c r="M36" s="146"/>
+      <c r="N36" s="141"/>
+      <c r="O36" s="142"/>
+      <c r="P36" s="143"/>
       <c r="Q36" s="46"/>
-      <c r="R36" s="126"/>
-      <c r="S36" s="126"/>
+      <c r="R36" s="139"/>
+      <c r="S36" s="139"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="46"/>
       <c r="B37" s="46"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="119"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="121"/>
-      <c r="J37" s="121"/>
-      <c r="K37" s="121"/>
-      <c r="L37" s="121"/>
-      <c r="M37" s="122"/>
-      <c r="N37" s="123"/>
-      <c r="O37" s="124"/>
-      <c r="P37" s="125"/>
+      <c r="C37" s="140"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="144"/>
+      <c r="I37" s="145"/>
+      <c r="J37" s="145"/>
+      <c r="K37" s="145"/>
+      <c r="L37" s="145"/>
+      <c r="M37" s="146"/>
+      <c r="N37" s="141"/>
+      <c r="O37" s="142"/>
+      <c r="P37" s="143"/>
       <c r="Q37" s="46"/>
-      <c r="R37" s="126"/>
-      <c r="S37" s="126"/>
+      <c r="R37" s="139"/>
+      <c r="S37" s="139"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="46"/>
       <c r="B38" s="46"/>
-      <c r="C38" s="119"/>
-      <c r="D38" s="119"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="119"/>
-      <c r="G38" s="119"/>
-      <c r="H38" s="120"/>
-      <c r="I38" s="121"/>
-      <c r="J38" s="121"/>
-      <c r="K38" s="121"/>
-      <c r="L38" s="121"/>
-      <c r="M38" s="122"/>
-      <c r="N38" s="123"/>
-      <c r="O38" s="124"/>
-      <c r="P38" s="125"/>
+      <c r="C38" s="140"/>
+      <c r="D38" s="140"/>
+      <c r="E38" s="140"/>
+      <c r="F38" s="140"/>
+      <c r="G38" s="140"/>
+      <c r="H38" s="144"/>
+      <c r="I38" s="145"/>
+      <c r="J38" s="145"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="145"/>
+      <c r="M38" s="146"/>
+      <c r="N38" s="141"/>
+      <c r="O38" s="142"/>
+      <c r="P38" s="143"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="126"/>
-      <c r="S38" s="126"/>
+      <c r="R38" s="139"/>
+      <c r="S38" s="139"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="46"/>
       <c r="B39" s="46"/>
-      <c r="C39" s="119"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="119"/>
-      <c r="G39" s="119"/>
-      <c r="H39" s="120"/>
-      <c r="I39" s="121"/>
-      <c r="J39" s="121"/>
-      <c r="K39" s="121"/>
-      <c r="L39" s="121"/>
-      <c r="M39" s="122"/>
-      <c r="N39" s="123"/>
-      <c r="O39" s="124"/>
-      <c r="P39" s="125"/>
+      <c r="C39" s="140"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="144"/>
+      <c r="I39" s="145"/>
+      <c r="J39" s="145"/>
+      <c r="K39" s="145"/>
+      <c r="L39" s="145"/>
+      <c r="M39" s="146"/>
+      <c r="N39" s="141"/>
+      <c r="O39" s="142"/>
+      <c r="P39" s="143"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="126"/>
-      <c r="S39" s="126"/>
+      <c r="R39" s="139"/>
+      <c r="S39" s="139"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="119"/>
-      <c r="D40" s="119"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="119"/>
-      <c r="G40" s="119"/>
-      <c r="H40" s="120"/>
-      <c r="I40" s="121"/>
-      <c r="J40" s="121"/>
-      <c r="K40" s="121"/>
-      <c r="L40" s="121"/>
-      <c r="M40" s="122"/>
-      <c r="N40" s="123"/>
-      <c r="O40" s="124"/>
-      <c r="P40" s="125"/>
+      <c r="C40" s="140"/>
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="144"/>
+      <c r="I40" s="145"/>
+      <c r="J40" s="145"/>
+      <c r="K40" s="145"/>
+      <c r="L40" s="145"/>
+      <c r="M40" s="146"/>
+      <c r="N40" s="141"/>
+      <c r="O40" s="142"/>
+      <c r="P40" s="143"/>
       <c r="Q40" s="46"/>
-      <c r="R40" s="126"/>
-      <c r="S40" s="126"/>
+      <c r="R40" s="139"/>
+      <c r="S40" s="139"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="46"/>
       <c r="B41" s="46"/>
-      <c r="C41" s="119"/>
-      <c r="D41" s="119"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="119"/>
-      <c r="G41" s="119"/>
-      <c r="H41" s="120"/>
-      <c r="I41" s="121"/>
-      <c r="J41" s="121"/>
-      <c r="K41" s="121"/>
-      <c r="L41" s="121"/>
-      <c r="M41" s="122"/>
-      <c r="N41" s="123"/>
-      <c r="O41" s="124"/>
-      <c r="P41" s="125"/>
+      <c r="C41" s="140"/>
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="144"/>
+      <c r="I41" s="145"/>
+      <c r="J41" s="145"/>
+      <c r="K41" s="145"/>
+      <c r="L41" s="145"/>
+      <c r="M41" s="146"/>
+      <c r="N41" s="141"/>
+      <c r="O41" s="142"/>
+      <c r="P41" s="143"/>
       <c r="Q41" s="46"/>
-      <c r="R41" s="126"/>
-      <c r="S41" s="126"/>
+      <c r="R41" s="139"/>
+      <c r="S41" s="139"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="46"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="119"/>
-      <c r="D42" s="119"/>
-      <c r="E42" s="119"/>
-      <c r="F42" s="119"/>
-      <c r="G42" s="119"/>
-      <c r="H42" s="120"/>
-      <c r="I42" s="121"/>
-      <c r="J42" s="121"/>
-      <c r="K42" s="121"/>
-      <c r="L42" s="121"/>
-      <c r="M42" s="122"/>
-      <c r="N42" s="123"/>
-      <c r="O42" s="124"/>
-      <c r="P42" s="125"/>
+      <c r="C42" s="140"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="144"/>
+      <c r="I42" s="145"/>
+      <c r="J42" s="145"/>
+      <c r="K42" s="145"/>
+      <c r="L42" s="145"/>
+      <c r="M42" s="146"/>
+      <c r="N42" s="141"/>
+      <c r="O42" s="142"/>
+      <c r="P42" s="143"/>
       <c r="Q42" s="46"/>
-      <c r="R42" s="126"/>
-      <c r="S42" s="126"/>
+      <c r="R42" s="139"/>
+      <c r="S42" s="139"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="46"/>
       <c r="B43" s="46"/>
-      <c r="C43" s="119"/>
-      <c r="D43" s="119"/>
-      <c r="E43" s="119"/>
-      <c r="F43" s="119"/>
-      <c r="G43" s="119"/>
-      <c r="H43" s="120"/>
-      <c r="I43" s="121"/>
-      <c r="J43" s="121"/>
-      <c r="K43" s="121"/>
-      <c r="L43" s="121"/>
-      <c r="M43" s="122"/>
-      <c r="N43" s="123"/>
-      <c r="O43" s="124"/>
-      <c r="P43" s="125"/>
+      <c r="C43" s="140"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="144"/>
+      <c r="I43" s="145"/>
+      <c r="J43" s="145"/>
+      <c r="K43" s="145"/>
+      <c r="L43" s="145"/>
+      <c r="M43" s="146"/>
+      <c r="N43" s="141"/>
+      <c r="O43" s="142"/>
+      <c r="P43" s="143"/>
       <c r="Q43" s="46"/>
-      <c r="R43" s="126"/>
-      <c r="S43" s="126"/>
+      <c r="R43" s="139"/>
+      <c r="S43" s="139"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="46"/>
       <c r="B44" s="46"/>
-      <c r="C44" s="119"/>
-      <c r="D44" s="119"/>
-      <c r="E44" s="119"/>
-      <c r="F44" s="119"/>
-      <c r="G44" s="119"/>
-      <c r="H44" s="120"/>
-      <c r="I44" s="121"/>
-      <c r="J44" s="121"/>
-      <c r="K44" s="121"/>
-      <c r="L44" s="121"/>
-      <c r="M44" s="122"/>
-      <c r="N44" s="123"/>
-      <c r="O44" s="124"/>
-      <c r="P44" s="125"/>
+      <c r="C44" s="140"/>
+      <c r="D44" s="140"/>
+      <c r="E44" s="140"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="140"/>
+      <c r="H44" s="144"/>
+      <c r="I44" s="145"/>
+      <c r="J44" s="145"/>
+      <c r="K44" s="145"/>
+      <c r="L44" s="145"/>
+      <c r="M44" s="146"/>
+      <c r="N44" s="141"/>
+      <c r="O44" s="142"/>
+      <c r="P44" s="143"/>
       <c r="Q44" s="46"/>
-      <c r="R44" s="126"/>
-      <c r="S44" s="126"/>
+      <c r="R44" s="139"/>
+      <c r="S44" s="139"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="46"/>
       <c r="B45" s="46"/>
-      <c r="C45" s="119"/>
-      <c r="D45" s="119"/>
-      <c r="E45" s="119"/>
-      <c r="F45" s="119"/>
-      <c r="G45" s="119"/>
-      <c r="H45" s="120"/>
-      <c r="I45" s="121"/>
-      <c r="J45" s="121"/>
-      <c r="K45" s="121"/>
-      <c r="L45" s="121"/>
-      <c r="M45" s="122"/>
-      <c r="N45" s="123"/>
-      <c r="O45" s="124"/>
-      <c r="P45" s="125"/>
+      <c r="C45" s="140"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="144"/>
+      <c r="I45" s="145"/>
+      <c r="J45" s="145"/>
+      <c r="K45" s="145"/>
+      <c r="L45" s="145"/>
+      <c r="M45" s="146"/>
+      <c r="N45" s="141"/>
+      <c r="O45" s="142"/>
+      <c r="P45" s="143"/>
       <c r="Q45" s="46"/>
-      <c r="R45" s="126"/>
-      <c r="S45" s="126"/>
+      <c r="R45" s="139"/>
+      <c r="S45" s="139"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="46"/>
       <c r="B46" s="46"/>
-      <c r="C46" s="119"/>
-      <c r="D46" s="119"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="119"/>
-      <c r="G46" s="119"/>
-      <c r="H46" s="120"/>
-      <c r="I46" s="121"/>
-      <c r="J46" s="121"/>
-      <c r="K46" s="121"/>
-      <c r="L46" s="121"/>
-      <c r="M46" s="122"/>
-      <c r="N46" s="123"/>
-      <c r="O46" s="124"/>
-      <c r="P46" s="125"/>
+      <c r="C46" s="140"/>
+      <c r="D46" s="140"/>
+      <c r="E46" s="140"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="144"/>
+      <c r="I46" s="145"/>
+      <c r="J46" s="145"/>
+      <c r="K46" s="145"/>
+      <c r="L46" s="145"/>
+      <c r="M46" s="146"/>
+      <c r="N46" s="141"/>
+      <c r="O46" s="142"/>
+      <c r="P46" s="143"/>
       <c r="Q46" s="46"/>
-      <c r="R46" s="126"/>
-      <c r="S46" s="126"/>
+      <c r="R46" s="139"/>
+      <c r="S46" s="139"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="46"/>
       <c r="B47" s="46"/>
-      <c r="C47" s="119"/>
-      <c r="D47" s="119"/>
-      <c r="E47" s="119"/>
-      <c r="F47" s="119"/>
-      <c r="G47" s="119"/>
-      <c r="H47" s="120"/>
-      <c r="I47" s="121"/>
-      <c r="J47" s="121"/>
-      <c r="K47" s="121"/>
-      <c r="L47" s="121"/>
-      <c r="M47" s="122"/>
-      <c r="N47" s="123"/>
-      <c r="O47" s="124"/>
-      <c r="P47" s="125"/>
+      <c r="C47" s="140"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="144"/>
+      <c r="I47" s="145"/>
+      <c r="J47" s="145"/>
+      <c r="K47" s="145"/>
+      <c r="L47" s="145"/>
+      <c r="M47" s="146"/>
+      <c r="N47" s="141"/>
+      <c r="O47" s="142"/>
+      <c r="P47" s="143"/>
       <c r="Q47" s="46"/>
-      <c r="R47" s="126"/>
-      <c r="S47" s="126"/>
+      <c r="R47" s="139"/>
+      <c r="S47" s="139"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="46"/>
       <c r="B48" s="46"/>
-      <c r="C48" s="119"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="119"/>
-      <c r="F48" s="119"/>
-      <c r="G48" s="119"/>
-      <c r="H48" s="120"/>
-      <c r="I48" s="121"/>
-      <c r="J48" s="121"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="122"/>
-      <c r="N48" s="123"/>
-      <c r="O48" s="124"/>
-      <c r="P48" s="125"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="144"/>
+      <c r="I48" s="145"/>
+      <c r="J48" s="145"/>
+      <c r="K48" s="145"/>
+      <c r="L48" s="145"/>
+      <c r="M48" s="146"/>
+      <c r="N48" s="141"/>
+      <c r="O48" s="142"/>
+      <c r="P48" s="143"/>
       <c r="Q48" s="46"/>
-      <c r="R48" s="126"/>
-      <c r="S48" s="126"/>
+      <c r="R48" s="139"/>
+      <c r="S48" s="139"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="46"/>
       <c r="B49" s="46"/>
-      <c r="C49" s="119"/>
-      <c r="D49" s="119"/>
-      <c r="E49" s="119"/>
-      <c r="F49" s="119"/>
-      <c r="G49" s="119"/>
-      <c r="H49" s="120"/>
-      <c r="I49" s="121"/>
-      <c r="J49" s="121"/>
-      <c r="K49" s="121"/>
-      <c r="L49" s="121"/>
-      <c r="M49" s="122"/>
-      <c r="N49" s="123"/>
-      <c r="O49" s="124"/>
-      <c r="P49" s="125"/>
+      <c r="C49" s="140"/>
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="144"/>
+      <c r="I49" s="145"/>
+      <c r="J49" s="145"/>
+      <c r="K49" s="145"/>
+      <c r="L49" s="145"/>
+      <c r="M49" s="146"/>
+      <c r="N49" s="141"/>
+      <c r="O49" s="142"/>
+      <c r="P49" s="143"/>
       <c r="Q49" s="46"/>
-      <c r="R49" s="126"/>
-      <c r="S49" s="126"/>
+      <c r="R49" s="139"/>
+      <c r="S49" s="139"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="46"/>
       <c r="B50" s="46"/>
-      <c r="C50" s="119"/>
-      <c r="D50" s="119"/>
-      <c r="E50" s="119"/>
-      <c r="F50" s="119"/>
-      <c r="G50" s="119"/>
-      <c r="H50" s="120"/>
-      <c r="I50" s="121"/>
-      <c r="J50" s="121"/>
-      <c r="K50" s="121"/>
-      <c r="L50" s="121"/>
-      <c r="M50" s="122"/>
-      <c r="N50" s="123"/>
-      <c r="O50" s="124"/>
-      <c r="P50" s="125"/>
+      <c r="C50" s="140"/>
+      <c r="D50" s="140"/>
+      <c r="E50" s="140"/>
+      <c r="F50" s="140"/>
+      <c r="G50" s="140"/>
+      <c r="H50" s="144"/>
+      <c r="I50" s="145"/>
+      <c r="J50" s="145"/>
+      <c r="K50" s="145"/>
+      <c r="L50" s="145"/>
+      <c r="M50" s="146"/>
+      <c r="N50" s="141"/>
+      <c r="O50" s="142"/>
+      <c r="P50" s="143"/>
       <c r="Q50" s="46"/>
-      <c r="R50" s="126"/>
-      <c r="S50" s="126"/>
+      <c r="R50" s="139"/>
+      <c r="S50" s="139"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="46"/>
       <c r="B51" s="46"/>
-      <c r="C51" s="119"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="119"/>
-      <c r="F51" s="119"/>
-      <c r="G51" s="119"/>
-      <c r="H51" s="120"/>
-      <c r="I51" s="121"/>
-      <c r="J51" s="121"/>
-      <c r="K51" s="121"/>
-      <c r="L51" s="121"/>
-      <c r="M51" s="122"/>
-      <c r="N51" s="123"/>
-      <c r="O51" s="124"/>
-      <c r="P51" s="125"/>
+      <c r="C51" s="140"/>
+      <c r="D51" s="140"/>
+      <c r="E51" s="140"/>
+      <c r="F51" s="140"/>
+      <c r="G51" s="140"/>
+      <c r="H51" s="144"/>
+      <c r="I51" s="145"/>
+      <c r="J51" s="145"/>
+      <c r="K51" s="145"/>
+      <c r="L51" s="145"/>
+      <c r="M51" s="146"/>
+      <c r="N51" s="141"/>
+      <c r="O51" s="142"/>
+      <c r="P51" s="143"/>
       <c r="Q51" s="46"/>
-      <c r="R51" s="126"/>
-      <c r="S51" s="126"/>
+      <c r="R51" s="139"/>
+      <c r="S51" s="139"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="46"/>
       <c r="B52" s="46"/>
-      <c r="C52" s="119"/>
-      <c r="D52" s="119"/>
-      <c r="E52" s="119"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="119"/>
-      <c r="H52" s="120"/>
-      <c r="I52" s="121"/>
-      <c r="J52" s="121"/>
-      <c r="K52" s="121"/>
-      <c r="L52" s="121"/>
-      <c r="M52" s="122"/>
-      <c r="N52" s="123"/>
-      <c r="O52" s="124"/>
-      <c r="P52" s="125"/>
+      <c r="C52" s="140"/>
+      <c r="D52" s="140"/>
+      <c r="E52" s="140"/>
+      <c r="F52" s="140"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="144"/>
+      <c r="I52" s="145"/>
+      <c r="J52" s="145"/>
+      <c r="K52" s="145"/>
+      <c r="L52" s="145"/>
+      <c r="M52" s="146"/>
+      <c r="N52" s="141"/>
+      <c r="O52" s="142"/>
+      <c r="P52" s="143"/>
       <c r="Q52" s="46"/>
-      <c r="R52" s="126"/>
-      <c r="S52" s="126"/>
+      <c r="R52" s="139"/>
+      <c r="S52" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="204">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -10316,193 +10503,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/ログイン機能設計書.xlsx
+++ b/Documents/ログイン機能設計書.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC49AD79-DA41-43EE-BB62-23BCFF4FDE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B44849F-9397-4687-BC28-A29770564CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
     <sheet name="画面設計書" sheetId="1" r:id="rId2"/>
-    <sheet name="詳細クラス図" sheetId="2" r:id="rId3"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId4"/>
-    <sheet name="JUnitテスト仕様書兼報告書" sheetId="6" r:id="rId5"/>
+    <sheet name="画面遷移図" sheetId="7" r:id="rId3"/>
+    <sheet name="詳細クラス図" sheetId="2" r:id="rId4"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId5"/>
+    <sheet name="JUnitテスト仕様書兼報告書" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="ああ">#REF!</definedName>
-    <definedName name="範囲１" localSheetId="4">#REF!</definedName>
+    <definedName name="範囲１" localSheetId="5">#REF!</definedName>
     <definedName name="範囲１">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="124">
   <si>
     <t>備考</t>
   </si>
@@ -596,22 +597,6 @@
   </si>
   <si>
     <t>UserDAOTset</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>間違ったidを渡したときに、帰ってくる値がNullである</t>
-    <rPh sb="0" eb="2">
-      <t>マチガ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ワタ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>カエ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>アタイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -725,6 +710,22 @@
     </rPh>
     <rPh sb="36" eb="38">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面遷移図</t>
+  </si>
+  <si>
+    <t>間違ったidを渡したときに、かえってくる値がNullである</t>
+    <rPh sb="0" eb="2">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1675,7 +1676,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1824,12 +1825,54 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="9" fillId="0" borderId="62" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1863,21 +1906,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1923,68 +1951,73 @@
     <xf numFmtId="56" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1992,40 +2025,41 @@
     <xf numFmtId="56" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2036,18 +2070,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2086,30 +2108,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2627,6 +2625,61 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99DB8143-B329-9048-5662-E7F06656401F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="323850" y="1019175"/>
+          <a:ext cx="7772400" cy="4295775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -2984,19 +3037,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
@@ -3008,190 +3061,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="88"/>
+      <c r="F2" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="82">
+      <c r="G2" s="88"/>
+      <c r="H2" s="91">
         <v>45806</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="57"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="61" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="62"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66" t="s">
+      <c r="B6" s="52"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="67"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="55"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="66" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="67"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="66" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="67"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="55"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="92" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="67"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="65" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="55"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="89"/>
-      <c r="B10" s="91" t="s">
+      <c r="A10" s="62"/>
+      <c r="B10" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="67"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="55"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91" t="s">
+      <c r="A11" s="63"/>
+      <c r="B11" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="92" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="67"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="55"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="66" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="67"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="55"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="87"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="60"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4182,6 +4235,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -4197,18 +4262,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4231,19 +4284,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -4255,190 +4308,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="88"/>
+      <c r="F2" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="82">
+      <c r="G2" s="88"/>
+      <c r="H2" s="91">
         <v>45806</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="56"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="96" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="62"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="55"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="101"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="102"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="71"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="102"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="102"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="102"/>
+      <c r="A11" s="80"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="102"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="102"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="67"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="55"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="66" t="s">
+      <c r="B15" s="52"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="53"/>
       <c r="I15" s="6" t="s">
         <v>6</v>
       </c>
@@ -4447,11 +4500,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="94" t="s">
+      <c r="A16" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="6" t="s">
         <v>4</v>
       </c>
@@ -4464,18 +4517,18 @@
       <c r="G16" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H16" s="103" t="s">
+      <c r="H16" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="55"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="95">
+      <c r="A17" s="101">
         <v>1</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="53"/>
       <c r="D17" s="5" t="s">
         <v>32</v>
       </c>
@@ -4488,18 +4541,18 @@
       <c r="G17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="66" t="s">
+      <c r="H17" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="67"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="55"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="95">
+      <c r="A18" s="101">
         <v>2</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="53"/>
       <c r="D18" s="5" t="s">
         <v>33</v>
       </c>
@@ -4512,18 +4565,18 @@
       <c r="G18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="66" t="s">
+      <c r="H18" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="67"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="55"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="95">
+      <c r="A19" s="101">
         <v>3</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="53"/>
       <c r="D19" s="5" t="s">
         <v>34</v>
       </c>
@@ -4536,16 +4589,16 @@
       <c r="G19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="66"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="67"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="55"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="95">
+      <c r="A20" s="101">
         <v>4</v>
       </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="53"/>
       <c r="D20" s="5" t="s">
         <v>35</v>
       </c>
@@ -4556,45 +4609,45 @@
       <c r="G20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="66"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="67"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="55"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="95"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="53"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="67"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="55"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="95"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="53"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="67"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="55"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="93"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="58"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="87"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="60"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5575,21 +5628,6 @@
     <row r="1000" s="1" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
@@ -5606,6 +5644,21 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -5615,7 +5668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D23437D6-B8D1-427C-9F76-51987DC9E0DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D907A3-49F7-4B66-AE50-A8BA3432C908}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -5626,19 +5679,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="77" t="s">
+      <c r="A1" s="92" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="10" t="s">
         <v>15</v>
       </c>
@@ -5650,48 +5703,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="88"/>
+      <c r="F2" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="82">
-        <v>45810</v>
-      </c>
-      <c r="I2" s="52" t="s">
+      <c r="G2" s="88"/>
+      <c r="H2" s="91">
+        <v>45818</v>
+      </c>
+      <c r="I2" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="57"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="11"/>
@@ -6029,19 +6082,30 @@
       <c r="I32" s="12"/>
       <c r="J32" s="13"/>
     </row>
-    <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="14"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="16"/>
-    </row>
-    <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="13"/>
+    </row>
+    <row r="34" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A34" s="14"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="16"/>
+    </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6051,9 +6115,7 @@
     <row r="41" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="J44" s="17"/>
-    </row>
+    <row r="44" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="47" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7029,6 +7091,1420 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D23437D6-B8D1-427C-9F76-51987DC9E0DD}">
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="4.5" style="1" customWidth="1"/>
+    <col min="4" max="10" width="14.625" style="1" customWidth="1"/>
+    <col min="11" max="26" width="7.625" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="12.625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="86" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="74"/>
+      <c r="F1" s="86" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="74"/>
+      <c r="H1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="88"/>
+      <c r="F2" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="88"/>
+      <c r="H2" s="91">
+        <v>45810</v>
+      </c>
+      <c r="I2" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="69"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="13"/>
+    </row>
+    <row r="6" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="13"/>
+    </row>
+    <row r="9" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="13"/>
+    </row>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="13"/>
+    </row>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="13"/>
+    </row>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="13"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="13"/>
+    </row>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="13"/>
+    </row>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="13"/>
+    </row>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="13"/>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="13"/>
+    </row>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="13"/>
+    </row>
+    <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A33" s="14"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="16"/>
+    </row>
+    <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="39" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="40" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="41" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="44" spans="1:10" ht="12.75" customHeight="1">
+      <c r="J44" s="17"/>
+    </row>
+    <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="47" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19EAADF0-8FB5-466C-B7DB-2454AA8DCCC5}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
@@ -7042,190 +8518,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="77" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="77" t="s">
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="77" t="s">
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="77" t="s">
+      <c r="P1" s="74"/>
+      <c r="Q1" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="60"/>
-      <c r="S1" s="77" t="s">
+      <c r="R1" s="74"/>
+      <c r="S1" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="62"/>
+      <c r="T1" s="76"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="78" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="78" t="s">
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="105">
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="117">
         <v>45810</v>
       </c>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="78" t="s">
+      <c r="P2" s="88"/>
+      <c r="Q2" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="79"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="101"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="87"/>
+      <c r="T2" s="96"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="102"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="97"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="81"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="81"/>
-      <c r="T4" s="104"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="90"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="90"/>
+      <c r="T4" s="116"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="61" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="59"/>
-      <c r="Q5" s="59"/>
-      <c r="R5" s="59"/>
-      <c r="S5" s="59"/>
-      <c r="T5" s="62"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="76"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="66" t="s">
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="67"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="55"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="98" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="66" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="67"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="55"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="11"/>
@@ -7424,37 +8900,37 @@
       <c r="T14" s="13"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="112" t="s">
+      <c r="B15" s="53"/>
+      <c r="C15" s="115" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="103" t="s">
+      <c r="D15" s="53"/>
+      <c r="E15" s="99" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="103" t="s">
+      <c r="F15" s="53"/>
+      <c r="G15" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="103" t="s">
+      <c r="H15" s="52"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="99" t="s">
         <v>66</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="103" t="s">
+      <c r="K15" s="53"/>
+      <c r="L15" s="99" t="s">
         <v>67</v>
       </c>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="103" t="s">
+      <c r="M15" s="52"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="65"/>
+      <c r="P15" s="52"/>
+      <c r="Q15" s="53"/>
       <c r="R15" s="6" t="s">
         <v>69</v>
       </c>
@@ -7466,38 +8942,38 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="106">
+      <c r="A16" s="108">
         <v>1</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="107" t="s">
+      <c r="B16" s="53"/>
+      <c r="C16" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="107" t="s">
+      <c r="D16" s="53"/>
+      <c r="E16" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="108" t="s">
+      <c r="F16" s="53"/>
+      <c r="G16" s="110" t="s">
         <v>108</v>
       </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="108" t="s">
+      <c r="H16" s="52"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="109" t="s">
+      <c r="K16" s="53"/>
+      <c r="L16" s="113" t="s">
         <v>91</v>
       </c>
-      <c r="M16" s="110"/>
-      <c r="N16" s="110"/>
-      <c r="O16" s="111" t="s">
+      <c r="M16" s="114"/>
+      <c r="N16" s="114"/>
+      <c r="O16" s="107" t="s">
         <v>75</v>
       </c>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="65"/>
-      <c r="R16" s="51">
+      <c r="P16" s="52"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="50">
         <v>45810</v>
       </c>
       <c r="S16" s="31" t="s">
@@ -7514,38 +8990,38 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="75" customHeight="1">
-      <c r="A17" s="106">
+      <c r="A17" s="108">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="107" t="s">
+      <c r="B17" s="53"/>
+      <c r="C17" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="107" t="s">
+      <c r="D17" s="53"/>
+      <c r="E17" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="108" t="s">
+      <c r="F17" s="53"/>
+      <c r="G17" s="110" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="108" t="s">
+      <c r="H17" s="52"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="111" t="s">
+      <c r="K17" s="53"/>
+      <c r="L17" s="107" t="s">
         <v>92</v>
       </c>
-      <c r="M17" s="113"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="111" t="s">
+      <c r="M17" s="111"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="51">
+      <c r="P17" s="52"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="50">
         <v>45810</v>
       </c>
       <c r="S17" s="31" t="s">
@@ -7562,38 +9038,38 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="79.5" customHeight="1">
-      <c r="A18" s="106">
+      <c r="A18" s="108">
         <v>3</v>
       </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="107" t="s">
+      <c r="B18" s="53"/>
+      <c r="C18" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="107" t="s">
+      <c r="D18" s="53"/>
+      <c r="E18" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="108" t="s">
+      <c r="F18" s="53"/>
+      <c r="G18" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="64"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="108" t="s">
+      <c r="H18" s="52"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="K18" s="65"/>
-      <c r="L18" s="111" t="s">
+      <c r="K18" s="53"/>
+      <c r="L18" s="107" t="s">
         <v>79</v>
       </c>
-      <c r="M18" s="64"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="111" t="s">
-        <v>118</v>
-      </c>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="65"/>
-      <c r="R18" s="51">
+      <c r="M18" s="52"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="107" t="s">
+        <v>117</v>
+      </c>
+      <c r="P18" s="52"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="50">
         <v>45810</v>
       </c>
       <c r="S18" s="31" t="s">
@@ -7610,38 +9086,38 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="42.75" customHeight="1">
-      <c r="A19" s="106">
+      <c r="A19" s="108">
         <v>4</v>
       </c>
-      <c r="B19" s="65"/>
-      <c r="C19" s="107" t="s">
+      <c r="B19" s="53"/>
+      <c r="C19" s="109" t="s">
         <v>85</v>
       </c>
-      <c r="D19" s="65"/>
-      <c r="E19" s="107" t="s">
+      <c r="D19" s="53"/>
+      <c r="E19" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="65"/>
-      <c r="G19" s="108" t="s">
+      <c r="F19" s="53"/>
+      <c r="G19" s="110" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="108" t="s">
+      <c r="H19" s="52"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="110" t="s">
         <v>88</v>
       </c>
-      <c r="K19" s="65"/>
-      <c r="L19" s="111" t="s">
+      <c r="K19" s="53"/>
+      <c r="L19" s="107" t="s">
         <v>79</v>
       </c>
-      <c r="M19" s="64"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="111" t="s">
+      <c r="M19" s="52"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="65"/>
-      <c r="R19" s="51">
+      <c r="P19" s="52"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="50">
         <v>45810</v>
       </c>
       <c r="S19" s="31" t="s">
@@ -7658,23 +9134,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="106"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="108"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="108"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="109"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="52"/>
+      <c r="Q20" s="53"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -7686,23 +9162,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="106"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="108"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="107"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="107"/>
+      <c r="P21" s="52"/>
+      <c r="Q21" s="53"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -7714,23 +9190,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="106"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="107"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="109"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="107"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="107"/>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="53"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -7742,23 +9218,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="106"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="108"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="108"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="109"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="107"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="107"/>
+      <c r="P23" s="52"/>
+      <c r="Q23" s="53"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -7770,23 +9246,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="106"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="107"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="107"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="108"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="108"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="109"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="107"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="107"/>
+      <c r="P24" s="52"/>
+      <c r="Q24" s="53"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -7798,23 +9274,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="106"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="107"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="108"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="108"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="109"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="107"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="107"/>
+      <c r="P25" s="52"/>
+      <c r="Q25" s="53"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -7826,23 +9302,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="106"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="108"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="111"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="111"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="108"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="109"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="107"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="107"/>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="53"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -7854,23 +9330,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="106"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="107"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="111"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="108"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="107"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="107"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="53"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -7882,23 +9358,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="106"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="108"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="111"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="108"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="107"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="107"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="53"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -7910,23 +9386,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="106"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="107"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="107"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="108"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="109"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="107"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="107"/>
+      <c r="P29" s="52"/>
+      <c r="Q29" s="53"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -7938,23 +9414,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="106"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="107"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="107"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="111"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="108"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="109"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="107"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="107"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="53"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -7966,23 +9442,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="116"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="84"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="115"/>
-      <c r="P31" s="84"/>
-      <c r="Q31" s="85"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="57"/>
+      <c r="Q31" s="58"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -8980,6 +10456,121 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -9001,121 +10592,6 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -9126,7 +10602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1434AE2-ECA4-4D9B-945B-3109E1075373}">
   <dimension ref="A1:S52"/>
   <sheetFormatPr defaultColWidth="7" defaultRowHeight="11.25" customHeight="1"/>
@@ -9141,72 +10617,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="135" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="129" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="136" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="130"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="132" t="s">
+      <c r="D1" s="137"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="134"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="141"/>
       <c r="N1" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="132" t="s">
+      <c r="O1" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="134"/>
+      <c r="P1" s="141"/>
       <c r="Q1" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="R1" s="132" t="s">
+      <c r="R1" s="139" t="s">
         <v>96</v>
       </c>
-      <c r="S1" s="134"/>
+      <c r="S1" s="141"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="128"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="129" t="s">
+      <c r="A2" s="135"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="130"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="132" t="s">
+      <c r="D2" s="137"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="139" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="134"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="141"/>
       <c r="N2" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="135">
+      <c r="O2" s="142">
         <v>45807</v>
       </c>
-      <c r="P2" s="136"/>
+      <c r="P2" s="143"/>
       <c r="Q2" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="R2" s="137" t="s">
+      <c r="R2" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="138"/>
+      <c r="S2" s="145"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="40"/>
@@ -9236,33 +10712,33 @@
       <c r="B4" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="119" t="s">
+      <c r="D4" s="131"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="119" t="s">
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="132"/>
+      <c r="N4" s="130" t="s">
         <v>102</v>
       </c>
-      <c r="O4" s="120"/>
-      <c r="P4" s="121"/>
+      <c r="O4" s="131"/>
+      <c r="P4" s="132"/>
       <c r="Q4" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="R4" s="119" t="s">
+      <c r="R4" s="130" t="s">
         <v>104</v>
       </c>
-      <c r="S4" s="121"/>
+      <c r="S4" s="132"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="44">
@@ -9271,31 +10747,31 @@
       <c r="B5" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="122" t="s">
+      <c r="C5" s="126" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122" t="s">
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
-      <c r="K5" s="122"/>
-      <c r="L5" s="122"/>
-      <c r="M5" s="122"/>
-      <c r="N5" s="123" t="s">
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="126"/>
+      <c r="M5" s="126"/>
+      <c r="N5" s="127" t="s">
         <v>113</v>
       </c>
-      <c r="O5" s="124"/>
-      <c r="P5" s="125"/>
-      <c r="Q5" s="50">
+      <c r="O5" s="128"/>
+      <c r="P5" s="129"/>
+      <c r="Q5" s="47">
         <v>45810</v>
       </c>
-      <c r="R5" s="126"/>
-      <c r="S5" s="127"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="134"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="46">
@@ -9304,1188 +10780,997 @@
       <c r="B6" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="122" t="s">
+      <c r="C6" s="126" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122" t="s">
+      <c r="D6" s="126"/>
+      <c r="E6" s="126"/>
+      <c r="F6" s="126"/>
+      <c r="G6" s="126"/>
+      <c r="H6" s="126" t="s">
         <v>111</v>
       </c>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="123" t="s">
-        <v>117</v>
-      </c>
-      <c r="O6" s="124"/>
-      <c r="P6" s="125"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="126"/>
+      <c r="L6" s="126"/>
+      <c r="M6" s="126"/>
+      <c r="N6" s="127" t="s">
+        <v>123</v>
+      </c>
+      <c r="O6" s="128"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="47">
         <v>45810</v>
       </c>
-      <c r="R6" s="139"/>
-      <c r="S6" s="139"/>
+      <c r="R6" s="125"/>
+      <c r="S6" s="125"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
-      <c r="A7" s="46">
-        <v>3</v>
-      </c>
+      <c r="A7" s="46"/>
       <c r="B7" s="45"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="123"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="125"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="126"/>
+      <c r="M7" s="126"/>
+      <c r="N7" s="127"/>
+      <c r="O7" s="128"/>
+      <c r="P7" s="129"/>
       <c r="Q7" s="47"/>
-      <c r="R7" s="139"/>
-      <c r="S7" s="139"/>
+      <c r="R7" s="125"/>
+      <c r="S7" s="125"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
-      <c r="A8" s="46">
-        <v>4</v>
-      </c>
+      <c r="A8" s="46"/>
       <c r="B8" s="46"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
-      <c r="H8" s="122"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="122"/>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="126"/>
+      <c r="H8" s="126"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="126"/>
+      <c r="K8" s="126"/>
+      <c r="L8" s="126"/>
+      <c r="M8" s="126"/>
       <c r="Q8" s="47"/>
-      <c r="R8" s="139"/>
-      <c r="S8" s="139"/>
+      <c r="R8" s="125"/>
+      <c r="S8" s="125"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="46"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="140"/>
-      <c r="E9" s="140"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="140"/>
-      <c r="L9" s="140"/>
-      <c r="M9" s="140"/>
-      <c r="N9" s="141"/>
-      <c r="O9" s="142"/>
-      <c r="P9" s="143"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="122"/>
+      <c r="O9" s="123"/>
+      <c r="P9" s="124"/>
       <c r="Q9" s="46"/>
-      <c r="R9" s="139"/>
-      <c r="S9" s="139"/>
+      <c r="R9" s="125"/>
+      <c r="S9" s="125"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="140"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="145"/>
-      <c r="J10" s="145"/>
-      <c r="K10" s="145"/>
-      <c r="L10" s="145"/>
-      <c r="M10" s="146"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="142"/>
-      <c r="P10" s="143"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="120"/>
+      <c r="K10" s="120"/>
+      <c r="L10" s="120"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="123"/>
+      <c r="P10" s="124"/>
       <c r="Q10" s="47"/>
-      <c r="R10" s="139"/>
-      <c r="S10" s="139"/>
+      <c r="R10" s="125"/>
+      <c r="S10" s="125"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="46"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="145"/>
-      <c r="K11" s="145"/>
-      <c r="L11" s="145"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="141"/>
-      <c r="O11" s="142"/>
-      <c r="P11" s="143"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="118"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="120"/>
+      <c r="K11" s="120"/>
+      <c r="L11" s="120"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="123"/>
+      <c r="P11" s="124"/>
       <c r="Q11" s="46"/>
-      <c r="R11" s="139"/>
-      <c r="S11" s="139"/>
+      <c r="R11" s="125"/>
+      <c r="S11" s="125"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="46"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="140"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="140"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="145"/>
-      <c r="J12" s="145"/>
-      <c r="K12" s="145"/>
-      <c r="L12" s="145"/>
-      <c r="M12" s="146"/>
-      <c r="N12" s="141"/>
-      <c r="O12" s="142"/>
-      <c r="P12" s="143"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="120"/>
+      <c r="J12" s="120"/>
+      <c r="K12" s="120"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="122"/>
+      <c r="O12" s="123"/>
+      <c r="P12" s="124"/>
       <c r="Q12" s="46"/>
-      <c r="R12" s="139"/>
-      <c r="S12" s="139"/>
+      <c r="R12" s="125"/>
+      <c r="S12" s="125"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="46"/>
-      <c r="C13" s="140"/>
-      <c r="D13" s="140"/>
-      <c r="E13" s="140"/>
-      <c r="F13" s="140"/>
-      <c r="G13" s="140"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="145"/>
-      <c r="J13" s="145"/>
-      <c r="K13" s="145"/>
-      <c r="L13" s="145"/>
-      <c r="M13" s="146"/>
-      <c r="N13" s="141"/>
-      <c r="O13" s="142"/>
-      <c r="P13" s="143"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="120"/>
+      <c r="J13" s="120"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="122"/>
+      <c r="O13" s="123"/>
+      <c r="P13" s="124"/>
       <c r="Q13" s="46"/>
-      <c r="R13" s="139"/>
-      <c r="S13" s="139"/>
+      <c r="R13" s="125"/>
+      <c r="S13" s="125"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="140"/>
-      <c r="D14" s="140"/>
-      <c r="E14" s="140"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="145"/>
-      <c r="J14" s="145"/>
-      <c r="K14" s="145"/>
-      <c r="L14" s="145"/>
-      <c r="M14" s="146"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="142"/>
-      <c r="P14" s="143"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="122"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="124"/>
       <c r="Q14" s="46"/>
-      <c r="R14" s="139"/>
-      <c r="S14" s="139"/>
+      <c r="R14" s="125"/>
+      <c r="S14" s="125"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="46"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="140"/>
-      <c r="F15" s="140"/>
-      <c r="G15" s="140"/>
-      <c r="H15" s="144"/>
-      <c r="I15" s="145"/>
-      <c r="J15" s="145"/>
-      <c r="K15" s="145"/>
-      <c r="L15" s="145"/>
-      <c r="M15" s="146"/>
-      <c r="N15" s="141"/>
-      <c r="O15" s="142"/>
-      <c r="P15" s="143"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="120"/>
+      <c r="J15" s="120"/>
+      <c r="K15" s="120"/>
+      <c r="L15" s="120"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="124"/>
       <c r="Q15" s="46"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="46"/>
-      <c r="C16" s="140"/>
-      <c r="D16" s="140"/>
-      <c r="E16" s="140"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="145"/>
-      <c r="K16" s="145"/>
-      <c r="L16" s="145"/>
-      <c r="M16" s="146"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="142"/>
-      <c r="P16" s="143"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="122"/>
+      <c r="O16" s="123"/>
+      <c r="P16" s="124"/>
       <c r="Q16" s="46"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="139"/>
+      <c r="R16" s="125"/>
+      <c r="S16" s="125"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="46"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="140"/>
-      <c r="E17" s="140"/>
-      <c r="F17" s="140"/>
-      <c r="G17" s="140"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="145"/>
-      <c r="J17" s="145"/>
-      <c r="K17" s="145"/>
-      <c r="L17" s="145"/>
-      <c r="M17" s="146"/>
-      <c r="N17" s="141"/>
-      <c r="O17" s="142"/>
-      <c r="P17" s="143"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="124"/>
       <c r="Q17" s="46"/>
-      <c r="R17" s="139"/>
-      <c r="S17" s="139"/>
+      <c r="R17" s="125"/>
+      <c r="S17" s="125"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="46"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="140"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="140"/>
-      <c r="G18" s="140"/>
-      <c r="H18" s="144"/>
-      <c r="I18" s="145"/>
-      <c r="J18" s="145"/>
-      <c r="K18" s="145"/>
-      <c r="L18" s="145"/>
-      <c r="M18" s="146"/>
-      <c r="N18" s="141"/>
-      <c r="O18" s="142"/>
-      <c r="P18" s="143"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="122"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="124"/>
       <c r="Q18" s="46"/>
-      <c r="R18" s="139"/>
-      <c r="S18" s="139"/>
+      <c r="R18" s="125"/>
+      <c r="S18" s="125"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="46"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="140"/>
-      <c r="E19" s="140"/>
-      <c r="F19" s="140"/>
-      <c r="G19" s="140"/>
-      <c r="H19" s="144"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="146"/>
-      <c r="N19" s="141"/>
-      <c r="O19" s="142"/>
-      <c r="P19" s="143"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="120"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="122"/>
+      <c r="O19" s="123"/>
+      <c r="P19" s="124"/>
       <c r="Q19" s="46"/>
-      <c r="R19" s="139"/>
-      <c r="S19" s="139"/>
+      <c r="R19" s="125"/>
+      <c r="S19" s="125"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="46"/>
       <c r="B20" s="46"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="144"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="146"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="142"/>
-      <c r="P20" s="143"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="120"/>
+      <c r="L20" s="120"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="122"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="124"/>
       <c r="Q20" s="46"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="139"/>
+      <c r="R20" s="125"/>
+      <c r="S20" s="125"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="46"/>
       <c r="B21" s="46"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="140"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="145"/>
-      <c r="J21" s="145"/>
-      <c r="K21" s="145"/>
-      <c r="L21" s="145"/>
-      <c r="M21" s="146"/>
-      <c r="N21" s="141"/>
-      <c r="O21" s="142"/>
-      <c r="P21" s="143"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="120"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="120"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="122"/>
+      <c r="O21" s="123"/>
+      <c r="P21" s="124"/>
       <c r="Q21" s="46"/>
-      <c r="R21" s="139"/>
-      <c r="S21" s="139"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="125"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="46"/>
       <c r="B22" s="46"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="140"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="140"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="144"/>
-      <c r="I22" s="145"/>
-      <c r="J22" s="145"/>
-      <c r="K22" s="145"/>
-      <c r="L22" s="145"/>
-      <c r="M22" s="146"/>
-      <c r="N22" s="141"/>
-      <c r="O22" s="142"/>
-      <c r="P22" s="143"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="120"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="120"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="122"/>
+      <c r="O22" s="123"/>
+      <c r="P22" s="124"/>
       <c r="Q22" s="46"/>
-      <c r="R22" s="139"/>
-      <c r="S22" s="139"/>
+      <c r="R22" s="125"/>
+      <c r="S22" s="125"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="46"/>
       <c r="B23" s="46"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="140"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="140"/>
-      <c r="G23" s="140"/>
-      <c r="H23" s="144"/>
-      <c r="I23" s="145"/>
-      <c r="J23" s="145"/>
-      <c r="K23" s="145"/>
-      <c r="L23" s="145"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="141"/>
-      <c r="O23" s="142"/>
-      <c r="P23" s="143"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="120"/>
+      <c r="L23" s="120"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="122"/>
+      <c r="O23" s="123"/>
+      <c r="P23" s="124"/>
       <c r="Q23" s="46"/>
-      <c r="R23" s="139"/>
-      <c r="S23" s="139"/>
+      <c r="R23" s="125"/>
+      <c r="S23" s="125"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="46"/>
       <c r="B24" s="46"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="140"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="140"/>
-      <c r="G24" s="140"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="145"/>
-      <c r="J24" s="145"/>
-      <c r="K24" s="145"/>
-      <c r="L24" s="145"/>
-      <c r="M24" s="146"/>
-      <c r="N24" s="141"/>
-      <c r="O24" s="142"/>
-      <c r="P24" s="143"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="120"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="120"/>
+      <c r="L24" s="120"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="123"/>
+      <c r="P24" s="124"/>
       <c r="Q24" s="46"/>
-      <c r="R24" s="139"/>
-      <c r="S24" s="139"/>
+      <c r="R24" s="125"/>
+      <c r="S24" s="125"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="46"/>
       <c r="B25" s="46"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="144"/>
-      <c r="I25" s="145"/>
-      <c r="J25" s="145"/>
-      <c r="K25" s="145"/>
-      <c r="L25" s="145"/>
-      <c r="M25" s="146"/>
-      <c r="N25" s="141"/>
-      <c r="O25" s="142"/>
-      <c r="P25" s="143"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="120"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="120"/>
+      <c r="L25" s="120"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="122"/>
+      <c r="O25" s="123"/>
+      <c r="P25" s="124"/>
       <c r="Q25" s="46"/>
-      <c r="R25" s="139"/>
-      <c r="S25" s="139"/>
+      <c r="R25" s="125"/>
+      <c r="S25" s="125"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="46"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="144"/>
-      <c r="I26" s="145"/>
-      <c r="J26" s="145"/>
-      <c r="K26" s="145"/>
-      <c r="L26" s="145"/>
-      <c r="M26" s="146"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="142"/>
-      <c r="P26" s="143"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="118"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="120"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="120"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="121"/>
+      <c r="N26" s="122"/>
+      <c r="O26" s="123"/>
+      <c r="P26" s="124"/>
       <c r="Q26" s="46"/>
-      <c r="R26" s="139"/>
-      <c r="S26" s="139"/>
+      <c r="R26" s="125"/>
+      <c r="S26" s="125"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="46"/>
       <c r="B27" s="46"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="144"/>
-      <c r="I27" s="145"/>
-      <c r="J27" s="145"/>
-      <c r="K27" s="145"/>
-      <c r="L27" s="145"/>
-      <c r="M27" s="146"/>
-      <c r="N27" s="141"/>
-      <c r="O27" s="142"/>
-      <c r="P27" s="143"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="118"/>
+      <c r="G27" s="118"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="122"/>
+      <c r="O27" s="123"/>
+      <c r="P27" s="124"/>
       <c r="Q27" s="46"/>
-      <c r="R27" s="139"/>
-      <c r="S27" s="139"/>
+      <c r="R27" s="125"/>
+      <c r="S27" s="125"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="46"/>
       <c r="B28" s="46"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="144"/>
-      <c r="I28" s="145"/>
-      <c r="J28" s="145"/>
-      <c r="K28" s="145"/>
-      <c r="L28" s="145"/>
-      <c r="M28" s="146"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="142"/>
-      <c r="P28" s="143"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="122"/>
+      <c r="O28" s="123"/>
+      <c r="P28" s="124"/>
       <c r="Q28" s="46"/>
-      <c r="R28" s="139"/>
-      <c r="S28" s="139"/>
+      <c r="R28" s="125"/>
+      <c r="S28" s="125"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="46"/>
       <c r="B29" s="46"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="140"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="140"/>
-      <c r="H29" s="144"/>
-      <c r="I29" s="145"/>
-      <c r="J29" s="145"/>
-      <c r="K29" s="145"/>
-      <c r="L29" s="145"/>
-      <c r="M29" s="146"/>
-      <c r="N29" s="141"/>
-      <c r="O29" s="142"/>
-      <c r="P29" s="143"/>
+      <c r="C29" s="118"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="118"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="120"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="120"/>
+      <c r="L29" s="120"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="122"/>
+      <c r="O29" s="123"/>
+      <c r="P29" s="124"/>
       <c r="Q29" s="46"/>
-      <c r="R29" s="139"/>
-      <c r="S29" s="139"/>
+      <c r="R29" s="125"/>
+      <c r="S29" s="125"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="46"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="140"/>
-      <c r="H30" s="144"/>
-      <c r="I30" s="145"/>
-      <c r="J30" s="145"/>
-      <c r="K30" s="145"/>
-      <c r="L30" s="145"/>
-      <c r="M30" s="146"/>
-      <c r="N30" s="141"/>
-      <c r="O30" s="142"/>
-      <c r="P30" s="143"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="118"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="120"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="120"/>
+      <c r="L30" s="120"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="122"/>
+      <c r="O30" s="123"/>
+      <c r="P30" s="124"/>
       <c r="Q30" s="46"/>
-      <c r="R30" s="139"/>
-      <c r="S30" s="139"/>
+      <c r="R30" s="125"/>
+      <c r="S30" s="125"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="144"/>
-      <c r="I31" s="145"/>
-      <c r="J31" s="145"/>
-      <c r="K31" s="145"/>
-      <c r="L31" s="145"/>
-      <c r="M31" s="146"/>
-      <c r="N31" s="141"/>
-      <c r="O31" s="142"/>
-      <c r="P31" s="143"/>
+      <c r="C31" s="118"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="118"/>
+      <c r="G31" s="118"/>
+      <c r="H31" s="119"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="122"/>
+      <c r="O31" s="123"/>
+      <c r="P31" s="124"/>
       <c r="Q31" s="46"/>
-      <c r="R31" s="139"/>
-      <c r="S31" s="139"/>
+      <c r="R31" s="125"/>
+      <c r="S31" s="125"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="140"/>
-      <c r="G32" s="140"/>
-      <c r="H32" s="144"/>
-      <c r="I32" s="145"/>
-      <c r="J32" s="145"/>
-      <c r="K32" s="145"/>
-      <c r="L32" s="145"/>
-      <c r="M32" s="146"/>
-      <c r="N32" s="141"/>
-      <c r="O32" s="142"/>
-      <c r="P32" s="143"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="118"/>
+      <c r="H32" s="119"/>
+      <c r="I32" s="120"/>
+      <c r="J32" s="120"/>
+      <c r="K32" s="120"/>
+      <c r="L32" s="120"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="122"/>
+      <c r="O32" s="123"/>
+      <c r="P32" s="124"/>
       <c r="Q32" s="46"/>
-      <c r="R32" s="139"/>
-      <c r="S32" s="139"/>
+      <c r="R32" s="125"/>
+      <c r="S32" s="125"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="46"/>
       <c r="B33" s="46"/>
-      <c r="C33" s="140"/>
-      <c r="D33" s="140"/>
-      <c r="E33" s="140"/>
-      <c r="F33" s="140"/>
-      <c r="G33" s="140"/>
-      <c r="H33" s="144"/>
-      <c r="I33" s="145"/>
-      <c r="J33" s="145"/>
-      <c r="K33" s="145"/>
-      <c r="L33" s="145"/>
-      <c r="M33" s="146"/>
-      <c r="N33" s="141"/>
-      <c r="O33" s="142"/>
-      <c r="P33" s="143"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="118"/>
+      <c r="G33" s="118"/>
+      <c r="H33" s="119"/>
+      <c r="I33" s="120"/>
+      <c r="J33" s="120"/>
+      <c r="K33" s="120"/>
+      <c r="L33" s="120"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="122"/>
+      <c r="O33" s="123"/>
+      <c r="P33" s="124"/>
       <c r="Q33" s="46"/>
-      <c r="R33" s="139"/>
-      <c r="S33" s="139"/>
+      <c r="R33" s="125"/>
+      <c r="S33" s="125"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="46"/>
       <c r="B34" s="46"/>
-      <c r="C34" s="140"/>
-      <c r="D34" s="140"/>
-      <c r="E34" s="140"/>
-      <c r="F34" s="140"/>
-      <c r="G34" s="140"/>
-      <c r="H34" s="144"/>
-      <c r="I34" s="145"/>
-      <c r="J34" s="145"/>
-      <c r="K34" s="145"/>
-      <c r="L34" s="145"/>
-      <c r="M34" s="146"/>
-      <c r="N34" s="141"/>
-      <c r="O34" s="142"/>
-      <c r="P34" s="143"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="118"/>
+      <c r="F34" s="118"/>
+      <c r="G34" s="118"/>
+      <c r="H34" s="119"/>
+      <c r="I34" s="120"/>
+      <c r="J34" s="120"/>
+      <c r="K34" s="120"/>
+      <c r="L34" s="120"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="122"/>
+      <c r="O34" s="123"/>
+      <c r="P34" s="124"/>
       <c r="Q34" s="46"/>
-      <c r="R34" s="139"/>
-      <c r="S34" s="139"/>
+      <c r="R34" s="125"/>
+      <c r="S34" s="125"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
-      <c r="C35" s="140"/>
-      <c r="D35" s="140"/>
-      <c r="E35" s="140"/>
-      <c r="F35" s="140"/>
-      <c r="G35" s="140"/>
-      <c r="H35" s="144"/>
-      <c r="I35" s="145"/>
-      <c r="J35" s="145"/>
-      <c r="K35" s="145"/>
-      <c r="L35" s="145"/>
-      <c r="M35" s="146"/>
-      <c r="N35" s="141"/>
-      <c r="O35" s="142"/>
-      <c r="P35" s="143"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="119"/>
+      <c r="I35" s="120"/>
+      <c r="J35" s="120"/>
+      <c r="K35" s="120"/>
+      <c r="L35" s="120"/>
+      <c r="M35" s="121"/>
+      <c r="N35" s="122"/>
+      <c r="O35" s="123"/>
+      <c r="P35" s="124"/>
       <c r="Q35" s="46"/>
-      <c r="R35" s="139"/>
-      <c r="S35" s="139"/>
+      <c r="R35" s="125"/>
+      <c r="S35" s="125"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="46"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="140"/>
-      <c r="D36" s="140"/>
-      <c r="E36" s="140"/>
-      <c r="F36" s="140"/>
-      <c r="G36" s="140"/>
-      <c r="H36" s="144"/>
-      <c r="I36" s="145"/>
-      <c r="J36" s="145"/>
-      <c r="K36" s="145"/>
-      <c r="L36" s="145"/>
-      <c r="M36" s="146"/>
-      <c r="N36" s="141"/>
-      <c r="O36" s="142"/>
-      <c r="P36" s="143"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="118"/>
+      <c r="G36" s="118"/>
+      <c r="H36" s="119"/>
+      <c r="I36" s="120"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="120"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="122"/>
+      <c r="O36" s="123"/>
+      <c r="P36" s="124"/>
       <c r="Q36" s="46"/>
-      <c r="R36" s="139"/>
-      <c r="S36" s="139"/>
+      <c r="R36" s="125"/>
+      <c r="S36" s="125"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="46"/>
       <c r="B37" s="46"/>
-      <c r="C37" s="140"/>
-      <c r="D37" s="140"/>
-      <c r="E37" s="140"/>
-      <c r="F37" s="140"/>
-      <c r="G37" s="140"/>
-      <c r="H37" s="144"/>
-      <c r="I37" s="145"/>
-      <c r="J37" s="145"/>
-      <c r="K37" s="145"/>
-      <c r="L37" s="145"/>
-      <c r="M37" s="146"/>
-      <c r="N37" s="141"/>
-      <c r="O37" s="142"/>
-      <c r="P37" s="143"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="119"/>
+      <c r="I37" s="120"/>
+      <c r="J37" s="120"/>
+      <c r="K37" s="120"/>
+      <c r="L37" s="120"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="122"/>
+      <c r="O37" s="123"/>
+      <c r="P37" s="124"/>
       <c r="Q37" s="46"/>
-      <c r="R37" s="139"/>
-      <c r="S37" s="139"/>
+      <c r="R37" s="125"/>
+      <c r="S37" s="125"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="46"/>
       <c r="B38" s="46"/>
-      <c r="C38" s="140"/>
-      <c r="D38" s="140"/>
-      <c r="E38" s="140"/>
-      <c r="F38" s="140"/>
-      <c r="G38" s="140"/>
-      <c r="H38" s="144"/>
-      <c r="I38" s="145"/>
-      <c r="J38" s="145"/>
-      <c r="K38" s="145"/>
-      <c r="L38" s="145"/>
-      <c r="M38" s="146"/>
-      <c r="N38" s="141"/>
-      <c r="O38" s="142"/>
-      <c r="P38" s="143"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="119"/>
+      <c r="I38" s="120"/>
+      <c r="J38" s="120"/>
+      <c r="K38" s="120"/>
+      <c r="L38" s="120"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="122"/>
+      <c r="O38" s="123"/>
+      <c r="P38" s="124"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="139"/>
+      <c r="R38" s="125"/>
+      <c r="S38" s="125"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="46"/>
       <c r="B39" s="46"/>
-      <c r="C39" s="140"/>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="144"/>
-      <c r="I39" s="145"/>
-      <c r="J39" s="145"/>
-      <c r="K39" s="145"/>
-      <c r="L39" s="145"/>
-      <c r="M39" s="146"/>
-      <c r="N39" s="141"/>
-      <c r="O39" s="142"/>
-      <c r="P39" s="143"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="118"/>
+      <c r="H39" s="119"/>
+      <c r="I39" s="120"/>
+      <c r="J39" s="120"/>
+      <c r="K39" s="120"/>
+      <c r="L39" s="120"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="122"/>
+      <c r="O39" s="123"/>
+      <c r="P39" s="124"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="139"/>
-      <c r="S39" s="139"/>
+      <c r="R39" s="125"/>
+      <c r="S39" s="125"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="140"/>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="140"/>
-      <c r="H40" s="144"/>
-      <c r="I40" s="145"/>
-      <c r="J40" s="145"/>
-      <c r="K40" s="145"/>
-      <c r="L40" s="145"/>
-      <c r="M40" s="146"/>
-      <c r="N40" s="141"/>
-      <c r="O40" s="142"/>
-      <c r="P40" s="143"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="119"/>
+      <c r="I40" s="120"/>
+      <c r="J40" s="120"/>
+      <c r="K40" s="120"/>
+      <c r="L40" s="120"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="122"/>
+      <c r="O40" s="123"/>
+      <c r="P40" s="124"/>
       <c r="Q40" s="46"/>
-      <c r="R40" s="139"/>
-      <c r="S40" s="139"/>
+      <c r="R40" s="125"/>
+      <c r="S40" s="125"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="46"/>
       <c r="B41" s="46"/>
-      <c r="C41" s="140"/>
-      <c r="D41" s="140"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="140"/>
-      <c r="G41" s="140"/>
-      <c r="H41" s="144"/>
-      <c r="I41" s="145"/>
-      <c r="J41" s="145"/>
-      <c r="K41" s="145"/>
-      <c r="L41" s="145"/>
-      <c r="M41" s="146"/>
-      <c r="N41" s="141"/>
-      <c r="O41" s="142"/>
-      <c r="P41" s="143"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="119"/>
+      <c r="I41" s="120"/>
+      <c r="J41" s="120"/>
+      <c r="K41" s="120"/>
+      <c r="L41" s="120"/>
+      <c r="M41" s="121"/>
+      <c r="N41" s="122"/>
+      <c r="O41" s="123"/>
+      <c r="P41" s="124"/>
       <c r="Q41" s="46"/>
-      <c r="R41" s="139"/>
-      <c r="S41" s="139"/>
+      <c r="R41" s="125"/>
+      <c r="S41" s="125"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="46"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="140"/>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="140"/>
-      <c r="H42" s="144"/>
-      <c r="I42" s="145"/>
-      <c r="J42" s="145"/>
-      <c r="K42" s="145"/>
-      <c r="L42" s="145"/>
-      <c r="M42" s="146"/>
-      <c r="N42" s="141"/>
-      <c r="O42" s="142"/>
-      <c r="P42" s="143"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="118"/>
+      <c r="H42" s="119"/>
+      <c r="I42" s="120"/>
+      <c r="J42" s="120"/>
+      <c r="K42" s="120"/>
+      <c r="L42" s="120"/>
+      <c r="M42" s="121"/>
+      <c r="N42" s="122"/>
+      <c r="O42" s="123"/>
+      <c r="P42" s="124"/>
       <c r="Q42" s="46"/>
-      <c r="R42" s="139"/>
-      <c r="S42" s="139"/>
+      <c r="R42" s="125"/>
+      <c r="S42" s="125"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="46"/>
       <c r="B43" s="46"/>
-      <c r="C43" s="140"/>
-      <c r="D43" s="140"/>
-      <c r="E43" s="140"/>
-      <c r="F43" s="140"/>
-      <c r="G43" s="140"/>
-      <c r="H43" s="144"/>
-      <c r="I43" s="145"/>
-      <c r="J43" s="145"/>
-      <c r="K43" s="145"/>
-      <c r="L43" s="145"/>
-      <c r="M43" s="146"/>
-      <c r="N43" s="141"/>
-      <c r="O43" s="142"/>
-      <c r="P43" s="143"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="118"/>
+      <c r="G43" s="118"/>
+      <c r="H43" s="119"/>
+      <c r="I43" s="120"/>
+      <c r="J43" s="120"/>
+      <c r="K43" s="120"/>
+      <c r="L43" s="120"/>
+      <c r="M43" s="121"/>
+      <c r="N43" s="122"/>
+      <c r="O43" s="123"/>
+      <c r="P43" s="124"/>
       <c r="Q43" s="46"/>
-      <c r="R43" s="139"/>
-      <c r="S43" s="139"/>
+      <c r="R43" s="125"/>
+      <c r="S43" s="125"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="46"/>
       <c r="B44" s="46"/>
-      <c r="C44" s="140"/>
-      <c r="D44" s="140"/>
-      <c r="E44" s="140"/>
-      <c r="F44" s="140"/>
-      <c r="G44" s="140"/>
-      <c r="H44" s="144"/>
-      <c r="I44" s="145"/>
-      <c r="J44" s="145"/>
-      <c r="K44" s="145"/>
-      <c r="L44" s="145"/>
-      <c r="M44" s="146"/>
-      <c r="N44" s="141"/>
-      <c r="O44" s="142"/>
-      <c r="P44" s="143"/>
+      <c r="C44" s="118"/>
+      <c r="D44" s="118"/>
+      <c r="E44" s="118"/>
+      <c r="F44" s="118"/>
+      <c r="G44" s="118"/>
+      <c r="H44" s="119"/>
+      <c r="I44" s="120"/>
+      <c r="J44" s="120"/>
+      <c r="K44" s="120"/>
+      <c r="L44" s="120"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="122"/>
+      <c r="O44" s="123"/>
+      <c r="P44" s="124"/>
       <c r="Q44" s="46"/>
-      <c r="R44" s="139"/>
-      <c r="S44" s="139"/>
+      <c r="R44" s="125"/>
+      <c r="S44" s="125"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="46"/>
       <c r="B45" s="46"/>
-      <c r="C45" s="140"/>
-      <c r="D45" s="140"/>
-      <c r="E45" s="140"/>
-      <c r="F45" s="140"/>
-      <c r="G45" s="140"/>
-      <c r="H45" s="144"/>
-      <c r="I45" s="145"/>
-      <c r="J45" s="145"/>
-      <c r="K45" s="145"/>
-      <c r="L45" s="145"/>
-      <c r="M45" s="146"/>
-      <c r="N45" s="141"/>
-      <c r="O45" s="142"/>
-      <c r="P45" s="143"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="118"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="118"/>
+      <c r="H45" s="119"/>
+      <c r="I45" s="120"/>
+      <c r="J45" s="120"/>
+      <c r="K45" s="120"/>
+      <c r="L45" s="120"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="122"/>
+      <c r="O45" s="123"/>
+      <c r="P45" s="124"/>
       <c r="Q45" s="46"/>
-      <c r="R45" s="139"/>
-      <c r="S45" s="139"/>
+      <c r="R45" s="125"/>
+      <c r="S45" s="125"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="46"/>
       <c r="B46" s="46"/>
-      <c r="C46" s="140"/>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="140"/>
-      <c r="H46" s="144"/>
-      <c r="I46" s="145"/>
-      <c r="J46" s="145"/>
-      <c r="K46" s="145"/>
-      <c r="L46" s="145"/>
-      <c r="M46" s="146"/>
-      <c r="N46" s="141"/>
-      <c r="O46" s="142"/>
-      <c r="P46" s="143"/>
+      <c r="C46" s="118"/>
+      <c r="D46" s="118"/>
+      <c r="E46" s="118"/>
+      <c r="F46" s="118"/>
+      <c r="G46" s="118"/>
+      <c r="H46" s="119"/>
+      <c r="I46" s="120"/>
+      <c r="J46" s="120"/>
+      <c r="K46" s="120"/>
+      <c r="L46" s="120"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="122"/>
+      <c r="O46" s="123"/>
+      <c r="P46" s="124"/>
       <c r="Q46" s="46"/>
-      <c r="R46" s="139"/>
-      <c r="S46" s="139"/>
+      <c r="R46" s="125"/>
+      <c r="S46" s="125"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="46"/>
       <c r="B47" s="46"/>
-      <c r="C47" s="140"/>
-      <c r="D47" s="140"/>
-      <c r="E47" s="140"/>
-      <c r="F47" s="140"/>
-      <c r="G47" s="140"/>
-      <c r="H47" s="144"/>
-      <c r="I47" s="145"/>
-      <c r="J47" s="145"/>
-      <c r="K47" s="145"/>
-      <c r="L47" s="145"/>
-      <c r="M47" s="146"/>
-      <c r="N47" s="141"/>
-      <c r="O47" s="142"/>
-      <c r="P47" s="143"/>
+      <c r="C47" s="118"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="118"/>
+      <c r="G47" s="118"/>
+      <c r="H47" s="119"/>
+      <c r="I47" s="120"/>
+      <c r="J47" s="120"/>
+      <c r="K47" s="120"/>
+      <c r="L47" s="120"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="122"/>
+      <c r="O47" s="123"/>
+      <c r="P47" s="124"/>
       <c r="Q47" s="46"/>
-      <c r="R47" s="139"/>
-      <c r="S47" s="139"/>
+      <c r="R47" s="125"/>
+      <c r="S47" s="125"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="46"/>
       <c r="B48" s="46"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
-      <c r="F48" s="140"/>
-      <c r="G48" s="140"/>
-      <c r="H48" s="144"/>
-      <c r="I48" s="145"/>
-      <c r="J48" s="145"/>
-      <c r="K48" s="145"/>
-      <c r="L48" s="145"/>
-      <c r="M48" s="146"/>
-      <c r="N48" s="141"/>
-      <c r="O48" s="142"/>
-      <c r="P48" s="143"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="118"/>
+      <c r="H48" s="119"/>
+      <c r="I48" s="120"/>
+      <c r="J48" s="120"/>
+      <c r="K48" s="120"/>
+      <c r="L48" s="120"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="123"/>
+      <c r="P48" s="124"/>
       <c r="Q48" s="46"/>
-      <c r="R48" s="139"/>
-      <c r="S48" s="139"/>
+      <c r="R48" s="125"/>
+      <c r="S48" s="125"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="46"/>
       <c r="B49" s="46"/>
-      <c r="C49" s="140"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="140"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="140"/>
-      <c r="H49" s="144"/>
-      <c r="I49" s="145"/>
-      <c r="J49" s="145"/>
-      <c r="K49" s="145"/>
-      <c r="L49" s="145"/>
-      <c r="M49" s="146"/>
-      <c r="N49" s="141"/>
-      <c r="O49" s="142"/>
-      <c r="P49" s="143"/>
+      <c r="C49" s="118"/>
+      <c r="D49" s="118"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="G49" s="118"/>
+      <c r="H49" s="119"/>
+      <c r="I49" s="120"/>
+      <c r="J49" s="120"/>
+      <c r="K49" s="120"/>
+      <c r="L49" s="120"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="122"/>
+      <c r="O49" s="123"/>
+      <c r="P49" s="124"/>
       <c r="Q49" s="46"/>
-      <c r="R49" s="139"/>
-      <c r="S49" s="139"/>
+      <c r="R49" s="125"/>
+      <c r="S49" s="125"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="46"/>
       <c r="B50" s="46"/>
-      <c r="C50" s="140"/>
-      <c r="D50" s="140"/>
-      <c r="E50" s="140"/>
-      <c r="F50" s="140"/>
-      <c r="G50" s="140"/>
-      <c r="H50" s="144"/>
-      <c r="I50" s="145"/>
-      <c r="J50" s="145"/>
-      <c r="K50" s="145"/>
-      <c r="L50" s="145"/>
-      <c r="M50" s="146"/>
-      <c r="N50" s="141"/>
-      <c r="O50" s="142"/>
-      <c r="P50" s="143"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="118"/>
+      <c r="H50" s="119"/>
+      <c r="I50" s="120"/>
+      <c r="J50" s="120"/>
+      <c r="K50" s="120"/>
+      <c r="L50" s="120"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="122"/>
+      <c r="O50" s="123"/>
+      <c r="P50" s="124"/>
       <c r="Q50" s="46"/>
-      <c r="R50" s="139"/>
-      <c r="S50" s="139"/>
+      <c r="R50" s="125"/>
+      <c r="S50" s="125"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="46"/>
       <c r="B51" s="46"/>
-      <c r="C51" s="140"/>
-      <c r="D51" s="140"/>
-      <c r="E51" s="140"/>
-      <c r="F51" s="140"/>
-      <c r="G51" s="140"/>
-      <c r="H51" s="144"/>
-      <c r="I51" s="145"/>
-      <c r="J51" s="145"/>
-      <c r="K51" s="145"/>
-      <c r="L51" s="145"/>
-      <c r="M51" s="146"/>
-      <c r="N51" s="141"/>
-      <c r="O51" s="142"/>
-      <c r="P51" s="143"/>
+      <c r="C51" s="118"/>
+      <c r="D51" s="118"/>
+      <c r="E51" s="118"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="118"/>
+      <c r="H51" s="119"/>
+      <c r="I51" s="120"/>
+      <c r="J51" s="120"/>
+      <c r="K51" s="120"/>
+      <c r="L51" s="120"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="122"/>
+      <c r="O51" s="123"/>
+      <c r="P51" s="124"/>
       <c r="Q51" s="46"/>
-      <c r="R51" s="139"/>
-      <c r="S51" s="139"/>
+      <c r="R51" s="125"/>
+      <c r="S51" s="125"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="46"/>
       <c r="B52" s="46"/>
-      <c r="C52" s="140"/>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="140"/>
-      <c r="H52" s="144"/>
-      <c r="I52" s="145"/>
-      <c r="J52" s="145"/>
-      <c r="K52" s="145"/>
-      <c r="L52" s="145"/>
-      <c r="M52" s="146"/>
-      <c r="N52" s="141"/>
-      <c r="O52" s="142"/>
-      <c r="P52" s="143"/>
+      <c r="C52" s="118"/>
+      <c r="D52" s="118"/>
+      <c r="E52" s="118"/>
+      <c r="F52" s="118"/>
+      <c r="G52" s="118"/>
+      <c r="H52" s="119"/>
+      <c r="I52" s="120"/>
+      <c r="J52" s="120"/>
+      <c r="K52" s="120"/>
+      <c r="L52" s="120"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="122"/>
+      <c r="O52" s="123"/>
+      <c r="P52" s="124"/>
       <c r="Q52" s="46"/>
-      <c r="R52" s="139"/>
-      <c r="S52" s="139"/>
+      <c r="R52" s="125"/>
+      <c r="S52" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="204">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -10503,6 +11788,193 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
